--- a/uploads/inbox/SPV_CABIN_ROSTER_TEMPLATE.xlsx
+++ b/uploads/inbox/SPV_CABIN_ROSTER_TEMPLATE.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ROSTER" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'ROSTER'!$A$1:$AI$60</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'ROSTER'!$A$1:$AI$59</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="27">
+  <fonts count="33">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -30,11 +30,7 @@
     <font>
       <b val="1"/>
       <color rgb="00196B24"/>
-      <sz val="12"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <sz val="12"/>
+      <sz val="11"/>
     </font>
     <font>
       <b val="1"/>
@@ -42,17 +38,7 @@
     </font>
     <font>
       <b val="1"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00B45309"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="001F4E3D"/>
-      <sz val="11"/>
+      <sz val="10"/>
     </font>
     <font>
       <b val="1"/>
@@ -60,15 +46,52 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="00B45309"/>
       <sz val="10"/>
     </font>
     <font>
-      <color rgb="008A9299"/>
-      <sz val="8"/>
+      <b val="1"/>
+      <color rgb="001F4E3D"/>
+      <sz val="10"/>
     </font>
     <font>
+      <b val="1"/>
+      <sz val="7.5"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <color rgb="009AA2A9"/>
+      <sz val="7.5"/>
+    </font>
+    <font>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <b val="1"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="0092400E"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001A56DB"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00065F46"/>
+      <sz val="8.5"/>
     </font>
     <font>
       <b val="1"/>
@@ -81,9 +104,6 @@
       <sz val="9"/>
     </font>
     <font>
-      <sz val="8"/>
-    </font>
-    <font>
       <b val="1"/>
       <color rgb="001A56DB"/>
       <sz val="9"/>
@@ -94,59 +114,66 @@
       <sz val="9"/>
     </font>
     <font>
+      <sz val="7"/>
+    </font>
+    <font>
       <b val="1"/>
       <color rgb="005521B5"/>
-      <sz val="9"/>
+      <sz val="8.5"/>
     </font>
     <font>
       <b val="1"/>
       <color rgb="000E7490"/>
-      <sz val="9"/>
+      <sz val="8.5"/>
     </font>
     <font>
       <b val="1"/>
       <color rgb="006B7280"/>
-      <sz val="9"/>
+      <sz val="8.5"/>
     </font>
     <font>
       <b val="1"/>
       <color rgb="00F9FAFB"/>
-      <sz val="9"/>
+      <sz val="8.5"/>
     </font>
     <font>
       <b val="1"/>
       <color rgb="007E22CE"/>
-      <sz val="9"/>
+      <sz val="8.5"/>
     </font>
     <font>
       <b val="1"/>
       <color rgb="00C2410C"/>
-      <sz val="9"/>
+      <sz val="8.5"/>
     </font>
     <font>
       <b val="1"/>
       <color rgb="003730A3"/>
-      <sz val="9"/>
+      <sz val="8.5"/>
     </font>
     <font>
       <b val="1"/>
       <color rgb="00BE123C"/>
-      <sz val="9"/>
+      <sz val="8.5"/>
     </font>
     <font>
       <b val="1"/>
       <color rgb="003F6212"/>
-      <sz val="9"/>
+      <sz val="8.5"/>
     </font>
     <font>
       <b val="1"/>
       <color rgb="00475569"/>
-      <sz val="9"/>
+      <sz val="8.5"/>
     </font>
     <font>
       <b val="1"/>
       <color rgb="00713F12"/>
-      <sz val="9"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="7"/>
     </font>
   </fonts>
   <fills count="21">
@@ -252,7 +279,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -275,16 +302,84 @@
       </bottom>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00C9CFD6"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C9CFD6"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C9CFD6"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C9CFD6"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C9CFD6"/>
+      </top>
       <bottom style="thin">
-        <color rgb="004A5560"/>
+        <color rgb="00C9CFD6"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C9CFD6"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C9CFD6"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C9CFD6"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00C9CFD6"/>
+      </bottom>
+      <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
       <top/>
       <bottom style="thin">
-        <color rgb="004A5560"/>
+        <color rgb="00C9CFD6"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C9CFD6"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00C9CFD6"/>
       </bottom>
       <diagonal/>
     </border>
@@ -292,59 +387,63 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -352,41 +451,66 @@
     <xf numFmtId="0" fontId="15" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="26" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="27" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="19" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="28" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="20" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="29" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="19" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="20" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -396,7 +520,7 @@
       <font>
         <b val="1"/>
         <color rgb="0092400E"/>
-        <sz val="9"/>
+        <sz val="8.5"/>
       </font>
       <fill>
         <patternFill patternType="solid">
@@ -408,7 +532,7 @@
       <font>
         <b val="1"/>
         <color rgb="001A56DB"/>
-        <sz val="9"/>
+        <sz val="8.5"/>
       </font>
       <fill>
         <patternFill patternType="solid">
@@ -420,7 +544,7 @@
       <font>
         <b val="1"/>
         <color rgb="00065F46"/>
-        <sz val="9"/>
+        <sz val="8.5"/>
       </font>
       <fill>
         <patternFill patternType="solid">
@@ -432,7 +556,7 @@
       <font>
         <b val="1"/>
         <color rgb="005521B5"/>
-        <sz val="9"/>
+        <sz val="8.5"/>
       </font>
       <fill>
         <patternFill patternType="solid">
@@ -444,7 +568,7 @@
       <font>
         <b val="1"/>
         <color rgb="000E7490"/>
-        <sz val="9"/>
+        <sz val="8.5"/>
       </font>
       <fill>
         <patternFill patternType="solid">
@@ -456,7 +580,7 @@
       <font>
         <b val="1"/>
         <color rgb="006B7280"/>
-        <sz val="9"/>
+        <sz val="8.5"/>
       </font>
       <fill>
         <patternFill patternType="solid">
@@ -468,7 +592,7 @@
       <font>
         <b val="1"/>
         <color rgb="00F9FAFB"/>
-        <sz val="9"/>
+        <sz val="8.5"/>
       </font>
       <fill>
         <patternFill patternType="solid">
@@ -480,7 +604,7 @@
       <font>
         <b val="1"/>
         <color rgb="007E22CE"/>
-        <sz val="9"/>
+        <sz val="8.5"/>
       </font>
       <fill>
         <patternFill patternType="solid">
@@ -492,7 +616,7 @@
       <font>
         <b val="1"/>
         <color rgb="00C2410C"/>
-        <sz val="9"/>
+        <sz val="8.5"/>
       </font>
       <fill>
         <patternFill patternType="solid">
@@ -504,7 +628,7 @@
       <font>
         <b val="1"/>
         <color rgb="003730A3"/>
-        <sz val="9"/>
+        <sz val="8.5"/>
       </font>
       <fill>
         <patternFill patternType="solid">
@@ -516,7 +640,7 @@
       <font>
         <b val="1"/>
         <color rgb="00BE123C"/>
-        <sz val="9"/>
+        <sz val="8.5"/>
       </font>
       <fill>
         <patternFill patternType="solid">
@@ -528,7 +652,7 @@
       <font>
         <b val="1"/>
         <color rgb="003F6212"/>
-        <sz val="9"/>
+        <sz val="8.5"/>
       </font>
       <fill>
         <patternFill patternType="solid">
@@ -540,7 +664,7 @@
       <font>
         <b val="1"/>
         <color rgb="00475569"/>
-        <sz val="9"/>
+        <sz val="8.5"/>
       </font>
       <fill>
         <patternFill patternType="solid">
@@ -552,7 +676,7 @@
       <font>
         <b val="1"/>
         <color rgb="00713F12"/>
-        <sz val="9"/>
+        <sz val="8.5"/>
       </font>
       <fill>
         <patternFill patternType="solid">
@@ -927,50 +1051,50 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AK59"/>
+  <dimension ref="A1:AK60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="3.5" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="9.5" customWidth="1" min="4" max="4"/>
-    <col width="3.4" customWidth="1" min="5" max="5"/>
-    <col width="3.4" customWidth="1" min="6" max="6"/>
-    <col width="3.4" customWidth="1" min="7" max="7"/>
-    <col width="3.4" customWidth="1" min="8" max="8"/>
-    <col width="3.4" customWidth="1" min="9" max="9"/>
-    <col width="3.4" customWidth="1" min="10" max="10"/>
-    <col width="3.4" customWidth="1" min="11" max="11"/>
-    <col width="3.4" customWidth="1" min="12" max="12"/>
-    <col width="3.4" customWidth="1" min="13" max="13"/>
-    <col width="3.4" customWidth="1" min="14" max="14"/>
-    <col width="3.4" customWidth="1" min="15" max="15"/>
-    <col width="3.4" customWidth="1" min="16" max="16"/>
-    <col width="3.4" customWidth="1" min="17" max="17"/>
-    <col width="3.4" customWidth="1" min="18" max="18"/>
-    <col width="3.4" customWidth="1" min="19" max="19"/>
-    <col width="3.4" customWidth="1" min="20" max="20"/>
-    <col width="3.4" customWidth="1" min="21" max="21"/>
-    <col width="3.4" customWidth="1" min="22" max="22"/>
-    <col width="3.4" customWidth="1" min="23" max="23"/>
-    <col width="3.4" customWidth="1" min="24" max="24"/>
-    <col width="3.4" customWidth="1" min="25" max="25"/>
-    <col width="3.4" customWidth="1" min="26" max="26"/>
-    <col width="3.4" customWidth="1" min="27" max="27"/>
-    <col width="3.4" customWidth="1" min="28" max="28"/>
-    <col width="3.4" customWidth="1" min="29" max="29"/>
-    <col width="3.4" customWidth="1" min="30" max="30"/>
-    <col width="3.4" customWidth="1" min="31" max="31"/>
-    <col width="3.4" customWidth="1" min="32" max="32"/>
-    <col width="3.4" customWidth="1" min="33" max="33"/>
-    <col width="3.4" customWidth="1" min="34" max="34"/>
-    <col width="3.4" customWidth="1" min="35" max="35"/>
+    <col width="6.4" customWidth="1" min="1" max="1"/>
+    <col width="9.5" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="8.800000000000001" customWidth="1" min="4" max="4"/>
+    <col width="3.5" customWidth="1" min="5" max="5"/>
+    <col width="3.5" customWidth="1" min="6" max="6"/>
+    <col width="3.5" customWidth="1" min="7" max="7"/>
+    <col width="3.5" customWidth="1" min="8" max="8"/>
+    <col width="3.5" customWidth="1" min="9" max="9"/>
+    <col width="3.5" customWidth="1" min="10" max="10"/>
+    <col width="3.5" customWidth="1" min="11" max="11"/>
+    <col width="3.5" customWidth="1" min="12" max="12"/>
+    <col width="3.5" customWidth="1" min="13" max="13"/>
+    <col width="3.5" customWidth="1" min="14" max="14"/>
+    <col width="3.5" customWidth="1" min="15" max="15"/>
+    <col width="3.5" customWidth="1" min="16" max="16"/>
+    <col width="3.5" customWidth="1" min="17" max="17"/>
+    <col width="3.5" customWidth="1" min="18" max="18"/>
+    <col width="3.5" customWidth="1" min="19" max="19"/>
+    <col width="3.5" customWidth="1" min="20" max="20"/>
+    <col width="3.5" customWidth="1" min="21" max="21"/>
+    <col width="3.5" customWidth="1" min="22" max="22"/>
+    <col width="3.5" customWidth="1" min="23" max="23"/>
+    <col width="3.5" customWidth="1" min="24" max="24"/>
+    <col width="3.5" customWidth="1" min="25" max="25"/>
+    <col width="3.5" customWidth="1" min="26" max="26"/>
+    <col width="3.5" customWidth="1" min="27" max="27"/>
+    <col width="3.5" customWidth="1" min="28" max="28"/>
+    <col width="3.5" customWidth="1" min="29" max="29"/>
+    <col width="3.5" customWidth="1" min="30" max="30"/>
+    <col width="3.5" customWidth="1" min="31" max="31"/>
+    <col width="3.5" customWidth="1" min="32" max="32"/>
+    <col width="3.5" customWidth="1" min="33" max="33"/>
+    <col width="3.5" customWidth="1" min="34" max="34"/>
+    <col width="3.5" customWidth="1" min="35" max="35"/>
     <col hidden="1" width="13" customWidth="1" min="37" max="37"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="18" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>SAUDIA TECHNIC</t>
@@ -981,16 +1105,16 @@
           <t>AIRCRAFT HEAVY MAINTENANCE · SPV CABIN — MONTHLY ROSTER</t>
         </is>
       </c>
-      <c r="Z1" s="3" t="inlineStr">
+      <c r="AF1" s="3" t="inlineStr">
         <is>
           <t>CC: 264</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>MONTH:</t>
+    <row r="2" ht="16" customHeight="1">
+      <c r="A2" s="42" t="inlineStr">
+        <is>
+          <t>MONTH</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
@@ -1000,7 +1124,7 @@
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>YEAR:</t>
+          <t>YEAR</t>
         </is>
       </c>
       <c r="D2" s="5" t="n">
@@ -1015,7 +1139,7 @@
         <v/>
       </c>
     </row>
-    <row r="3">
+    <row r="3" ht="12" customHeight="1">
       <c r="E3" s="7">
         <f>IF(1&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,1),"ddd"),"")</f>
         <v/>
@@ -1141,7 +1265,7 @@
         <v/>
       </c>
     </row>
-    <row r="4">
+    <row r="4" ht="14" customHeight="1">
       <c r="A4" s="8" t="inlineStr">
         <is>
           <t>#</t>
@@ -1287,7 +1411,7 @@
         <v/>
       </c>
     </row>
-    <row r="5" ht="16" customHeight="1">
+    <row r="5" ht="15" customHeight="1">
       <c r="A5" s="9" t="inlineStr">
         <is>
           <t>CREW 1</t>
@@ -1325,7 +1449,7 @@
       <c r="AH5" s="10" t="n"/>
       <c r="AI5" s="10" t="n"/>
     </row>
-    <row r="6">
+    <row r="6" ht="14.5" customHeight="1">
       <c r="A6" s="11" t="n">
         <v>1</v>
       </c>
@@ -1364,7 +1488,7 @@
       <c r="AH6" s="13" t="n"/>
       <c r="AI6" s="13" t="n"/>
     </row>
-    <row r="7">
+    <row r="7" ht="14.5" customHeight="1">
       <c r="A7" s="11" t="n">
         <v>2</v>
       </c>
@@ -1403,7 +1527,7 @@
       <c r="AH7" s="13" t="n"/>
       <c r="AI7" s="13" t="n"/>
     </row>
-    <row r="8">
+    <row r="8" ht="14.5" customHeight="1">
       <c r="A8" s="11" t="n">
         <v>3</v>
       </c>
@@ -1442,7 +1566,7 @@
       <c r="AH8" s="13" t="n"/>
       <c r="AI8" s="13" t="n"/>
     </row>
-    <row r="9">
+    <row r="9" ht="14.5" customHeight="1">
       <c r="A9" s="11" t="n">
         <v>4</v>
       </c>
@@ -1481,7 +1605,7 @@
       <c r="AH9" s="13" t="n"/>
       <c r="AI9" s="13" t="n"/>
     </row>
-    <row r="10">
+    <row r="10" ht="14.5" customHeight="1">
       <c r="A10" s="11" t="n">
         <v>5</v>
       </c>
@@ -1520,7 +1644,7 @@
       <c r="AH10" s="13" t="n"/>
       <c r="AI10" s="13" t="n"/>
     </row>
-    <row r="11">
+    <row r="11" ht="14.5" customHeight="1">
       <c r="A11" s="11" t="n">
         <v>6</v>
       </c>
@@ -1559,7 +1683,7 @@
       <c r="AH11" s="13" t="n"/>
       <c r="AI11" s="13" t="n"/>
     </row>
-    <row r="12">
+    <row r="12" ht="14.5" customHeight="1">
       <c r="A12" s="11" t="n">
         <v>7</v>
       </c>
@@ -1598,7 +1722,7 @@
       <c r="AH12" s="13" t="n"/>
       <c r="AI12" s="13" t="n"/>
     </row>
-    <row r="13">
+    <row r="13" ht="14.5" customHeight="1">
       <c r="A13" s="11" t="n">
         <v>8</v>
       </c>
@@ -1637,7 +1761,7 @@
       <c r="AH13" s="13" t="n"/>
       <c r="AI13" s="13" t="n"/>
     </row>
-    <row r="14">
+    <row r="14" ht="14.5" customHeight="1">
       <c r="A14" s="11" t="n">
         <v>9</v>
       </c>
@@ -1676,7 +1800,7 @@
       <c r="AH14" s="13" t="n"/>
       <c r="AI14" s="13" t="n"/>
     </row>
-    <row r="15">
+    <row r="15" ht="14.5" customHeight="1">
       <c r="A15" s="11" t="n">
         <v>10</v>
       </c>
@@ -1715,7 +1839,7 @@
       <c r="AH15" s="13" t="n"/>
       <c r="AI15" s="13" t="n"/>
     </row>
-    <row r="16">
+    <row r="16" ht="14.5" customHeight="1">
       <c r="A16" s="11" t="n">
         <v>11</v>
       </c>
@@ -1754,7 +1878,7 @@
       <c r="AH16" s="13" t="n"/>
       <c r="AI16" s="13" t="n"/>
     </row>
-    <row r="17">
+    <row r="17" ht="14.5" customHeight="1">
       <c r="A17" s="11" t="n">
         <v>12</v>
       </c>
@@ -1793,47 +1917,86 @@
       <c r="AH17" s="13" t="n"/>
       <c r="AI17" s="13" t="n"/>
     </row>
-    <row r="19" ht="16" customHeight="1">
-      <c r="A19" s="14" t="inlineStr">
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" s="14" t="inlineStr">
         <is>
           <t>CREW 2</t>
         </is>
       </c>
-      <c r="E19" s="15" t="n"/>
-      <c r="F19" s="15" t="n"/>
-      <c r="G19" s="15" t="n"/>
-      <c r="H19" s="15" t="n"/>
-      <c r="I19" s="15" t="n"/>
-      <c r="J19" s="15" t="n"/>
-      <c r="K19" s="15" t="n"/>
-      <c r="L19" s="15" t="n"/>
-      <c r="M19" s="15" t="n"/>
-      <c r="N19" s="15" t="n"/>
-      <c r="O19" s="15" t="n"/>
-      <c r="P19" s="15" t="n"/>
-      <c r="Q19" s="15" t="n"/>
-      <c r="R19" s="15" t="n"/>
-      <c r="S19" s="15" t="n"/>
-      <c r="T19" s="15" t="n"/>
-      <c r="U19" s="15" t="n"/>
-      <c r="V19" s="15" t="n"/>
-      <c r="W19" s="15" t="n"/>
-      <c r="X19" s="15" t="n"/>
-      <c r="Y19" s="15" t="n"/>
-      <c r="Z19" s="15" t="n"/>
-      <c r="AA19" s="15" t="n"/>
-      <c r="AB19" s="15" t="n"/>
-      <c r="AC19" s="15" t="n"/>
-      <c r="AD19" s="15" t="n"/>
-      <c r="AE19" s="15" t="n"/>
-      <c r="AF19" s="15" t="n"/>
-      <c r="AG19" s="15" t="n"/>
-      <c r="AH19" s="15" t="n"/>
-      <c r="AI19" s="15" t="n"/>
-    </row>
-    <row r="20">
+      <c r="E18" s="15" t="n"/>
+      <c r="F18" s="15" t="n"/>
+      <c r="G18" s="15" t="n"/>
+      <c r="H18" s="15" t="n"/>
+      <c r="I18" s="15" t="n"/>
+      <c r="J18" s="15" t="n"/>
+      <c r="K18" s="15" t="n"/>
+      <c r="L18" s="15" t="n"/>
+      <c r="M18" s="15" t="n"/>
+      <c r="N18" s="15" t="n"/>
+      <c r="O18" s="15" t="n"/>
+      <c r="P18" s="15" t="n"/>
+      <c r="Q18" s="15" t="n"/>
+      <c r="R18" s="15" t="n"/>
+      <c r="S18" s="15" t="n"/>
+      <c r="T18" s="15" t="n"/>
+      <c r="U18" s="15" t="n"/>
+      <c r="V18" s="15" t="n"/>
+      <c r="W18" s="15" t="n"/>
+      <c r="X18" s="15" t="n"/>
+      <c r="Y18" s="15" t="n"/>
+      <c r="Z18" s="15" t="n"/>
+      <c r="AA18" s="15" t="n"/>
+      <c r="AB18" s="15" t="n"/>
+      <c r="AC18" s="15" t="n"/>
+      <c r="AD18" s="15" t="n"/>
+      <c r="AE18" s="15" t="n"/>
+      <c r="AF18" s="15" t="n"/>
+      <c r="AG18" s="15" t="n"/>
+      <c r="AH18" s="15" t="n"/>
+      <c r="AI18" s="15" t="n"/>
+    </row>
+    <row r="19" ht="14.5" customHeight="1">
+      <c r="A19" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="B19" s="11" t="n"/>
+      <c r="C19" s="12" t="n"/>
+      <c r="D19" s="11" t="n"/>
+      <c r="E19" s="13" t="n"/>
+      <c r="F19" s="13" t="n"/>
+      <c r="G19" s="13" t="n"/>
+      <c r="H19" s="13" t="n"/>
+      <c r="I19" s="13" t="n"/>
+      <c r="J19" s="13" t="n"/>
+      <c r="K19" s="13" t="n"/>
+      <c r="L19" s="13" t="n"/>
+      <c r="M19" s="13" t="n"/>
+      <c r="N19" s="13" t="n"/>
+      <c r="O19" s="13" t="n"/>
+      <c r="P19" s="13" t="n"/>
+      <c r="Q19" s="13" t="n"/>
+      <c r="R19" s="13" t="n"/>
+      <c r="S19" s="13" t="n"/>
+      <c r="T19" s="13" t="n"/>
+      <c r="U19" s="13" t="n"/>
+      <c r="V19" s="13" t="n"/>
+      <c r="W19" s="13" t="n"/>
+      <c r="X19" s="13" t="n"/>
+      <c r="Y19" s="13" t="n"/>
+      <c r="Z19" s="13" t="n"/>
+      <c r="AA19" s="13" t="n"/>
+      <c r="AB19" s="13" t="n"/>
+      <c r="AC19" s="13" t="n"/>
+      <c r="AD19" s="13" t="n"/>
+      <c r="AE19" s="13" t="n"/>
+      <c r="AF19" s="13" t="n"/>
+      <c r="AG19" s="13" t="n"/>
+      <c r="AH19" s="13" t="n"/>
+      <c r="AI19" s="13" t="n"/>
+    </row>
+    <row r="20" ht="14.5" customHeight="1">
       <c r="A20" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B20" s="11" t="n"/>
       <c r="C20" s="12" t="n"/>
@@ -1870,9 +2033,9 @@
       <c r="AH20" s="13" t="n"/>
       <c r="AI20" s="13" t="n"/>
     </row>
-    <row r="21">
+    <row r="21" ht="14.5" customHeight="1">
       <c r="A21" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B21" s="11" t="n"/>
       <c r="C21" s="12" t="n"/>
@@ -1909,9 +2072,9 @@
       <c r="AH21" s="13" t="n"/>
       <c r="AI21" s="13" t="n"/>
     </row>
-    <row r="22">
+    <row r="22" ht="14.5" customHeight="1">
       <c r="A22" s="11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B22" s="11" t="n"/>
       <c r="C22" s="12" t="n"/>
@@ -1948,9 +2111,9 @@
       <c r="AH22" s="13" t="n"/>
       <c r="AI22" s="13" t="n"/>
     </row>
-    <row r="23">
+    <row r="23" ht="14.5" customHeight="1">
       <c r="A23" s="11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B23" s="11" t="n"/>
       <c r="C23" s="12" t="n"/>
@@ -1987,9 +2150,9 @@
       <c r="AH23" s="13" t="n"/>
       <c r="AI23" s="13" t="n"/>
     </row>
-    <row r="24">
+    <row r="24" ht="14.5" customHeight="1">
       <c r="A24" s="11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B24" s="11" t="n"/>
       <c r="C24" s="12" t="n"/>
@@ -2026,9 +2189,9 @@
       <c r="AH24" s="13" t="n"/>
       <c r="AI24" s="13" t="n"/>
     </row>
-    <row r="25">
+    <row r="25" ht="14.5" customHeight="1">
       <c r="A25" s="11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B25" s="11" t="n"/>
       <c r="C25" s="12" t="n"/>
@@ -2065,9 +2228,9 @@
       <c r="AH25" s="13" t="n"/>
       <c r="AI25" s="13" t="n"/>
     </row>
-    <row r="26">
+    <row r="26" ht="14.5" customHeight="1">
       <c r="A26" s="11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B26" s="11" t="n"/>
       <c r="C26" s="12" t="n"/>
@@ -2104,9 +2267,9 @@
       <c r="AH26" s="13" t="n"/>
       <c r="AI26" s="13" t="n"/>
     </row>
-    <row r="27">
+    <row r="27" ht="14.5" customHeight="1">
       <c r="A27" s="11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B27" s="11" t="n"/>
       <c r="C27" s="12" t="n"/>
@@ -2143,9 +2306,9 @@
       <c r="AH27" s="13" t="n"/>
       <c r="AI27" s="13" t="n"/>
     </row>
-    <row r="28">
+    <row r="28" ht="14.5" customHeight="1">
       <c r="A28" s="11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B28" s="11" t="n"/>
       <c r="C28" s="12" t="n"/>
@@ -2182,9 +2345,9 @@
       <c r="AH28" s="13" t="n"/>
       <c r="AI28" s="13" t="n"/>
     </row>
-    <row r="29">
+    <row r="29" ht="14.5" customHeight="1">
       <c r="A29" s="11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B29" s="11" t="n"/>
       <c r="C29" s="12" t="n"/>
@@ -2221,9 +2384,9 @@
       <c r="AH29" s="13" t="n"/>
       <c r="AI29" s="13" t="n"/>
     </row>
-    <row r="30">
+    <row r="30" ht="14.5" customHeight="1">
       <c r="A30" s="11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B30" s="11" t="n"/>
       <c r="C30" s="12" t="n"/>
@@ -2260,86 +2423,125 @@
       <c r="AH30" s="13" t="n"/>
       <c r="AI30" s="13" t="n"/>
     </row>
-    <row r="31">
-      <c r="A31" s="11" t="n">
-        <v>12</v>
-      </c>
-      <c r="B31" s="11" t="n"/>
-      <c r="C31" s="12" t="n"/>
-      <c r="D31" s="11" t="n"/>
-      <c r="E31" s="13" t="n"/>
-      <c r="F31" s="13" t="n"/>
-      <c r="G31" s="13" t="n"/>
-      <c r="H31" s="13" t="n"/>
-      <c r="I31" s="13" t="n"/>
-      <c r="J31" s="13" t="n"/>
-      <c r="K31" s="13" t="n"/>
-      <c r="L31" s="13" t="n"/>
-      <c r="M31" s="13" t="n"/>
-      <c r="N31" s="13" t="n"/>
-      <c r="O31" s="13" t="n"/>
-      <c r="P31" s="13" t="n"/>
-      <c r="Q31" s="13" t="n"/>
-      <c r="R31" s="13" t="n"/>
-      <c r="S31" s="13" t="n"/>
-      <c r="T31" s="13" t="n"/>
-      <c r="U31" s="13" t="n"/>
-      <c r="V31" s="13" t="n"/>
-      <c r="W31" s="13" t="n"/>
-      <c r="X31" s="13" t="n"/>
-      <c r="Y31" s="13" t="n"/>
-      <c r="Z31" s="13" t="n"/>
-      <c r="AA31" s="13" t="n"/>
-      <c r="AB31" s="13" t="n"/>
-      <c r="AC31" s="13" t="n"/>
-      <c r="AD31" s="13" t="n"/>
-      <c r="AE31" s="13" t="n"/>
-      <c r="AF31" s="13" t="n"/>
-      <c r="AG31" s="13" t="n"/>
-      <c r="AH31" s="13" t="n"/>
-      <c r="AI31" s="13" t="n"/>
-    </row>
-    <row r="33" ht="16" customHeight="1">
-      <c r="A33" s="16" t="inlineStr">
+    <row r="31" ht="15" customHeight="1">
+      <c r="A31" s="16" t="inlineStr">
         <is>
           <t>CREW 3</t>
         </is>
       </c>
-      <c r="E33" s="17" t="n"/>
-      <c r="F33" s="17" t="n"/>
-      <c r="G33" s="17" t="n"/>
-      <c r="H33" s="17" t="n"/>
-      <c r="I33" s="17" t="n"/>
-      <c r="J33" s="17" t="n"/>
-      <c r="K33" s="17" t="n"/>
-      <c r="L33" s="17" t="n"/>
-      <c r="M33" s="17" t="n"/>
-      <c r="N33" s="17" t="n"/>
-      <c r="O33" s="17" t="n"/>
-      <c r="P33" s="17" t="n"/>
-      <c r="Q33" s="17" t="n"/>
-      <c r="R33" s="17" t="n"/>
-      <c r="S33" s="17" t="n"/>
-      <c r="T33" s="17" t="n"/>
-      <c r="U33" s="17" t="n"/>
-      <c r="V33" s="17" t="n"/>
-      <c r="W33" s="17" t="n"/>
-      <c r="X33" s="17" t="n"/>
-      <c r="Y33" s="17" t="n"/>
-      <c r="Z33" s="17" t="n"/>
-      <c r="AA33" s="17" t="n"/>
-      <c r="AB33" s="17" t="n"/>
-      <c r="AC33" s="17" t="n"/>
-      <c r="AD33" s="17" t="n"/>
-      <c r="AE33" s="17" t="n"/>
-      <c r="AF33" s="17" t="n"/>
-      <c r="AG33" s="17" t="n"/>
-      <c r="AH33" s="17" t="n"/>
-      <c r="AI33" s="17" t="n"/>
-    </row>
-    <row r="34">
+      <c r="E31" s="17" t="n"/>
+      <c r="F31" s="17" t="n"/>
+      <c r="G31" s="17" t="n"/>
+      <c r="H31" s="17" t="n"/>
+      <c r="I31" s="17" t="n"/>
+      <c r="J31" s="17" t="n"/>
+      <c r="K31" s="17" t="n"/>
+      <c r="L31" s="17" t="n"/>
+      <c r="M31" s="17" t="n"/>
+      <c r="N31" s="17" t="n"/>
+      <c r="O31" s="17" t="n"/>
+      <c r="P31" s="17" t="n"/>
+      <c r="Q31" s="17" t="n"/>
+      <c r="R31" s="17" t="n"/>
+      <c r="S31" s="17" t="n"/>
+      <c r="T31" s="17" t="n"/>
+      <c r="U31" s="17" t="n"/>
+      <c r="V31" s="17" t="n"/>
+      <c r="W31" s="17" t="n"/>
+      <c r="X31" s="17" t="n"/>
+      <c r="Y31" s="17" t="n"/>
+      <c r="Z31" s="17" t="n"/>
+      <c r="AA31" s="17" t="n"/>
+      <c r="AB31" s="17" t="n"/>
+      <c r="AC31" s="17" t="n"/>
+      <c r="AD31" s="17" t="n"/>
+      <c r="AE31" s="17" t="n"/>
+      <c r="AF31" s="17" t="n"/>
+      <c r="AG31" s="17" t="n"/>
+      <c r="AH31" s="17" t="n"/>
+      <c r="AI31" s="17" t="n"/>
+    </row>
+    <row r="32" ht="14.5" customHeight="1">
+      <c r="A32" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="B32" s="11" t="n"/>
+      <c r="C32" s="12" t="n"/>
+      <c r="D32" s="11" t="n"/>
+      <c r="E32" s="13" t="n"/>
+      <c r="F32" s="13" t="n"/>
+      <c r="G32" s="13" t="n"/>
+      <c r="H32" s="13" t="n"/>
+      <c r="I32" s="13" t="n"/>
+      <c r="J32" s="13" t="n"/>
+      <c r="K32" s="13" t="n"/>
+      <c r="L32" s="13" t="n"/>
+      <c r="M32" s="13" t="n"/>
+      <c r="N32" s="13" t="n"/>
+      <c r="O32" s="13" t="n"/>
+      <c r="P32" s="13" t="n"/>
+      <c r="Q32" s="13" t="n"/>
+      <c r="R32" s="13" t="n"/>
+      <c r="S32" s="13" t="n"/>
+      <c r="T32" s="13" t="n"/>
+      <c r="U32" s="13" t="n"/>
+      <c r="V32" s="13" t="n"/>
+      <c r="W32" s="13" t="n"/>
+      <c r="X32" s="13" t="n"/>
+      <c r="Y32" s="13" t="n"/>
+      <c r="Z32" s="13" t="n"/>
+      <c r="AA32" s="13" t="n"/>
+      <c r="AB32" s="13" t="n"/>
+      <c r="AC32" s="13" t="n"/>
+      <c r="AD32" s="13" t="n"/>
+      <c r="AE32" s="13" t="n"/>
+      <c r="AF32" s="13" t="n"/>
+      <c r="AG32" s="13" t="n"/>
+      <c r="AH32" s="13" t="n"/>
+      <c r="AI32" s="13" t="n"/>
+    </row>
+    <row r="33" ht="14.5" customHeight="1">
+      <c r="A33" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="B33" s="11" t="n"/>
+      <c r="C33" s="12" t="n"/>
+      <c r="D33" s="11" t="n"/>
+      <c r="E33" s="13" t="n"/>
+      <c r="F33" s="13" t="n"/>
+      <c r="G33" s="13" t="n"/>
+      <c r="H33" s="13" t="n"/>
+      <c r="I33" s="13" t="n"/>
+      <c r="J33" s="13" t="n"/>
+      <c r="K33" s="13" t="n"/>
+      <c r="L33" s="13" t="n"/>
+      <c r="M33" s="13" t="n"/>
+      <c r="N33" s="13" t="n"/>
+      <c r="O33" s="13" t="n"/>
+      <c r="P33" s="13" t="n"/>
+      <c r="Q33" s="13" t="n"/>
+      <c r="R33" s="13" t="n"/>
+      <c r="S33" s="13" t="n"/>
+      <c r="T33" s="13" t="n"/>
+      <c r="U33" s="13" t="n"/>
+      <c r="V33" s="13" t="n"/>
+      <c r="W33" s="13" t="n"/>
+      <c r="X33" s="13" t="n"/>
+      <c r="Y33" s="13" t="n"/>
+      <c r="Z33" s="13" t="n"/>
+      <c r="AA33" s="13" t="n"/>
+      <c r="AB33" s="13" t="n"/>
+      <c r="AC33" s="13" t="n"/>
+      <c r="AD33" s="13" t="n"/>
+      <c r="AE33" s="13" t="n"/>
+      <c r="AF33" s="13" t="n"/>
+      <c r="AG33" s="13" t="n"/>
+      <c r="AH33" s="13" t="n"/>
+      <c r="AI33" s="13" t="n"/>
+    </row>
+    <row r="34" ht="14.5" customHeight="1">
       <c r="A34" s="11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B34" s="11" t="n"/>
       <c r="C34" s="12" t="n"/>
@@ -2376,9 +2578,9 @@
       <c r="AH34" s="13" t="n"/>
       <c r="AI34" s="13" t="n"/>
     </row>
-    <row r="35">
+    <row r="35" ht="14.5" customHeight="1">
       <c r="A35" s="11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B35" s="11" t="n"/>
       <c r="C35" s="12" t="n"/>
@@ -2415,9 +2617,9 @@
       <c r="AH35" s="13" t="n"/>
       <c r="AI35" s="13" t="n"/>
     </row>
-    <row r="36">
+    <row r="36" ht="14.5" customHeight="1">
       <c r="A36" s="11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B36" s="11" t="n"/>
       <c r="C36" s="12" t="n"/>
@@ -2454,9 +2656,9 @@
       <c r="AH36" s="13" t="n"/>
       <c r="AI36" s="13" t="n"/>
     </row>
-    <row r="37">
+    <row r="37" ht="14.5" customHeight="1">
       <c r="A37" s="11" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B37" s="11" t="n"/>
       <c r="C37" s="12" t="n"/>
@@ -2493,9 +2695,9 @@
       <c r="AH37" s="13" t="n"/>
       <c r="AI37" s="13" t="n"/>
     </row>
-    <row r="38">
+    <row r="38" ht="14.5" customHeight="1">
       <c r="A38" s="11" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B38" s="11" t="n"/>
       <c r="C38" s="12" t="n"/>
@@ -2532,9 +2734,9 @@
       <c r="AH38" s="13" t="n"/>
       <c r="AI38" s="13" t="n"/>
     </row>
-    <row r="39">
+    <row r="39" ht="14.5" customHeight="1">
       <c r="A39" s="11" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B39" s="11" t="n"/>
       <c r="C39" s="12" t="n"/>
@@ -2571,9 +2773,9 @@
       <c r="AH39" s="13" t="n"/>
       <c r="AI39" s="13" t="n"/>
     </row>
-    <row r="40">
+    <row r="40" ht="14.5" customHeight="1">
       <c r="A40" s="11" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B40" s="11" t="n"/>
       <c r="C40" s="12" t="n"/>
@@ -2610,9 +2812,9 @@
       <c r="AH40" s="13" t="n"/>
       <c r="AI40" s="13" t="n"/>
     </row>
-    <row r="41">
+    <row r="41" ht="14.5" customHeight="1">
       <c r="A41" s="11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B41" s="11" t="n"/>
       <c r="C41" s="12" t="n"/>
@@ -2649,9 +2851,9 @@
       <c r="AH41" s="13" t="n"/>
       <c r="AI41" s="13" t="n"/>
     </row>
-    <row r="42">
+    <row r="42" ht="14.5" customHeight="1">
       <c r="A42" s="11" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B42" s="11" t="n"/>
       <c r="C42" s="12" t="n"/>
@@ -2688,9 +2890,9 @@
       <c r="AH42" s="13" t="n"/>
       <c r="AI42" s="13" t="n"/>
     </row>
-    <row r="43">
+    <row r="43" ht="14.5" customHeight="1">
       <c r="A43" s="11" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B43" s="11" t="n"/>
       <c r="C43" s="12" t="n"/>
@@ -2727,48 +2929,47 @@
       <c r="AH43" s="13" t="n"/>
       <c r="AI43" s="13" t="n"/>
     </row>
-    <row r="44">
-      <c r="A44" s="11" t="n">
-        <v>11</v>
-      </c>
-      <c r="B44" s="11" t="n"/>
-      <c r="C44" s="12" t="n"/>
-      <c r="D44" s="11" t="n"/>
-      <c r="E44" s="13" t="n"/>
-      <c r="F44" s="13" t="n"/>
-      <c r="G44" s="13" t="n"/>
-      <c r="H44" s="13" t="n"/>
-      <c r="I44" s="13" t="n"/>
-      <c r="J44" s="13" t="n"/>
-      <c r="K44" s="13" t="n"/>
-      <c r="L44" s="13" t="n"/>
-      <c r="M44" s="13" t="n"/>
-      <c r="N44" s="13" t="n"/>
-      <c r="O44" s="13" t="n"/>
-      <c r="P44" s="13" t="n"/>
-      <c r="Q44" s="13" t="n"/>
-      <c r="R44" s="13" t="n"/>
-      <c r="S44" s="13" t="n"/>
-      <c r="T44" s="13" t="n"/>
-      <c r="U44" s="13" t="n"/>
-      <c r="V44" s="13" t="n"/>
-      <c r="W44" s="13" t="n"/>
-      <c r="X44" s="13" t="n"/>
-      <c r="Y44" s="13" t="n"/>
-      <c r="Z44" s="13" t="n"/>
-      <c r="AA44" s="13" t="n"/>
-      <c r="AB44" s="13" t="n"/>
-      <c r="AC44" s="13" t="n"/>
-      <c r="AD44" s="13" t="n"/>
-      <c r="AE44" s="13" t="n"/>
-      <c r="AF44" s="13" t="n"/>
-      <c r="AG44" s="13" t="n"/>
-      <c r="AH44" s="13" t="n"/>
-      <c r="AI44" s="13" t="n"/>
-    </row>
-    <row r="45">
+    <row r="44" ht="15" customHeight="1">
+      <c r="A44" s="18" t="inlineStr">
+        <is>
+          <t>SPECIAL SHIFTING</t>
+        </is>
+      </c>
+      <c r="E44" s="19" t="n"/>
+      <c r="F44" s="19" t="n"/>
+      <c r="G44" s="19" t="n"/>
+      <c r="H44" s="19" t="n"/>
+      <c r="I44" s="19" t="n"/>
+      <c r="J44" s="19" t="n"/>
+      <c r="K44" s="19" t="n"/>
+      <c r="L44" s="19" t="n"/>
+      <c r="M44" s="19" t="n"/>
+      <c r="N44" s="19" t="n"/>
+      <c r="O44" s="19" t="n"/>
+      <c r="P44" s="19" t="n"/>
+      <c r="Q44" s="19" t="n"/>
+      <c r="R44" s="19" t="n"/>
+      <c r="S44" s="19" t="n"/>
+      <c r="T44" s="19" t="n"/>
+      <c r="U44" s="19" t="n"/>
+      <c r="V44" s="19" t="n"/>
+      <c r="W44" s="19" t="n"/>
+      <c r="X44" s="19" t="n"/>
+      <c r="Y44" s="19" t="n"/>
+      <c r="Z44" s="19" t="n"/>
+      <c r="AA44" s="19" t="n"/>
+      <c r="AB44" s="19" t="n"/>
+      <c r="AC44" s="19" t="n"/>
+      <c r="AD44" s="19" t="n"/>
+      <c r="AE44" s="19" t="n"/>
+      <c r="AF44" s="19" t="n"/>
+      <c r="AG44" s="19" t="n"/>
+      <c r="AH44" s="19" t="n"/>
+      <c r="AI44" s="19" t="n"/>
+    </row>
+    <row r="45" ht="14.5" customHeight="1">
       <c r="A45" s="11" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="B45" s="11" t="n"/>
       <c r="C45" s="12" t="n"/>
@@ -2805,47 +3006,87 @@
       <c r="AH45" s="13" t="n"/>
       <c r="AI45" s="13" t="n"/>
     </row>
-    <row r="47" ht="16" customHeight="1">
-      <c r="A47" s="18" t="inlineStr">
-        <is>
-          <t>SPECIAL SHIFTING</t>
-        </is>
-      </c>
-      <c r="E47" s="19" t="n"/>
-      <c r="F47" s="19" t="n"/>
-      <c r="G47" s="19" t="n"/>
-      <c r="H47" s="19" t="n"/>
-      <c r="I47" s="19" t="n"/>
-      <c r="J47" s="19" t="n"/>
-      <c r="K47" s="19" t="n"/>
-      <c r="L47" s="19" t="n"/>
-      <c r="M47" s="19" t="n"/>
-      <c r="N47" s="19" t="n"/>
-      <c r="O47" s="19" t="n"/>
-      <c r="P47" s="19" t="n"/>
-      <c r="Q47" s="19" t="n"/>
-      <c r="R47" s="19" t="n"/>
-      <c r="S47" s="19" t="n"/>
-      <c r="T47" s="19" t="n"/>
-      <c r="U47" s="19" t="n"/>
-      <c r="V47" s="19" t="n"/>
-      <c r="W47" s="19" t="n"/>
-      <c r="X47" s="19" t="n"/>
-      <c r="Y47" s="19" t="n"/>
-      <c r="Z47" s="19" t="n"/>
-      <c r="AA47" s="19" t="n"/>
-      <c r="AB47" s="19" t="n"/>
-      <c r="AC47" s="19" t="n"/>
-      <c r="AD47" s="19" t="n"/>
-      <c r="AE47" s="19" t="n"/>
-      <c r="AF47" s="19" t="n"/>
-      <c r="AG47" s="19" t="n"/>
-      <c r="AH47" s="19" t="n"/>
-      <c r="AI47" s="19" t="n"/>
-    </row>
-    <row r="48">
+    <row r="46" ht="14.5" customHeight="1">
+      <c r="A46" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="B46" s="11" t="n"/>
+      <c r="C46" s="12" t="n"/>
+      <c r="D46" s="11" t="n"/>
+      <c r="E46" s="13" t="n"/>
+      <c r="F46" s="13" t="n"/>
+      <c r="G46" s="13" t="n"/>
+      <c r="H46" s="13" t="n"/>
+      <c r="I46" s="13" t="n"/>
+      <c r="J46" s="13" t="n"/>
+      <c r="K46" s="13" t="n"/>
+      <c r="L46" s="13" t="n"/>
+      <c r="M46" s="13" t="n"/>
+      <c r="N46" s="13" t="n"/>
+      <c r="O46" s="13" t="n"/>
+      <c r="P46" s="13" t="n"/>
+      <c r="Q46" s="13" t="n"/>
+      <c r="R46" s="13" t="n"/>
+      <c r="S46" s="13" t="n"/>
+      <c r="T46" s="13" t="n"/>
+      <c r="U46" s="13" t="n"/>
+      <c r="V46" s="13" t="n"/>
+      <c r="W46" s="13" t="n"/>
+      <c r="X46" s="13" t="n"/>
+      <c r="Y46" s="13" t="n"/>
+      <c r="Z46" s="13" t="n"/>
+      <c r="AA46" s="13" t="n"/>
+      <c r="AB46" s="13" t="n"/>
+      <c r="AC46" s="13" t="n"/>
+      <c r="AD46" s="13" t="n"/>
+      <c r="AE46" s="13" t="n"/>
+      <c r="AF46" s="13" t="n"/>
+      <c r="AG46" s="13" t="n"/>
+      <c r="AH46" s="13" t="n"/>
+      <c r="AI46" s="13" t="n"/>
+    </row>
+    <row r="47" ht="14.5" customHeight="1">
+      <c r="A47" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="B47" s="11" t="n"/>
+      <c r="C47" s="12" t="n"/>
+      <c r="D47" s="11" t="n"/>
+      <c r="E47" s="13" t="n"/>
+      <c r="F47" s="13" t="n"/>
+      <c r="G47" s="13" t="n"/>
+      <c r="H47" s="13" t="n"/>
+      <c r="I47" s="13" t="n"/>
+      <c r="J47" s="13" t="n"/>
+      <c r="K47" s="13" t="n"/>
+      <c r="L47" s="13" t="n"/>
+      <c r="M47" s="13" t="n"/>
+      <c r="N47" s="13" t="n"/>
+      <c r="O47" s="13" t="n"/>
+      <c r="P47" s="13" t="n"/>
+      <c r="Q47" s="13" t="n"/>
+      <c r="R47" s="13" t="n"/>
+      <c r="S47" s="13" t="n"/>
+      <c r="T47" s="13" t="n"/>
+      <c r="U47" s="13" t="n"/>
+      <c r="V47" s="13" t="n"/>
+      <c r="W47" s="13" t="n"/>
+      <c r="X47" s="13" t="n"/>
+      <c r="Y47" s="13" t="n"/>
+      <c r="Z47" s="13" t="n"/>
+      <c r="AA47" s="13" t="n"/>
+      <c r="AB47" s="13" t="n"/>
+      <c r="AC47" s="13" t="n"/>
+      <c r="AD47" s="13" t="n"/>
+      <c r="AE47" s="13" t="n"/>
+      <c r="AF47" s="13" t="n"/>
+      <c r="AG47" s="13" t="n"/>
+      <c r="AH47" s="13" t="n"/>
+      <c r="AI47" s="13" t="n"/>
+    </row>
+    <row r="48" ht="14.5" customHeight="1">
       <c r="A48" s="11" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B48" s="11" t="n"/>
       <c r="C48" s="12" t="n"/>
@@ -2882,9 +3123,9 @@
       <c r="AH48" s="13" t="n"/>
       <c r="AI48" s="13" t="n"/>
     </row>
-    <row r="49">
+    <row r="49" ht="14.5" customHeight="1">
       <c r="A49" s="11" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B49" s="11" t="n"/>
       <c r="C49" s="12" t="n"/>
@@ -2921,308 +3162,923 @@
       <c r="AH49" s="13" t="n"/>
       <c r="AI49" s="13" t="n"/>
     </row>
-    <row r="50">
-      <c r="A50" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="B50" s="11" t="n"/>
-      <c r="C50" s="12" t="n"/>
-      <c r="D50" s="11" t="n"/>
-      <c r="E50" s="13" t="n"/>
-      <c r="F50" s="13" t="n"/>
-      <c r="G50" s="13" t="n"/>
-      <c r="H50" s="13" t="n"/>
-      <c r="I50" s="13" t="n"/>
-      <c r="J50" s="13" t="n"/>
-      <c r="K50" s="13" t="n"/>
-      <c r="L50" s="13" t="n"/>
-      <c r="M50" s="13" t="n"/>
-      <c r="N50" s="13" t="n"/>
-      <c r="O50" s="13" t="n"/>
-      <c r="P50" s="13" t="n"/>
-      <c r="Q50" s="13" t="n"/>
-      <c r="R50" s="13" t="n"/>
-      <c r="S50" s="13" t="n"/>
-      <c r="T50" s="13" t="n"/>
-      <c r="U50" s="13" t="n"/>
-      <c r="V50" s="13" t="n"/>
-      <c r="W50" s="13" t="n"/>
-      <c r="X50" s="13" t="n"/>
-      <c r="Y50" s="13" t="n"/>
-      <c r="Z50" s="13" t="n"/>
-      <c r="AA50" s="13" t="n"/>
-      <c r="AB50" s="13" t="n"/>
-      <c r="AC50" s="13" t="n"/>
-      <c r="AD50" s="13" t="n"/>
-      <c r="AE50" s="13" t="n"/>
-      <c r="AF50" s="13" t="n"/>
-      <c r="AG50" s="13" t="n"/>
-      <c r="AH50" s="13" t="n"/>
-      <c r="AI50" s="13" t="n"/>
-    </row>
     <row r="51">
-      <c r="A51" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="B51" s="11" t="n"/>
-      <c r="C51" s="12" t="n"/>
-      <c r="D51" s="11" t="n"/>
-      <c r="E51" s="13" t="n"/>
-      <c r="F51" s="13" t="n"/>
-      <c r="G51" s="13" t="n"/>
-      <c r="H51" s="13" t="n"/>
-      <c r="I51" s="13" t="n"/>
-      <c r="J51" s="13" t="n"/>
-      <c r="K51" s="13" t="n"/>
-      <c r="L51" s="13" t="n"/>
-      <c r="M51" s="13" t="n"/>
-      <c r="N51" s="13" t="n"/>
-      <c r="O51" s="13" t="n"/>
-      <c r="P51" s="13" t="n"/>
-      <c r="Q51" s="13" t="n"/>
-      <c r="R51" s="13" t="n"/>
-      <c r="S51" s="13" t="n"/>
-      <c r="T51" s="13" t="n"/>
-      <c r="U51" s="13" t="n"/>
-      <c r="V51" s="13" t="n"/>
-      <c r="W51" s="13" t="n"/>
-      <c r="X51" s="13" t="n"/>
-      <c r="Y51" s="13" t="n"/>
-      <c r="Z51" s="13" t="n"/>
-      <c r="AA51" s="13" t="n"/>
-      <c r="AB51" s="13" t="n"/>
-      <c r="AC51" s="13" t="n"/>
-      <c r="AD51" s="13" t="n"/>
-      <c r="AE51" s="13" t="n"/>
-      <c r="AF51" s="13" t="n"/>
-      <c r="AG51" s="13" t="n"/>
-      <c r="AH51" s="13" t="n"/>
-      <c r="AI51" s="13" t="n"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="B52" s="11" t="n"/>
-      <c r="C52" s="12" t="n"/>
-      <c r="D52" s="11" t="n"/>
-      <c r="E52" s="13" t="n"/>
-      <c r="F52" s="13" t="n"/>
-      <c r="G52" s="13" t="n"/>
-      <c r="H52" s="13" t="n"/>
-      <c r="I52" s="13" t="n"/>
-      <c r="J52" s="13" t="n"/>
-      <c r="K52" s="13" t="n"/>
-      <c r="L52" s="13" t="n"/>
-      <c r="M52" s="13" t="n"/>
-      <c r="N52" s="13" t="n"/>
-      <c r="O52" s="13" t="n"/>
-      <c r="P52" s="13" t="n"/>
-      <c r="Q52" s="13" t="n"/>
-      <c r="R52" s="13" t="n"/>
-      <c r="S52" s="13" t="n"/>
-      <c r="T52" s="13" t="n"/>
-      <c r="U52" s="13" t="n"/>
-      <c r="V52" s="13" t="n"/>
-      <c r="W52" s="13" t="n"/>
-      <c r="X52" s="13" t="n"/>
-      <c r="Y52" s="13" t="n"/>
-      <c r="Z52" s="13" t="n"/>
-      <c r="AA52" s="13" t="n"/>
-      <c r="AB52" s="13" t="n"/>
-      <c r="AC52" s="13" t="n"/>
-      <c r="AD52" s="13" t="n"/>
-      <c r="AE52" s="13" t="n"/>
-      <c r="AF52" s="13" t="n"/>
-      <c r="AG52" s="13" t="n"/>
-      <c r="AH52" s="13" t="n"/>
-      <c r="AI52" s="13" t="n"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="20" t="inlineStr">
+      <c r="A51" s="20" t="inlineStr">
+        <is>
+          <t>TOTAL DAILY
+CREWS MANPOWER</t>
+        </is>
+      </c>
+      <c r="B51" s="43" t="n"/>
+      <c r="C51" s="44" t="n"/>
+      <c r="D51" s="8" t="inlineStr">
+        <is>
+          <t>SHIFT</t>
+        </is>
+      </c>
+      <c r="E51" s="7">
+        <f>E3</f>
+        <v/>
+      </c>
+      <c r="F51" s="7">
+        <f>F3</f>
+        <v/>
+      </c>
+      <c r="G51" s="7">
+        <f>G3</f>
+        <v/>
+      </c>
+      <c r="H51" s="7">
+        <f>H3</f>
+        <v/>
+      </c>
+      <c r="I51" s="7">
+        <f>I3</f>
+        <v/>
+      </c>
+      <c r="J51" s="7">
+        <f>J3</f>
+        <v/>
+      </c>
+      <c r="K51" s="7">
+        <f>K3</f>
+        <v/>
+      </c>
+      <c r="L51" s="7">
+        <f>L3</f>
+        <v/>
+      </c>
+      <c r="M51" s="7">
+        <f>M3</f>
+        <v/>
+      </c>
+      <c r="N51" s="7">
+        <f>N3</f>
+        <v/>
+      </c>
+      <c r="O51" s="7">
+        <f>O3</f>
+        <v/>
+      </c>
+      <c r="P51" s="7">
+        <f>P3</f>
+        <v/>
+      </c>
+      <c r="Q51" s="7">
+        <f>Q3</f>
+        <v/>
+      </c>
+      <c r="R51" s="7">
+        <f>R3</f>
+        <v/>
+      </c>
+      <c r="S51" s="7">
+        <f>S3</f>
+        <v/>
+      </c>
+      <c r="T51" s="7">
+        <f>T3</f>
+        <v/>
+      </c>
+      <c r="U51" s="7">
+        <f>U3</f>
+        <v/>
+      </c>
+      <c r="V51" s="7">
+        <f>V3</f>
+        <v/>
+      </c>
+      <c r="W51" s="7">
+        <f>W3</f>
+        <v/>
+      </c>
+      <c r="X51" s="7">
+        <f>X3</f>
+        <v/>
+      </c>
+      <c r="Y51" s="7">
+        <f>Y3</f>
+        <v/>
+      </c>
+      <c r="Z51" s="7">
+        <f>Z3</f>
+        <v/>
+      </c>
+      <c r="AA51" s="7">
+        <f>AA3</f>
+        <v/>
+      </c>
+      <c r="AB51" s="7">
+        <f>AB3</f>
+        <v/>
+      </c>
+      <c r="AC51" s="7">
+        <f>AC3</f>
+        <v/>
+      </c>
+      <c r="AD51" s="7">
+        <f>AD3</f>
+        <v/>
+      </c>
+      <c r="AE51" s="7">
+        <f>AE3</f>
+        <v/>
+      </c>
+      <c r="AF51" s="7">
+        <f>AF3</f>
+        <v/>
+      </c>
+      <c r="AG51" s="7">
+        <f>AG3</f>
+        <v/>
+      </c>
+      <c r="AH51" s="7">
+        <f>AH3</f>
+        <v/>
+      </c>
+      <c r="AI51" s="7">
+        <f>AI3</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52" ht="13.5" customHeight="1">
+      <c r="A52" s="45" t="n"/>
+      <c r="C52" s="46" t="n"/>
+      <c r="D52" s="22" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E52" s="11">
+        <f>IF(E$4="","",COUNTIF(E6:E49,"D"))</f>
+        <v/>
+      </c>
+      <c r="F52" s="11">
+        <f>IF(F$4="","",COUNTIF(F6:F49,"D"))</f>
+        <v/>
+      </c>
+      <c r="G52" s="11">
+        <f>IF(G$4="","",COUNTIF(G6:G49,"D"))</f>
+        <v/>
+      </c>
+      <c r="H52" s="11">
+        <f>IF(H$4="","",COUNTIF(H6:H49,"D"))</f>
+        <v/>
+      </c>
+      <c r="I52" s="11">
+        <f>IF(I$4="","",COUNTIF(I6:I49,"D"))</f>
+        <v/>
+      </c>
+      <c r="J52" s="11">
+        <f>IF(J$4="","",COUNTIF(J6:J49,"D"))</f>
+        <v/>
+      </c>
+      <c r="K52" s="11">
+        <f>IF(K$4="","",COUNTIF(K6:K49,"D"))</f>
+        <v/>
+      </c>
+      <c r="L52" s="11">
+        <f>IF(L$4="","",COUNTIF(L6:L49,"D"))</f>
+        <v/>
+      </c>
+      <c r="M52" s="11">
+        <f>IF(M$4="","",COUNTIF(M6:M49,"D"))</f>
+        <v/>
+      </c>
+      <c r="N52" s="11">
+        <f>IF(N$4="","",COUNTIF(N6:N49,"D"))</f>
+        <v/>
+      </c>
+      <c r="O52" s="11">
+        <f>IF(O$4="","",COUNTIF(O6:O49,"D"))</f>
+        <v/>
+      </c>
+      <c r="P52" s="11">
+        <f>IF(P$4="","",COUNTIF(P6:P49,"D"))</f>
+        <v/>
+      </c>
+      <c r="Q52" s="11">
+        <f>IF(Q$4="","",COUNTIF(Q6:Q49,"D"))</f>
+        <v/>
+      </c>
+      <c r="R52" s="11">
+        <f>IF(R$4="","",COUNTIF(R6:R49,"D"))</f>
+        <v/>
+      </c>
+      <c r="S52" s="11">
+        <f>IF(S$4="","",COUNTIF(S6:S49,"D"))</f>
+        <v/>
+      </c>
+      <c r="T52" s="11">
+        <f>IF(T$4="","",COUNTIF(T6:T49,"D"))</f>
+        <v/>
+      </c>
+      <c r="U52" s="11">
+        <f>IF(U$4="","",COUNTIF(U6:U49,"D"))</f>
+        <v/>
+      </c>
+      <c r="V52" s="11">
+        <f>IF(V$4="","",COUNTIF(V6:V49,"D"))</f>
+        <v/>
+      </c>
+      <c r="W52" s="11">
+        <f>IF(W$4="","",COUNTIF(W6:W49,"D"))</f>
+        <v/>
+      </c>
+      <c r="X52" s="11">
+        <f>IF(X$4="","",COUNTIF(X6:X49,"D"))</f>
+        <v/>
+      </c>
+      <c r="Y52" s="11">
+        <f>IF(Y$4="","",COUNTIF(Y6:Y49,"D"))</f>
+        <v/>
+      </c>
+      <c r="Z52" s="11">
+        <f>IF(Z$4="","",COUNTIF(Z6:Z49,"D"))</f>
+        <v/>
+      </c>
+      <c r="AA52" s="11">
+        <f>IF(AA$4="","",COUNTIF(AA6:AA49,"D"))</f>
+        <v/>
+      </c>
+      <c r="AB52" s="11">
+        <f>IF(AB$4="","",COUNTIF(AB6:AB49,"D"))</f>
+        <v/>
+      </c>
+      <c r="AC52" s="11">
+        <f>IF(AC$4="","",COUNTIF(AC6:AC49,"D"))</f>
+        <v/>
+      </c>
+      <c r="AD52" s="11">
+        <f>IF(AD$4="","",COUNTIF(AD6:AD49,"D"))</f>
+        <v/>
+      </c>
+      <c r="AE52" s="11">
+        <f>IF(AE$4="","",COUNTIF(AE6:AE49,"D"))</f>
+        <v/>
+      </c>
+      <c r="AF52" s="11">
+        <f>IF(AF$4="","",COUNTIF(AF6:AF49,"D"))</f>
+        <v/>
+      </c>
+      <c r="AG52" s="11">
+        <f>IF(AG$4="","",COUNTIF(AG6:AG49,"D"))</f>
+        <v/>
+      </c>
+      <c r="AH52" s="11">
+        <f>IF(AH$4="","",COUNTIF(AH6:AH49,"D"))</f>
+        <v/>
+      </c>
+      <c r="AI52" s="11">
+        <f>IF(AI$4="","",COUNTIF(AI6:AI49,"D"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53" ht="13.5" customHeight="1">
+      <c r="A53" s="45" t="n"/>
+      <c r="C53" s="46" t="n"/>
+      <c r="D53" s="23" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="E53" s="11">
+        <f>IF(E$4="","",COUNTIF(E6:E49,"T"))</f>
+        <v/>
+      </c>
+      <c r="F53" s="11">
+        <f>IF(F$4="","",COUNTIF(F6:F49,"T"))</f>
+        <v/>
+      </c>
+      <c r="G53" s="11">
+        <f>IF(G$4="","",COUNTIF(G6:G49,"T"))</f>
+        <v/>
+      </c>
+      <c r="H53" s="11">
+        <f>IF(H$4="","",COUNTIF(H6:H49,"T"))</f>
+        <v/>
+      </c>
+      <c r="I53" s="11">
+        <f>IF(I$4="","",COUNTIF(I6:I49,"T"))</f>
+        <v/>
+      </c>
+      <c r="J53" s="11">
+        <f>IF(J$4="","",COUNTIF(J6:J49,"T"))</f>
+        <v/>
+      </c>
+      <c r="K53" s="11">
+        <f>IF(K$4="","",COUNTIF(K6:K49,"T"))</f>
+        <v/>
+      </c>
+      <c r="L53" s="11">
+        <f>IF(L$4="","",COUNTIF(L6:L49,"T"))</f>
+        <v/>
+      </c>
+      <c r="M53" s="11">
+        <f>IF(M$4="","",COUNTIF(M6:M49,"T"))</f>
+        <v/>
+      </c>
+      <c r="N53" s="11">
+        <f>IF(N$4="","",COUNTIF(N6:N49,"T"))</f>
+        <v/>
+      </c>
+      <c r="O53" s="11">
+        <f>IF(O$4="","",COUNTIF(O6:O49,"T"))</f>
+        <v/>
+      </c>
+      <c r="P53" s="11">
+        <f>IF(P$4="","",COUNTIF(P6:P49,"T"))</f>
+        <v/>
+      </c>
+      <c r="Q53" s="11">
+        <f>IF(Q$4="","",COUNTIF(Q6:Q49,"T"))</f>
+        <v/>
+      </c>
+      <c r="R53" s="11">
+        <f>IF(R$4="","",COUNTIF(R6:R49,"T"))</f>
+        <v/>
+      </c>
+      <c r="S53" s="11">
+        <f>IF(S$4="","",COUNTIF(S6:S49,"T"))</f>
+        <v/>
+      </c>
+      <c r="T53" s="11">
+        <f>IF(T$4="","",COUNTIF(T6:T49,"T"))</f>
+        <v/>
+      </c>
+      <c r="U53" s="11">
+        <f>IF(U$4="","",COUNTIF(U6:U49,"T"))</f>
+        <v/>
+      </c>
+      <c r="V53" s="11">
+        <f>IF(V$4="","",COUNTIF(V6:V49,"T"))</f>
+        <v/>
+      </c>
+      <c r="W53" s="11">
+        <f>IF(W$4="","",COUNTIF(W6:W49,"T"))</f>
+        <v/>
+      </c>
+      <c r="X53" s="11">
+        <f>IF(X$4="","",COUNTIF(X6:X49,"T"))</f>
+        <v/>
+      </c>
+      <c r="Y53" s="11">
+        <f>IF(Y$4="","",COUNTIF(Y6:Y49,"T"))</f>
+        <v/>
+      </c>
+      <c r="Z53" s="11">
+        <f>IF(Z$4="","",COUNTIF(Z6:Z49,"T"))</f>
+        <v/>
+      </c>
+      <c r="AA53" s="11">
+        <f>IF(AA$4="","",COUNTIF(AA6:AA49,"T"))</f>
+        <v/>
+      </c>
+      <c r="AB53" s="11">
+        <f>IF(AB$4="","",COUNTIF(AB6:AB49,"T"))</f>
+        <v/>
+      </c>
+      <c r="AC53" s="11">
+        <f>IF(AC$4="","",COUNTIF(AC6:AC49,"T"))</f>
+        <v/>
+      </c>
+      <c r="AD53" s="11">
+        <f>IF(AD$4="","",COUNTIF(AD6:AD49,"T"))</f>
+        <v/>
+      </c>
+      <c r="AE53" s="11">
+        <f>IF(AE$4="","",COUNTIF(AE6:AE49,"T"))</f>
+        <v/>
+      </c>
+      <c r="AF53" s="11">
+        <f>IF(AF$4="","",COUNTIF(AF6:AF49,"T"))</f>
+        <v/>
+      </c>
+      <c r="AG53" s="11">
+        <f>IF(AG$4="","",COUNTIF(AG6:AG49,"T"))</f>
+        <v/>
+      </c>
+      <c r="AH53" s="11">
+        <f>IF(AH$4="","",COUNTIF(AH6:AH49,"T"))</f>
+        <v/>
+      </c>
+      <c r="AI53" s="11">
+        <f>IF(AI$4="","",COUNTIF(AI6:AI49,"T"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54" ht="13.5" customHeight="1">
+      <c r="A54" s="47" t="n"/>
+      <c r="B54" s="48" t="n"/>
+      <c r="C54" s="49" t="n"/>
+      <c r="D54" s="24" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="E54" s="11">
+        <f>IF(E$4="","",COUNTIF(E6:E49,"G"))</f>
+        <v/>
+      </c>
+      <c r="F54" s="11">
+        <f>IF(F$4="","",COUNTIF(F6:F49,"G"))</f>
+        <v/>
+      </c>
+      <c r="G54" s="11">
+        <f>IF(G$4="","",COUNTIF(G6:G49,"G"))</f>
+        <v/>
+      </c>
+      <c r="H54" s="11">
+        <f>IF(H$4="","",COUNTIF(H6:H49,"G"))</f>
+        <v/>
+      </c>
+      <c r="I54" s="11">
+        <f>IF(I$4="","",COUNTIF(I6:I49,"G"))</f>
+        <v/>
+      </c>
+      <c r="J54" s="11">
+        <f>IF(J$4="","",COUNTIF(J6:J49,"G"))</f>
+        <v/>
+      </c>
+      <c r="K54" s="11">
+        <f>IF(K$4="","",COUNTIF(K6:K49,"G"))</f>
+        <v/>
+      </c>
+      <c r="L54" s="11">
+        <f>IF(L$4="","",COUNTIF(L6:L49,"G"))</f>
+        <v/>
+      </c>
+      <c r="M54" s="11">
+        <f>IF(M$4="","",COUNTIF(M6:M49,"G"))</f>
+        <v/>
+      </c>
+      <c r="N54" s="11">
+        <f>IF(N$4="","",COUNTIF(N6:N49,"G"))</f>
+        <v/>
+      </c>
+      <c r="O54" s="11">
+        <f>IF(O$4="","",COUNTIF(O6:O49,"G"))</f>
+        <v/>
+      </c>
+      <c r="P54" s="11">
+        <f>IF(P$4="","",COUNTIF(P6:P49,"G"))</f>
+        <v/>
+      </c>
+      <c r="Q54" s="11">
+        <f>IF(Q$4="","",COUNTIF(Q6:Q49,"G"))</f>
+        <v/>
+      </c>
+      <c r="R54" s="11">
+        <f>IF(R$4="","",COUNTIF(R6:R49,"G"))</f>
+        <v/>
+      </c>
+      <c r="S54" s="11">
+        <f>IF(S$4="","",COUNTIF(S6:S49,"G"))</f>
+        <v/>
+      </c>
+      <c r="T54" s="11">
+        <f>IF(T$4="","",COUNTIF(T6:T49,"G"))</f>
+        <v/>
+      </c>
+      <c r="U54" s="11">
+        <f>IF(U$4="","",COUNTIF(U6:U49,"G"))</f>
+        <v/>
+      </c>
+      <c r="V54" s="11">
+        <f>IF(V$4="","",COUNTIF(V6:V49,"G"))</f>
+        <v/>
+      </c>
+      <c r="W54" s="11">
+        <f>IF(W$4="","",COUNTIF(W6:W49,"G"))</f>
+        <v/>
+      </c>
+      <c r="X54" s="11">
+        <f>IF(X$4="","",COUNTIF(X6:X49,"G"))</f>
+        <v/>
+      </c>
+      <c r="Y54" s="11">
+        <f>IF(Y$4="","",COUNTIF(Y6:Y49,"G"))</f>
+        <v/>
+      </c>
+      <c r="Z54" s="11">
+        <f>IF(Z$4="","",COUNTIF(Z6:Z49,"G"))</f>
+        <v/>
+      </c>
+      <c r="AA54" s="11">
+        <f>IF(AA$4="","",COUNTIF(AA6:AA49,"G"))</f>
+        <v/>
+      </c>
+      <c r="AB54" s="11">
+        <f>IF(AB$4="","",COUNTIF(AB6:AB49,"G"))</f>
+        <v/>
+      </c>
+      <c r="AC54" s="11">
+        <f>IF(AC$4="","",COUNTIF(AC6:AC49,"G"))</f>
+        <v/>
+      </c>
+      <c r="AD54" s="11">
+        <f>IF(AD$4="","",COUNTIF(AD6:AD49,"G"))</f>
+        <v/>
+      </c>
+      <c r="AE54" s="11">
+        <f>IF(AE$4="","",COUNTIF(AE6:AE49,"G"))</f>
+        <v/>
+      </c>
+      <c r="AF54" s="11">
+        <f>IF(AF$4="","",COUNTIF(AF6:AF49,"G"))</f>
+        <v/>
+      </c>
+      <c r="AG54" s="11">
+        <f>IF(AG$4="","",COUNTIF(AG6:AG49,"G"))</f>
+        <v/>
+      </c>
+      <c r="AH54" s="11">
+        <f>IF(AH$4="","",COUNTIF(AH6:AH49,"G"))</f>
+        <v/>
+      </c>
+      <c r="AI54" s="11">
+        <f>IF(AI$4="","",COUNTIF(AI6:AI49,"G"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55" ht="13.5" customHeight="1">
+      <c r="A55" s="21" t="n"/>
+      <c r="B55" s="21" t="n"/>
+      <c r="C55" s="21" t="n"/>
+      <c r="D55" s="13" t="inlineStr">
+        <is>
+          <t>TOT</t>
+        </is>
+      </c>
+      <c r="E55" s="13">
+        <f>IF(E$4="","",SUM(E52:E54))</f>
+        <v/>
+      </c>
+      <c r="F55" s="13">
+        <f>IF(F$4="","",SUM(F52:F54))</f>
+        <v/>
+      </c>
+      <c r="G55" s="13">
+        <f>IF(G$4="","",SUM(G52:G54))</f>
+        <v/>
+      </c>
+      <c r="H55" s="13">
+        <f>IF(H$4="","",SUM(H52:H54))</f>
+        <v/>
+      </c>
+      <c r="I55" s="13">
+        <f>IF(I$4="","",SUM(I52:I54))</f>
+        <v/>
+      </c>
+      <c r="J55" s="13">
+        <f>IF(J$4="","",SUM(J52:J54))</f>
+        <v/>
+      </c>
+      <c r="K55" s="13">
+        <f>IF(K$4="","",SUM(K52:K54))</f>
+        <v/>
+      </c>
+      <c r="L55" s="13">
+        <f>IF(L$4="","",SUM(L52:L54))</f>
+        <v/>
+      </c>
+      <c r="M55" s="13">
+        <f>IF(M$4="","",SUM(M52:M54))</f>
+        <v/>
+      </c>
+      <c r="N55" s="13">
+        <f>IF(N$4="","",SUM(N52:N54))</f>
+        <v/>
+      </c>
+      <c r="O55" s="13">
+        <f>IF(O$4="","",SUM(O52:O54))</f>
+        <v/>
+      </c>
+      <c r="P55" s="13">
+        <f>IF(P$4="","",SUM(P52:P54))</f>
+        <v/>
+      </c>
+      <c r="Q55" s="13">
+        <f>IF(Q$4="","",SUM(Q52:Q54))</f>
+        <v/>
+      </c>
+      <c r="R55" s="13">
+        <f>IF(R$4="","",SUM(R52:R54))</f>
+        <v/>
+      </c>
+      <c r="S55" s="13">
+        <f>IF(S$4="","",SUM(S52:S54))</f>
+        <v/>
+      </c>
+      <c r="T55" s="13">
+        <f>IF(T$4="","",SUM(T52:T54))</f>
+        <v/>
+      </c>
+      <c r="U55" s="13">
+        <f>IF(U$4="","",SUM(U52:U54))</f>
+        <v/>
+      </c>
+      <c r="V55" s="13">
+        <f>IF(V$4="","",SUM(V52:V54))</f>
+        <v/>
+      </c>
+      <c r="W55" s="13">
+        <f>IF(W$4="","",SUM(W52:W54))</f>
+        <v/>
+      </c>
+      <c r="X55" s="13">
+        <f>IF(X$4="","",SUM(X52:X54))</f>
+        <v/>
+      </c>
+      <c r="Y55" s="13">
+        <f>IF(Y$4="","",SUM(Y52:Y54))</f>
+        <v/>
+      </c>
+      <c r="Z55" s="13">
+        <f>IF(Z$4="","",SUM(Z52:Z54))</f>
+        <v/>
+      </c>
+      <c r="AA55" s="13">
+        <f>IF(AA$4="","",SUM(AA52:AA54))</f>
+        <v/>
+      </c>
+      <c r="AB55" s="13">
+        <f>IF(AB$4="","",SUM(AB52:AB54))</f>
+        <v/>
+      </c>
+      <c r="AC55" s="13">
+        <f>IF(AC$4="","",SUM(AC52:AC54))</f>
+        <v/>
+      </c>
+      <c r="AD55" s="13">
+        <f>IF(AD$4="","",SUM(AD52:AD54))</f>
+        <v/>
+      </c>
+      <c r="AE55" s="13">
+        <f>IF(AE$4="","",SUM(AE52:AE54))</f>
+        <v/>
+      </c>
+      <c r="AF55" s="13">
+        <f>IF(AF$4="","",SUM(AF52:AF54))</f>
+        <v/>
+      </c>
+      <c r="AG55" s="13">
+        <f>IF(AG$4="","",SUM(AG52:AG54))</f>
+        <v/>
+      </c>
+      <c r="AH55" s="13">
+        <f>IF(AH$4="","",SUM(AH52:AH54))</f>
+        <v/>
+      </c>
+      <c r="AI55" s="13">
+        <f>IF(AI$4="","",SUM(AI52:AI54))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="25" t="inlineStr">
+        <is>
+          <t>SHIFT TIMES</t>
+        </is>
+      </c>
+      <c r="F57" s="25" t="inlineStr">
         <is>
           <t>CODE LEGEND</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="21" t="inlineStr">
+    <row r="58" ht="14" customHeight="1">
+      <c r="B58" s="26" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="B56" s="22" t="inlineStr">
+      <c r="C58" s="27" t="inlineStr">
+        <is>
+          <t>DAY (07:00 - 15:00)</t>
+        </is>
+      </c>
+      <c r="F58" s="22" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G58" s="50" t="n"/>
+      <c r="H58" s="28" t="inlineStr">
         <is>
           <t>DAY</t>
         </is>
       </c>
-      <c r="C56" s="23" t="inlineStr">
+      <c r="J58" s="23" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="D56" s="22" t="inlineStr">
+      <c r="K58" s="50" t="n"/>
+      <c r="L58" s="28" t="inlineStr">
         <is>
           <t>TWILIGHT</t>
         </is>
       </c>
-      <c r="E56" s="24" t="inlineStr">
+      <c r="N58" s="24" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
-      <c r="F56" s="22" t="inlineStr">
+      <c r="O58" s="50" t="n"/>
+      <c r="P58" s="28" t="inlineStr">
         <is>
           <t>GRAVEYARD</t>
         </is>
       </c>
-      <c r="G56" s="25" t="inlineStr">
+      <c r="R58" s="29" t="inlineStr">
         <is>
           <t>TR</t>
         </is>
       </c>
-      <c r="H56" s="22" t="inlineStr">
+      <c r="S58" s="50" t="n"/>
+      <c r="T58" s="28" t="inlineStr">
         <is>
           <t>TRAINING</t>
         </is>
       </c>
-      <c r="I56" s="26" t="inlineStr">
+      <c r="V58" s="30" t="inlineStr">
         <is>
           <t>V</t>
         </is>
       </c>
-      <c r="J56" s="22" t="inlineStr">
+      <c r="W58" s="50" t="n"/>
+      <c r="X58" s="28" t="inlineStr">
         <is>
           <t>VACATION</t>
         </is>
       </c>
-      <c r="K56" s="27" t="inlineStr">
+      <c r="Z58" s="31" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="L56" s="22" t="inlineStr">
+      <c r="AA58" s="50" t="n"/>
+      <c r="AB58" s="28" t="inlineStr">
         <is>
           <t>REST/RDO</t>
         </is>
       </c>
-      <c r="M56" s="28" t="inlineStr">
+      <c r="AD58" s="32" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="N56" s="22" t="inlineStr">
+      <c r="AE58" s="50" t="n"/>
+      <c r="AF58" s="28" t="inlineStr">
         <is>
           <t>ABSENT</t>
         </is>
       </c>
-      <c r="O56" s="29" t="inlineStr">
+    </row>
+    <row r="59" ht="14" customHeight="1">
+      <c r="B59" s="33" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C59" s="27" t="inlineStr">
+        <is>
+          <t>TWI (15:00 - 23:00)</t>
+        </is>
+      </c>
+      <c r="F59" s="34" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="P56" s="22" t="inlineStr">
+      <c r="G59" s="50" t="n"/>
+      <c r="H59" s="28" t="inlineStr">
         <is>
           <t>HOLIDAY</t>
         </is>
       </c>
-      <c r="Q56" s="30" t="inlineStr">
+      <c r="J59" s="35" t="inlineStr">
         <is>
           <t>OT</t>
         </is>
       </c>
-      <c r="R56" s="22" t="inlineStr">
+      <c r="K59" s="50" t="n"/>
+      <c r="L59" s="28" t="inlineStr">
         <is>
           <t>OVERTIME</t>
         </is>
       </c>
-      <c r="S56" s="31" t="inlineStr">
+      <c r="N59" s="36" t="inlineStr">
         <is>
           <t>OS</t>
         </is>
       </c>
-      <c r="T56" s="22" t="inlineStr">
+      <c r="O59" s="50" t="n"/>
+      <c r="P59" s="28" t="inlineStr">
         <is>
           <t>OUTSTATION</t>
         </is>
       </c>
-      <c r="U56" s="32" t="inlineStr">
+      <c r="R59" s="37" t="inlineStr">
         <is>
           <t>S/L</t>
         </is>
       </c>
-      <c r="V56" s="22" t="inlineStr">
+      <c r="S59" s="50" t="n"/>
+      <c r="T59" s="28" t="inlineStr">
         <is>
           <t>SICK LEAVE</t>
         </is>
       </c>
-      <c r="W56" s="33" t="inlineStr">
+      <c r="V59" s="38" t="inlineStr">
         <is>
           <t>C/T</t>
         </is>
       </c>
-      <c r="X56" s="22" t="inlineStr">
+      <c r="W59" s="50" t="n"/>
+      <c r="X59" s="28" t="inlineStr">
         <is>
           <t>COMP TIME</t>
         </is>
       </c>
-      <c r="Y56" s="34" t="inlineStr">
+      <c r="Z59" s="39" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="Z56" s="22" t="inlineStr">
+      <c r="AA59" s="50" t="n"/>
+      <c r="AB59" s="28" t="inlineStr">
         <is>
           <t>LATE/LEAVE</t>
         </is>
       </c>
-      <c r="AA56" s="35" t="inlineStr">
+      <c r="AD59" s="40" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="AB56" s="22" t="inlineStr">
+      <c r="AE59" s="50" t="n"/>
+      <c r="AF59" s="28" t="inlineStr">
         <is>
           <t>NOTE</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="B59" s="4" t="inlineStr">
-        <is>
-          <t>PREPARED BY:</t>
-        </is>
-      </c>
-      <c r="C59" s="36" t="n"/>
-      <c r="D59" s="37" t="n"/>
-      <c r="E59" s="37" t="n"/>
-      <c r="F59" s="37" t="n"/>
-      <c r="G59" s="37" t="n"/>
-      <c r="H59" s="37" t="n"/>
-      <c r="T59" s="4" t="inlineStr">
-        <is>
-          <t>APPROVED BY:</t>
-        </is>
-      </c>
-      <c r="V59" s="36" t="n"/>
-      <c r="W59" s="37" t="n"/>
-      <c r="X59" s="37" t="n"/>
-      <c r="Y59" s="37" t="n"/>
-      <c r="Z59" s="37" t="n"/>
-      <c r="AA59" s="37" t="n"/>
+    <row r="60" ht="14" customHeight="1">
+      <c r="B60" s="41" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="C60" s="27" t="inlineStr">
+        <is>
+          <t>GRV (23:00 - 07:00)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="40">
+    <mergeCell ref="A5:D5"/>
+    <mergeCell ref="E2:AI2"/>
+    <mergeCell ref="AB58:AC58"/>
+    <mergeCell ref="C58:D58"/>
+    <mergeCell ref="E1:AE1"/>
+    <mergeCell ref="V58:W58"/>
+    <mergeCell ref="J59:K59"/>
+    <mergeCell ref="H58:I58"/>
+    <mergeCell ref="R59:S59"/>
+    <mergeCell ref="AF1:AI1"/>
+    <mergeCell ref="A44:D44"/>
+    <mergeCell ref="F59:G59"/>
+    <mergeCell ref="T58:U58"/>
+    <mergeCell ref="AD59:AE59"/>
+    <mergeCell ref="H59:I59"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="A51:C54"/>
+    <mergeCell ref="P59:Q59"/>
+    <mergeCell ref="T59:U59"/>
+    <mergeCell ref="V59:W59"/>
+    <mergeCell ref="AB59:AC59"/>
+    <mergeCell ref="N58:O58"/>
+    <mergeCell ref="Z58:AA58"/>
+    <mergeCell ref="C59:D59"/>
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A5:D5"/>
-    <mergeCell ref="V59:AA59"/>
-    <mergeCell ref="E2:AC2"/>
-    <mergeCell ref="E1:Y1"/>
-    <mergeCell ref="A19:D19"/>
-    <mergeCell ref="A33:D33"/>
-    <mergeCell ref="Z1:AC1"/>
-    <mergeCell ref="C59:H59"/>
-    <mergeCell ref="A47:D47"/>
+    <mergeCell ref="C60:D60"/>
+    <mergeCell ref="L58:M58"/>
+    <mergeCell ref="X58:Y58"/>
+    <mergeCell ref="AF59:AG59"/>
+    <mergeCell ref="AF58:AG58"/>
+    <mergeCell ref="N59:O59"/>
+    <mergeCell ref="F58:G58"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="L59:M59"/>
+    <mergeCell ref="X59:Y59"/>
+    <mergeCell ref="P58:Q58"/>
+    <mergeCell ref="Z59:AA59"/>
+    <mergeCell ref="R58:S58"/>
+    <mergeCell ref="J58:K58"/>
+    <mergeCell ref="AD58:AE58"/>
   </mergeCells>
   <conditionalFormatting sqref="E6:AI17">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
@@ -3271,7 +4127,7 @@
       <formula>AND(E$4&lt;&gt;"",OR(E$3="Fri",E$3="Sat"))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E20:AI31">
+  <conditionalFormatting sqref="E19:AI30">
     <cfRule type="cellIs" priority="16" operator="equal" dxfId="0">
       <formula>"D"</formula>
     </cfRule>
@@ -3318,7 +4174,7 @@
       <formula>AND(E$4&lt;&gt;"",OR(E$3="Fri",E$3="Sat"))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E34:AI45">
+  <conditionalFormatting sqref="E32:AI43">
     <cfRule type="cellIs" priority="31" operator="equal" dxfId="0">
       <formula>"D"</formula>
     </cfRule>
@@ -3365,7 +4221,7 @@
       <formula>AND(E$4&lt;&gt;"",OR(E$3="Fri",E$3="Sat"))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E48:AI52">
+  <conditionalFormatting sqref="E45:AI49">
     <cfRule type="cellIs" priority="46" operator="equal" dxfId="0">
       <formula>"D"</formula>
     </cfRule>
@@ -3412,7 +4268,8 @@
       <formula>AND(E$4&lt;&gt;"",OR(E$3="Fri",E$3="Sat"))</formula>
     </cfRule>
   </conditionalFormatting>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="1" fitToWidth="1"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.25" right="0.25" top="0.3" bottom="0.3" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
 </file>
--- a/uploads/inbox/SPV_CABIN_ROSTER_TEMPLATE.xlsx
+++ b/uploads/inbox/SPV_CABIN_ROSTER_TEMPLATE.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ROSTER" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'ROSTER'!$A$1:$AI$59</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'ROSTER'!$A$1:$AI$60</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>

--- a/uploads/inbox/SPV_CABIN_ROSTER_TEMPLATE.xlsx
+++ b/uploads/inbox/SPV_CABIN_ROSTER_TEMPLATE.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ROSTER" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'ROSTER'!$A$1:$AI$60</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'ROSTER'!$A$1:$AI$66</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -28,155 +28,194 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Times New Roman"/>
       <b val="1"/>
-      <color rgb="00196B24"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <b val="1"/>
+      <color rgb="00B45309"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <b val="1"/>
+      <color rgb="0015803D"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
     <font>
+      <name val="Times New Roman"/>
       <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <color rgb="009AA2A9"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <color rgb="00000000"/>
       <sz val="11"/>
     </font>
     <font>
+      <name val="Times New Roman"/>
+      <color rgb="00000000"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
       <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <b val="1"/>
+      <color rgb="0092400E"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <b val="1"/>
+      <color rgb="001A56DB"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <b val="1"/>
+      <color rgb="00065F46"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <b val="1"/>
+      <color rgb="0015803D"/>
       <sz val="10"/>
     </font>
     <font>
-      <b val="1"/>
-      <sz val="8"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00B45309"/>
+      <name val="Times New Roman"/>
+      <color rgb="00000000"/>
       <sz val="10"/>
     </font>
     <font>
+      <name val="Times New Roman"/>
       <b val="1"/>
-      <color rgb="001F4E3D"/>
+      <color rgb="0092400E"/>
       <sz val="10"/>
     </font>
     <font>
-      <b val="1"/>
-      <sz val="7.5"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <sz val="8.5"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="9.5"/>
-    </font>
-    <font>
-      <color rgb="009AA2A9"/>
-      <sz val="7.5"/>
-    </font>
-    <font>
-      <sz val="8.5"/>
-    </font>
-    <font>
-      <b val="1"/>
+      <name val="Times New Roman"/>
+      <color rgb="00000000"/>
       <sz val="9"/>
     </font>
     <font>
+      <name val="Times New Roman"/>
       <b val="1"/>
-      <color rgb="0092400E"/>
-      <sz val="8.5"/>
+      <color rgb="001A56DB"/>
+      <sz val="10"/>
     </font>
     <font>
+      <name val="Times New Roman"/>
       <b val="1"/>
-      <color rgb="001A56DB"/>
-      <sz val="8.5"/>
+      <color rgb="00065F46"/>
+      <sz val="10"/>
     </font>
     <font>
+      <name val="Times New Roman"/>
       <b val="1"/>
-      <color rgb="00065F46"/>
-      <sz val="8.5"/>
+      <color rgb="005521B5"/>
+      <sz val="10"/>
     </font>
     <font>
+      <name val="Times New Roman"/>
       <b val="1"/>
-      <color rgb="001F4E3D"/>
-      <sz val="9"/>
+      <color rgb="000E7490"/>
+      <sz val="10"/>
     </font>
     <font>
+      <name val="Times New Roman"/>
       <b val="1"/>
-      <color rgb="0092400E"/>
-      <sz val="9"/>
+      <color rgb="006B7280"/>
+      <sz val="10"/>
     </font>
     <font>
+      <name val="Times New Roman"/>
       <b val="1"/>
-      <color rgb="001A56DB"/>
-      <sz val="9"/>
+      <color rgb="00F9FAFB"/>
+      <sz val="10"/>
     </font>
     <font>
+      <name val="Times New Roman"/>
       <b val="1"/>
-      <color rgb="00065F46"/>
-      <sz val="9"/>
+      <color rgb="007E22CE"/>
+      <sz val="10"/>
     </font>
     <font>
-      <sz val="7"/>
+      <name val="Times New Roman"/>
+      <b val="1"/>
+      <color rgb="00C2410C"/>
+      <sz val="10"/>
     </font>
     <font>
+      <name val="Times New Roman"/>
       <b val="1"/>
-      <color rgb="005521B5"/>
-      <sz val="8.5"/>
+      <color rgb="003730A3"/>
+      <sz val="10"/>
     </font>
     <font>
+      <name val="Times New Roman"/>
       <b val="1"/>
-      <color rgb="000E7490"/>
-      <sz val="8.5"/>
+      <color rgb="00BE123C"/>
+      <sz val="10"/>
     </font>
     <font>
+      <name val="Times New Roman"/>
       <b val="1"/>
-      <color rgb="006B7280"/>
-      <sz val="8.5"/>
+      <color rgb="003F6212"/>
+      <sz val="10"/>
     </font>
     <font>
+      <name val="Times New Roman"/>
       <b val="1"/>
-      <color rgb="00F9FAFB"/>
-      <sz val="8.5"/>
+      <color rgb="00475569"/>
+      <sz val="10"/>
     </font>
     <font>
-      <b val="1"/>
-      <color rgb="007E22CE"/>
-      <sz val="8.5"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00C2410C"/>
-      <sz val="8.5"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="003730A3"/>
-      <sz val="8.5"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00BE123C"/>
-      <sz val="8.5"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="003F6212"/>
-      <sz val="8.5"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00475569"/>
-      <sz val="8.5"/>
-    </font>
-    <font>
+      <name val="Times New Roman"/>
       <b val="1"/>
       <color rgb="00713F12"/>
-      <sz val="8.5"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <sz val="7"/>
+      <sz val="10"/>
     </font>
   </fonts>
-  <fills count="21">
+  <fills count="22">
     <fill>
       <patternFill/>
     </fill>
@@ -185,12 +224,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EEF2F0"/>
+        <fgColor rgb="0015803D"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001A56DB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EEF2F0"/>
       </patternFill>
     </fill>
     <fill>
@@ -279,7 +323,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -301,96 +345,14 @@
         <color rgb="00C9CFD6"/>
       </bottom>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="00C9CFD6"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00C9CFD6"/>
-      </right>
-      <top style="thin">
-        <color rgb="00C9CFD6"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00C9CFD6"/>
-      </right>
-      <top style="thin">
-        <color rgb="00C9CFD6"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00C9CFD6"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="00C9CFD6"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00C9CFD6"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="00C9CFD6"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color rgb="00C9CFD6"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color rgb="00C9CFD6"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00C9CFD6"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="00C9CFD6"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -398,68 +360,76 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -471,9 +441,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -497,197 +464,207 @@
     <xf numFmtId="0" fontId="31" fillId="20" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="32" fillId="21" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="15">
+  <dxfs count="17">
     <dxf>
       <font>
+        <name val="Times New Roman"/>
         <b val="1"/>
         <color rgb="0092400E"/>
-        <sz val="8.5"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="00FEF3C7"/>
+        <patternFill>
+          <bgColor rgb="00FEF3C7"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
+        <name val="Times New Roman"/>
         <b val="1"/>
         <color rgb="001A56DB"/>
-        <sz val="8.5"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="00DBEAFE"/>
+        <patternFill>
+          <bgColor rgb="00DBEAFE"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
+        <name val="Times New Roman"/>
         <b val="1"/>
         <color rgb="00065F46"/>
-        <sz val="8.5"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="00D1FAE5"/>
+        <patternFill>
+          <bgColor rgb="00D1FAE5"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
+        <name val="Times New Roman"/>
         <b val="1"/>
         <color rgb="005521B5"/>
-        <sz val="8.5"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="00EDEBFE"/>
+        <patternFill>
+          <bgColor rgb="00EDEBFE"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
+        <name val="Times New Roman"/>
         <b val="1"/>
         <color rgb="000E7490"/>
-        <sz val="8.5"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="00CFFAFE"/>
+        <patternFill>
+          <bgColor rgb="00CFFAFE"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
+        <name val="Times New Roman"/>
         <b val="1"/>
         <color rgb="006B7280"/>
-        <sz val="8.5"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="00F3F4F6"/>
+        <patternFill>
+          <bgColor rgb="00F3F4F6"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
+        <name val="Times New Roman"/>
         <b val="1"/>
         <color rgb="00F9FAFB"/>
-        <sz val="8.5"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="001F2937"/>
+        <patternFill>
+          <bgColor rgb="001F2937"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
+        <name val="Times New Roman"/>
         <b val="1"/>
         <color rgb="007E22CE"/>
-        <sz val="8.5"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="00FDF4FF"/>
+        <patternFill>
+          <bgColor rgb="00FDF4FF"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
+        <name val="Times New Roman"/>
         <b val="1"/>
         <color rgb="00C2410C"/>
-        <sz val="8.5"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="00FFF7ED"/>
+        <patternFill>
+          <bgColor rgb="00FFF7ED"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
+        <name val="Times New Roman"/>
         <b val="1"/>
         <color rgb="003730A3"/>
-        <sz val="8.5"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="00E0E7FF"/>
+        <patternFill>
+          <bgColor rgb="00E0E7FF"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
+        <name val="Times New Roman"/>
         <b val="1"/>
         <color rgb="00BE123C"/>
-        <sz val="8.5"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="00FFE4E6"/>
+        <patternFill>
+          <bgColor rgb="00FFE4E6"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
+        <name val="Times New Roman"/>
         <b val="1"/>
         <color rgb="003F6212"/>
-        <sz val="8.5"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="00ECFCCB"/>
+        <patternFill>
+          <bgColor rgb="00ECFCCB"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
+        <name val="Times New Roman"/>
         <b val="1"/>
         <color rgb="00475569"/>
-        <sz val="8.5"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="00F1F5F9"/>
+        <patternFill>
+          <bgColor rgb="00F1F5F9"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
+        <name val="Times New Roman"/>
         <b val="1"/>
         <color rgb="00713F12"/>
-        <sz val="8.5"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="00FEF9C3"/>
+        <patternFill>
+          <bgColor rgb="00FEF9C3"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="00F6F7F9"/>
+        <patternFill>
+          <bgColor rgb="00F3F4F6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="00E2EFDA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="00B4C6E7"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1053,71 +1030,61 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AK60"/>
+  <dimension ref="A1:AK112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="6.4" customWidth="1" min="1" max="1"/>
-    <col width="9.5" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
-    <col width="8.800000000000001" customWidth="1" min="4" max="4"/>
-    <col width="3.5" customWidth="1" min="5" max="5"/>
-    <col width="3.5" customWidth="1" min="6" max="6"/>
-    <col width="3.5" customWidth="1" min="7" max="7"/>
-    <col width="3.5" customWidth="1" min="8" max="8"/>
-    <col width="3.5" customWidth="1" min="9" max="9"/>
-    <col width="3.5" customWidth="1" min="10" max="10"/>
-    <col width="3.5" customWidth="1" min="11" max="11"/>
-    <col width="3.5" customWidth="1" min="12" max="12"/>
-    <col width="3.5" customWidth="1" min="13" max="13"/>
-    <col width="3.5" customWidth="1" min="14" max="14"/>
-    <col width="3.5" customWidth="1" min="15" max="15"/>
-    <col width="3.5" customWidth="1" min="16" max="16"/>
-    <col width="3.5" customWidth="1" min="17" max="17"/>
-    <col width="3.5" customWidth="1" min="18" max="18"/>
-    <col width="3.5" customWidth="1" min="19" max="19"/>
-    <col width="3.5" customWidth="1" min="20" max="20"/>
-    <col width="3.5" customWidth="1" min="21" max="21"/>
-    <col width="3.5" customWidth="1" min="22" max="22"/>
-    <col width="3.5" customWidth="1" min="23" max="23"/>
-    <col width="3.5" customWidth="1" min="24" max="24"/>
-    <col width="3.5" customWidth="1" min="25" max="25"/>
-    <col width="3.5" customWidth="1" min="26" max="26"/>
-    <col width="3.5" customWidth="1" min="27" max="27"/>
-    <col width="3.5" customWidth="1" min="28" max="28"/>
-    <col width="3.5" customWidth="1" min="29" max="29"/>
-    <col width="3.5" customWidth="1" min="30" max="30"/>
-    <col width="3.5" customWidth="1" min="31" max="31"/>
-    <col width="3.5" customWidth="1" min="32" max="32"/>
-    <col width="3.5" customWidth="1" min="33" max="33"/>
-    <col width="3.5" customWidth="1" min="34" max="34"/>
-    <col width="3.5" customWidth="1" min="35" max="35"/>
+    <col width="6.8" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="10.5" customWidth="1" min="4" max="4"/>
+    <col width="4.6" customWidth="1" min="5" max="5"/>
+    <col width="4.6" customWidth="1" min="6" max="6"/>
+    <col width="4.6" customWidth="1" min="7" max="7"/>
+    <col width="4.6" customWidth="1" min="8" max="8"/>
+    <col width="4.6" customWidth="1" min="9" max="9"/>
+    <col width="4.6" customWidth="1" min="10" max="10"/>
+    <col width="4.6" customWidth="1" min="11" max="11"/>
+    <col width="4.6" customWidth="1" min="12" max="12"/>
+    <col width="4.6" customWidth="1" min="13" max="13"/>
+    <col width="4.6" customWidth="1" min="14" max="14"/>
+    <col width="4.6" customWidth="1" min="15" max="15"/>
+    <col width="4.6" customWidth="1" min="16" max="16"/>
+    <col width="4.6" customWidth="1" min="17" max="17"/>
+    <col width="4.6" customWidth="1" min="18" max="18"/>
+    <col width="4.6" customWidth="1" min="19" max="19"/>
+    <col width="4.6" customWidth="1" min="20" max="20"/>
+    <col width="4.6" customWidth="1" min="21" max="21"/>
+    <col width="4.6" customWidth="1" min="22" max="22"/>
+    <col width="4.6" customWidth="1" min="23" max="23"/>
+    <col width="4.6" customWidth="1" min="24" max="24"/>
+    <col width="4.6" customWidth="1" min="25" max="25"/>
+    <col width="4.6" customWidth="1" min="26" max="26"/>
+    <col width="4.6" customWidth="1" min="27" max="27"/>
+    <col width="4.6" customWidth="1" min="28" max="28"/>
+    <col width="4.6" customWidth="1" min="29" max="29"/>
+    <col width="4.6" customWidth="1" min="30" max="30"/>
+    <col width="4.6" customWidth="1" min="31" max="31"/>
+    <col width="4.6" customWidth="1" min="32" max="32"/>
+    <col width="4.6" customWidth="1" min="33" max="33"/>
+    <col width="4.6" customWidth="1" min="34" max="34"/>
+    <col width="4.6" customWidth="1" min="35" max="35"/>
     <col hidden="1" width="13" customWidth="1" min="37" max="37"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1">
+    <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>SAUDIA TECHNIC</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>AIRCRAFT HEAVY MAINTENANCE · SPV CABIN — MONTHLY ROSTER</t>
-        </is>
-      </c>
-      <c r="AF1" s="3" t="inlineStr">
-        <is>
-          <t>CC: 264</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="16" customHeight="1">
-      <c r="A2" s="42" t="inlineStr">
+          <t>SAUDIA TECHNIC — AIRCRAFT HEAVY MAINTENANCE · SPV CABIN MONTHLY ROSTER · CC: 264</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>MONTH</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>JUL</t>
         </is>
@@ -1127,10 +1094,10 @@
           <t>YEAR</t>
         </is>
       </c>
-      <c r="D2" s="5" t="n">
+      <c r="D2" s="3" t="n">
         <v>2026</v>
       </c>
-      <c r="E2" s="6">
+      <c r="E2" s="5">
         <f>TEXT(DATE($D$2,$AK$2,1),"mmmm yyyy")</f>
         <v/>
       </c>
@@ -1139,319 +1106,289 @@
         <v/>
       </c>
     </row>
-    <row r="3" ht="12" customHeight="1">
-      <c r="E3" s="7">
+    <row r="3" ht="17" customHeight="1">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>CREW 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="13" customHeight="1">
+      <c r="E4" s="7">
         <f>IF(1&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,1),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="F3" s="7">
+      <c r="F4" s="7">
         <f>IF(2&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,2),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="G3" s="7">
+      <c r="G4" s="7">
         <f>IF(3&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,3),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="H3" s="7">
+      <c r="H4" s="7">
         <f>IF(4&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,4),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="I3" s="7">
+      <c r="I4" s="7">
         <f>IF(5&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,5),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="J3" s="7">
+      <c r="J4" s="7">
         <f>IF(6&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,6),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="K3" s="7">
+      <c r="K4" s="7">
         <f>IF(7&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,7),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="L3" s="7">
+      <c r="L4" s="7">
         <f>IF(8&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,8),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="M3" s="7">
+      <c r="M4" s="7">
         <f>IF(9&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,9),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="N3" s="7">
+      <c r="N4" s="7">
         <f>IF(10&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,10),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="O3" s="7">
+      <c r="O4" s="7">
         <f>IF(11&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,11),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="P3" s="7">
+      <c r="P4" s="7">
         <f>IF(12&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,12),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="Q3" s="7">
+      <c r="Q4" s="7">
         <f>IF(13&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,13),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="R3" s="7">
+      <c r="R4" s="7">
         <f>IF(14&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,14),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="S3" s="7">
+      <c r="S4" s="7">
         <f>IF(15&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,15),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="T3" s="7">
+      <c r="T4" s="7">
         <f>IF(16&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,16),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="U3" s="7">
+      <c r="U4" s="7">
         <f>IF(17&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,17),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="V3" s="7">
+      <c r="V4" s="7">
         <f>IF(18&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,18),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="W3" s="7">
+      <c r="W4" s="7">
         <f>IF(19&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,19),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="X3" s="7">
+      <c r="X4" s="7">
         <f>IF(20&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,20),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="Y3" s="7">
+      <c r="Y4" s="7">
         <f>IF(21&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,21),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="Z3" s="7">
+      <c r="Z4" s="7">
         <f>IF(22&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,22),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="AA3" s="7">
+      <c r="AA4" s="7">
         <f>IF(23&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,23),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="AB3" s="7">
+      <c r="AB4" s="7">
         <f>IF(24&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,24),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="AC3" s="7">
+      <c r="AC4" s="7">
         <f>IF(25&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,25),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="AD3" s="7">
+      <c r="AD4" s="7">
         <f>IF(26&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,26),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="AE3" s="7">
+      <c r="AE4" s="7">
         <f>IF(27&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,27),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="AF3" s="7">
+      <c r="AF4" s="7">
         <f>IF(28&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,28),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="AG3" s="7">
+      <c r="AG4" s="7">
         <f>IF(29&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,29),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="AH3" s="7">
+      <c r="AH4" s="7">
         <f>IF(30&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,30),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="AI3" s="7">
+      <c r="AI4" s="7">
         <f>IF(31&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,31),"ddd"),"")</f>
         <v/>
       </c>
     </row>
-    <row r="4" ht="14" customHeight="1">
-      <c r="A4" s="8" t="inlineStr">
+    <row r="5" ht="16" customHeight="1">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B5" s="8" t="inlineStr">
         <is>
           <t>PRN</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C5" s="8" t="inlineStr">
         <is>
           <t>NAME</t>
         </is>
       </c>
-      <c r="D4" s="8" t="inlineStr">
+      <c r="D5" s="8" t="inlineStr">
         <is>
           <t>Posn</t>
         </is>
       </c>
-      <c r="E4" s="8">
+      <c r="E5" s="9">
         <f>IF(1&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),1,"")</f>
         <v/>
       </c>
-      <c r="F4" s="8">
+      <c r="F5" s="9">
         <f>IF(2&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),2,"")</f>
         <v/>
       </c>
-      <c r="G4" s="8">
+      <c r="G5" s="9">
         <f>IF(3&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),3,"")</f>
         <v/>
       </c>
-      <c r="H4" s="8">
+      <c r="H5" s="9">
         <f>IF(4&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),4,"")</f>
         <v/>
       </c>
-      <c r="I4" s="8">
+      <c r="I5" s="9">
         <f>IF(5&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),5,"")</f>
         <v/>
       </c>
-      <c r="J4" s="8">
+      <c r="J5" s="9">
         <f>IF(6&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),6,"")</f>
         <v/>
       </c>
-      <c r="K4" s="8">
+      <c r="K5" s="9">
         <f>IF(7&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),7,"")</f>
         <v/>
       </c>
-      <c r="L4" s="8">
+      <c r="L5" s="9">
         <f>IF(8&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),8,"")</f>
         <v/>
       </c>
-      <c r="M4" s="8">
+      <c r="M5" s="9">
         <f>IF(9&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),9,"")</f>
         <v/>
       </c>
-      <c r="N4" s="8">
+      <c r="N5" s="9">
         <f>IF(10&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),10,"")</f>
         <v/>
       </c>
-      <c r="O4" s="8">
+      <c r="O5" s="9">
         <f>IF(11&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),11,"")</f>
         <v/>
       </c>
-      <c r="P4" s="8">
+      <c r="P5" s="9">
         <f>IF(12&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),12,"")</f>
         <v/>
       </c>
-      <c r="Q4" s="8">
+      <c r="Q5" s="9">
         <f>IF(13&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),13,"")</f>
         <v/>
       </c>
-      <c r="R4" s="8">
+      <c r="R5" s="9">
         <f>IF(14&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),14,"")</f>
         <v/>
       </c>
-      <c r="S4" s="8">
+      <c r="S5" s="9">
         <f>IF(15&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),15,"")</f>
         <v/>
       </c>
-      <c r="T4" s="8">
+      <c r="T5" s="9">
         <f>IF(16&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),16,"")</f>
         <v/>
       </c>
-      <c r="U4" s="8">
+      <c r="U5" s="9">
         <f>IF(17&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),17,"")</f>
         <v/>
       </c>
-      <c r="V4" s="8">
+      <c r="V5" s="9">
         <f>IF(18&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),18,"")</f>
         <v/>
       </c>
-      <c r="W4" s="8">
+      <c r="W5" s="9">
         <f>IF(19&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),19,"")</f>
         <v/>
       </c>
-      <c r="X4" s="8">
+      <c r="X5" s="9">
         <f>IF(20&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),20,"")</f>
         <v/>
       </c>
-      <c r="Y4" s="8">
+      <c r="Y5" s="9">
         <f>IF(21&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),21,"")</f>
         <v/>
       </c>
-      <c r="Z4" s="8">
+      <c r="Z5" s="9">
         <f>IF(22&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),22,"")</f>
         <v/>
       </c>
-      <c r="AA4" s="8">
+      <c r="AA5" s="9">
         <f>IF(23&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),23,"")</f>
         <v/>
       </c>
-      <c r="AB4" s="8">
+      <c r="AB5" s="9">
         <f>IF(24&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),24,"")</f>
         <v/>
       </c>
-      <c r="AC4" s="8">
+      <c r="AC5" s="9">
         <f>IF(25&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),25,"")</f>
         <v/>
       </c>
-      <c r="AD4" s="8">
+      <c r="AD5" s="9">
         <f>IF(26&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),26,"")</f>
         <v/>
       </c>
-      <c r="AE4" s="8">
+      <c r="AE5" s="9">
         <f>IF(27&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),27,"")</f>
         <v/>
       </c>
-      <c r="AF4" s="8">
+      <c r="AF5" s="9">
         <f>IF(28&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),28,"")</f>
         <v/>
       </c>
-      <c r="AG4" s="8">
+      <c r="AG5" s="9">
         <f>IF(29&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),29,"")</f>
         <v/>
       </c>
-      <c r="AH4" s="8">
+      <c r="AH5" s="9">
         <f>IF(30&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),30,"")</f>
         <v/>
       </c>
-      <c r="AI4" s="8">
+      <c r="AI5" s="9">
         <f>IF(31&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),31,"")</f>
         <v/>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="9" t="inlineStr">
-        <is>
-          <t>CREW 1</t>
-        </is>
-      </c>
-      <c r="E5" s="10" t="n"/>
-      <c r="F5" s="10" t="n"/>
-      <c r="G5" s="10" t="n"/>
-      <c r="H5" s="10" t="n"/>
-      <c r="I5" s="10" t="n"/>
-      <c r="J5" s="10" t="n"/>
-      <c r="K5" s="10" t="n"/>
-      <c r="L5" s="10" t="n"/>
-      <c r="M5" s="10" t="n"/>
-      <c r="N5" s="10" t="n"/>
-      <c r="O5" s="10" t="n"/>
-      <c r="P5" s="10" t="n"/>
-      <c r="Q5" s="10" t="n"/>
-      <c r="R5" s="10" t="n"/>
-      <c r="S5" s="10" t="n"/>
-      <c r="T5" s="10" t="n"/>
-      <c r="U5" s="10" t="n"/>
-      <c r="V5" s="10" t="n"/>
-      <c r="W5" s="10" t="n"/>
-      <c r="X5" s="10" t="n"/>
-      <c r="Y5" s="10" t="n"/>
-      <c r="Z5" s="10" t="n"/>
-      <c r="AA5" s="10" t="n"/>
-      <c r="AB5" s="10" t="n"/>
-      <c r="AC5" s="10" t="n"/>
-      <c r="AD5" s="10" t="n"/>
-      <c r="AE5" s="10" t="n"/>
-      <c r="AF5" s="10" t="n"/>
-      <c r="AG5" s="10" t="n"/>
-      <c r="AH5" s="10" t="n"/>
-      <c r="AI5" s="10" t="n"/>
-    </row>
-    <row r="6" ht="14.5" customHeight="1">
-      <c r="A6" s="11" t="n">
-        <v>1</v>
+    <row r="6" ht="17" customHeight="1">
+      <c r="A6" s="10">
+        <f>IF($C6="","",ROW()-5)</f>
+        <v/>
       </c>
       <c r="B6" s="11" t="n"/>
       <c r="C6" s="12" t="n"/>
@@ -1488,9 +1425,10 @@
       <c r="AH6" s="13" t="n"/>
       <c r="AI6" s="13" t="n"/>
     </row>
-    <row r="7" ht="14.5" customHeight="1">
-      <c r="A7" s="11" t="n">
-        <v>2</v>
+    <row r="7" ht="17" customHeight="1">
+      <c r="A7" s="10">
+        <f>IF($C7="","",ROW()-5)</f>
+        <v/>
       </c>
       <c r="B7" s="11" t="n"/>
       <c r="C7" s="12" t="n"/>
@@ -1527,9 +1465,10 @@
       <c r="AH7" s="13" t="n"/>
       <c r="AI7" s="13" t="n"/>
     </row>
-    <row r="8" ht="14.5" customHeight="1">
-      <c r="A8" s="11" t="n">
-        <v>3</v>
+    <row r="8" ht="17" customHeight="1">
+      <c r="A8" s="10">
+        <f>IF($C8="","",ROW()-5)</f>
+        <v/>
       </c>
       <c r="B8" s="11" t="n"/>
       <c r="C8" s="12" t="n"/>
@@ -1566,9 +1505,10 @@
       <c r="AH8" s="13" t="n"/>
       <c r="AI8" s="13" t="n"/>
     </row>
-    <row r="9" ht="14.5" customHeight="1">
-      <c r="A9" s="11" t="n">
-        <v>4</v>
+    <row r="9" ht="17" customHeight="1">
+      <c r="A9" s="10">
+        <f>IF($C9="","",ROW()-5)</f>
+        <v/>
       </c>
       <c r="B9" s="11" t="n"/>
       <c r="C9" s="12" t="n"/>
@@ -1605,9 +1545,10 @@
       <c r="AH9" s="13" t="n"/>
       <c r="AI9" s="13" t="n"/>
     </row>
-    <row r="10" ht="14.5" customHeight="1">
-      <c r="A10" s="11" t="n">
-        <v>5</v>
+    <row r="10" ht="17" customHeight="1">
+      <c r="A10" s="10">
+        <f>IF($C10="","",ROW()-5)</f>
+        <v/>
       </c>
       <c r="B10" s="11" t="n"/>
       <c r="C10" s="12" t="n"/>
@@ -1644,9 +1585,10 @@
       <c r="AH10" s="13" t="n"/>
       <c r="AI10" s="13" t="n"/>
     </row>
-    <row r="11" ht="14.5" customHeight="1">
-      <c r="A11" s="11" t="n">
-        <v>6</v>
+    <row r="11" ht="17" customHeight="1">
+      <c r="A11" s="10">
+        <f>IF($C11="","",ROW()-5)</f>
+        <v/>
       </c>
       <c r="B11" s="11" t="n"/>
       <c r="C11" s="12" t="n"/>
@@ -1683,9 +1625,10 @@
       <c r="AH11" s="13" t="n"/>
       <c r="AI11" s="13" t="n"/>
     </row>
-    <row r="12" ht="14.5" customHeight="1">
-      <c r="A12" s="11" t="n">
-        <v>7</v>
+    <row r="12" ht="17" customHeight="1">
+      <c r="A12" s="10">
+        <f>IF($C12="","",ROW()-5)</f>
+        <v/>
       </c>
       <c r="B12" s="11" t="n"/>
       <c r="C12" s="12" t="n"/>
@@ -1722,9 +1665,10 @@
       <c r="AH12" s="13" t="n"/>
       <c r="AI12" s="13" t="n"/>
     </row>
-    <row r="13" ht="14.5" customHeight="1">
-      <c r="A13" s="11" t="n">
-        <v>8</v>
+    <row r="13" ht="17" customHeight="1">
+      <c r="A13" s="10">
+        <f>IF($C13="","",ROW()-5)</f>
+        <v/>
       </c>
       <c r="B13" s="11" t="n"/>
       <c r="C13" s="12" t="n"/>
@@ -1761,9 +1705,10 @@
       <c r="AH13" s="13" t="n"/>
       <c r="AI13" s="13" t="n"/>
     </row>
-    <row r="14" ht="14.5" customHeight="1">
-      <c r="A14" s="11" t="n">
-        <v>9</v>
+    <row r="14" ht="17" customHeight="1">
+      <c r="A14" s="10">
+        <f>IF($C14="","",ROW()-5)</f>
+        <v/>
       </c>
       <c r="B14" s="11" t="n"/>
       <c r="C14" s="12" t="n"/>
@@ -1800,9 +1745,10 @@
       <c r="AH14" s="13" t="n"/>
       <c r="AI14" s="13" t="n"/>
     </row>
-    <row r="15" ht="14.5" customHeight="1">
-      <c r="A15" s="11" t="n">
-        <v>10</v>
+    <row r="15" ht="17" customHeight="1">
+      <c r="A15" s="10">
+        <f>IF($C15="","",ROW()-5)</f>
+        <v/>
       </c>
       <c r="B15" s="11" t="n"/>
       <c r="C15" s="12" t="n"/>
@@ -1839,9 +1785,10 @@
       <c r="AH15" s="13" t="n"/>
       <c r="AI15" s="13" t="n"/>
     </row>
-    <row r="16" ht="14.5" customHeight="1">
-      <c r="A16" s="11" t="n">
-        <v>11</v>
+    <row r="16" ht="17" customHeight="1">
+      <c r="A16" s="10">
+        <f>IF($C16="","",ROW()-5)</f>
+        <v/>
       </c>
       <c r="B16" s="11" t="n"/>
       <c r="C16" s="12" t="n"/>
@@ -1878,9 +1825,10 @@
       <c r="AH16" s="13" t="n"/>
       <c r="AI16" s="13" t="n"/>
     </row>
-    <row r="17" ht="14.5" customHeight="1">
-      <c r="A17" s="11" t="n">
-        <v>12</v>
+    <row r="17" ht="17" customHeight="1">
+      <c r="A17" s="10">
+        <f>IF($C17="","",ROW()-5)</f>
+        <v/>
       </c>
       <c r="B17" s="11" t="n"/>
       <c r="C17" s="12" t="n"/>
@@ -1917,125 +1865,289 @@
       <c r="AH17" s="13" t="n"/>
       <c r="AI17" s="13" t="n"/>
     </row>
-    <row r="18" ht="15" customHeight="1">
+    <row r="18" ht="17" customHeight="1">
       <c r="A18" s="14" t="inlineStr">
         <is>
           <t>CREW 2</t>
         </is>
       </c>
-      <c r="E18" s="15" t="n"/>
-      <c r="F18" s="15" t="n"/>
-      <c r="G18" s="15" t="n"/>
-      <c r="H18" s="15" t="n"/>
-      <c r="I18" s="15" t="n"/>
-      <c r="J18" s="15" t="n"/>
-      <c r="K18" s="15" t="n"/>
-      <c r="L18" s="15" t="n"/>
-      <c r="M18" s="15" t="n"/>
-      <c r="N18" s="15" t="n"/>
-      <c r="O18" s="15" t="n"/>
-      <c r="P18" s="15" t="n"/>
-      <c r="Q18" s="15" t="n"/>
-      <c r="R18" s="15" t="n"/>
-      <c r="S18" s="15" t="n"/>
-      <c r="T18" s="15" t="n"/>
-      <c r="U18" s="15" t="n"/>
-      <c r="V18" s="15" t="n"/>
-      <c r="W18" s="15" t="n"/>
-      <c r="X18" s="15" t="n"/>
-      <c r="Y18" s="15" t="n"/>
-      <c r="Z18" s="15" t="n"/>
-      <c r="AA18" s="15" t="n"/>
-      <c r="AB18" s="15" t="n"/>
-      <c r="AC18" s="15" t="n"/>
-      <c r="AD18" s="15" t="n"/>
-      <c r="AE18" s="15" t="n"/>
-      <c r="AF18" s="15" t="n"/>
-      <c r="AG18" s="15" t="n"/>
-      <c r="AH18" s="15" t="n"/>
-      <c r="AI18" s="15" t="n"/>
-    </row>
-    <row r="19" ht="14.5" customHeight="1">
-      <c r="A19" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="B19" s="11" t="n"/>
-      <c r="C19" s="12" t="n"/>
-      <c r="D19" s="11" t="n"/>
-      <c r="E19" s="13" t="n"/>
-      <c r="F19" s="13" t="n"/>
-      <c r="G19" s="13" t="n"/>
-      <c r="H19" s="13" t="n"/>
-      <c r="I19" s="13" t="n"/>
-      <c r="J19" s="13" t="n"/>
-      <c r="K19" s="13" t="n"/>
-      <c r="L19" s="13" t="n"/>
-      <c r="M19" s="13" t="n"/>
-      <c r="N19" s="13" t="n"/>
-      <c r="O19" s="13" t="n"/>
-      <c r="P19" s="13" t="n"/>
-      <c r="Q19" s="13" t="n"/>
-      <c r="R19" s="13" t="n"/>
-      <c r="S19" s="13" t="n"/>
-      <c r="T19" s="13" t="n"/>
-      <c r="U19" s="13" t="n"/>
-      <c r="V19" s="13" t="n"/>
-      <c r="W19" s="13" t="n"/>
-      <c r="X19" s="13" t="n"/>
-      <c r="Y19" s="13" t="n"/>
-      <c r="Z19" s="13" t="n"/>
-      <c r="AA19" s="13" t="n"/>
-      <c r="AB19" s="13" t="n"/>
-      <c r="AC19" s="13" t="n"/>
-      <c r="AD19" s="13" t="n"/>
-      <c r="AE19" s="13" t="n"/>
-      <c r="AF19" s="13" t="n"/>
-      <c r="AG19" s="13" t="n"/>
-      <c r="AH19" s="13" t="n"/>
-      <c r="AI19" s="13" t="n"/>
-    </row>
-    <row r="20" ht="14.5" customHeight="1">
-      <c r="A20" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="B20" s="11" t="n"/>
-      <c r="C20" s="12" t="n"/>
-      <c r="D20" s="11" t="n"/>
-      <c r="E20" s="13" t="n"/>
-      <c r="F20" s="13" t="n"/>
-      <c r="G20" s="13" t="n"/>
-      <c r="H20" s="13" t="n"/>
-      <c r="I20" s="13" t="n"/>
-      <c r="J20" s="13" t="n"/>
-      <c r="K20" s="13" t="n"/>
-      <c r="L20" s="13" t="n"/>
-      <c r="M20" s="13" t="n"/>
-      <c r="N20" s="13" t="n"/>
-      <c r="O20" s="13" t="n"/>
-      <c r="P20" s="13" t="n"/>
-      <c r="Q20" s="13" t="n"/>
-      <c r="R20" s="13" t="n"/>
-      <c r="S20" s="13" t="n"/>
-      <c r="T20" s="13" t="n"/>
-      <c r="U20" s="13" t="n"/>
-      <c r="V20" s="13" t="n"/>
-      <c r="W20" s="13" t="n"/>
-      <c r="X20" s="13" t="n"/>
-      <c r="Y20" s="13" t="n"/>
-      <c r="Z20" s="13" t="n"/>
-      <c r="AA20" s="13" t="n"/>
-      <c r="AB20" s="13" t="n"/>
-      <c r="AC20" s="13" t="n"/>
-      <c r="AD20" s="13" t="n"/>
-      <c r="AE20" s="13" t="n"/>
-      <c r="AF20" s="13" t="n"/>
-      <c r="AG20" s="13" t="n"/>
-      <c r="AH20" s="13" t="n"/>
-      <c r="AI20" s="13" t="n"/>
-    </row>
-    <row r="21" ht="14.5" customHeight="1">
-      <c r="A21" s="11" t="n">
-        <v>3</v>
+    </row>
+    <row r="19" ht="13" customHeight="1">
+      <c r="E19" s="7">
+        <f>IF(1&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,1),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="F19" s="7">
+        <f>IF(2&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,2),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="G19" s="7">
+        <f>IF(3&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,3),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="H19" s="7">
+        <f>IF(4&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,4),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="I19" s="7">
+        <f>IF(5&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,5),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="J19" s="7">
+        <f>IF(6&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,6),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="K19" s="7">
+        <f>IF(7&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,7),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="L19" s="7">
+        <f>IF(8&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,8),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="M19" s="7">
+        <f>IF(9&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,9),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="N19" s="7">
+        <f>IF(10&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,10),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="O19" s="7">
+        <f>IF(11&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,11),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="P19" s="7">
+        <f>IF(12&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,12),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="Q19" s="7">
+        <f>IF(13&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,13),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="R19" s="7">
+        <f>IF(14&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,14),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="S19" s="7">
+        <f>IF(15&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,15),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="T19" s="7">
+        <f>IF(16&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,16),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="U19" s="7">
+        <f>IF(17&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,17),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="V19" s="7">
+        <f>IF(18&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,18),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="W19" s="7">
+        <f>IF(19&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,19),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="X19" s="7">
+        <f>IF(20&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,20),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="Y19" s="7">
+        <f>IF(21&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,21),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="Z19" s="7">
+        <f>IF(22&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,22),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="AA19" s="7">
+        <f>IF(23&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,23),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="AB19" s="7">
+        <f>IF(24&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,24),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="AC19" s="7">
+        <f>IF(25&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,25),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="AD19" s="7">
+        <f>IF(26&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,26),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="AE19" s="7">
+        <f>IF(27&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,27),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="AF19" s="7">
+        <f>IF(28&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,28),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="AG19" s="7">
+        <f>IF(29&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,29),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="AH19" s="7">
+        <f>IF(30&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,30),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="AI19" s="7">
+        <f>IF(31&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,31),"ddd"),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="16" customHeight="1">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>PRN</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>NAME</t>
+        </is>
+      </c>
+      <c r="D20" s="8" t="inlineStr">
+        <is>
+          <t>Posn</t>
+        </is>
+      </c>
+      <c r="E20" s="9">
+        <f>IF(1&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),1,"")</f>
+        <v/>
+      </c>
+      <c r="F20" s="9">
+        <f>IF(2&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),2,"")</f>
+        <v/>
+      </c>
+      <c r="G20" s="9">
+        <f>IF(3&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),3,"")</f>
+        <v/>
+      </c>
+      <c r="H20" s="9">
+        <f>IF(4&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),4,"")</f>
+        <v/>
+      </c>
+      <c r="I20" s="9">
+        <f>IF(5&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),5,"")</f>
+        <v/>
+      </c>
+      <c r="J20" s="9">
+        <f>IF(6&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),6,"")</f>
+        <v/>
+      </c>
+      <c r="K20" s="9">
+        <f>IF(7&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),7,"")</f>
+        <v/>
+      </c>
+      <c r="L20" s="9">
+        <f>IF(8&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),8,"")</f>
+        <v/>
+      </c>
+      <c r="M20" s="9">
+        <f>IF(9&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),9,"")</f>
+        <v/>
+      </c>
+      <c r="N20" s="9">
+        <f>IF(10&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),10,"")</f>
+        <v/>
+      </c>
+      <c r="O20" s="9">
+        <f>IF(11&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),11,"")</f>
+        <v/>
+      </c>
+      <c r="P20" s="9">
+        <f>IF(12&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),12,"")</f>
+        <v/>
+      </c>
+      <c r="Q20" s="9">
+        <f>IF(13&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),13,"")</f>
+        <v/>
+      </c>
+      <c r="R20" s="9">
+        <f>IF(14&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),14,"")</f>
+        <v/>
+      </c>
+      <c r="S20" s="9">
+        <f>IF(15&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),15,"")</f>
+        <v/>
+      </c>
+      <c r="T20" s="9">
+        <f>IF(16&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),16,"")</f>
+        <v/>
+      </c>
+      <c r="U20" s="9">
+        <f>IF(17&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),17,"")</f>
+        <v/>
+      </c>
+      <c r="V20" s="9">
+        <f>IF(18&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),18,"")</f>
+        <v/>
+      </c>
+      <c r="W20" s="9">
+        <f>IF(19&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),19,"")</f>
+        <v/>
+      </c>
+      <c r="X20" s="9">
+        <f>IF(20&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),20,"")</f>
+        <v/>
+      </c>
+      <c r="Y20" s="9">
+        <f>IF(21&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),21,"")</f>
+        <v/>
+      </c>
+      <c r="Z20" s="9">
+        <f>IF(22&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),22,"")</f>
+        <v/>
+      </c>
+      <c r="AA20" s="9">
+        <f>IF(23&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),23,"")</f>
+        <v/>
+      </c>
+      <c r="AB20" s="9">
+        <f>IF(24&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),24,"")</f>
+        <v/>
+      </c>
+      <c r="AC20" s="9">
+        <f>IF(25&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),25,"")</f>
+        <v/>
+      </c>
+      <c r="AD20" s="9">
+        <f>IF(26&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),26,"")</f>
+        <v/>
+      </c>
+      <c r="AE20" s="9">
+        <f>IF(27&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),27,"")</f>
+        <v/>
+      </c>
+      <c r="AF20" s="9">
+        <f>IF(28&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),28,"")</f>
+        <v/>
+      </c>
+      <c r="AG20" s="9">
+        <f>IF(29&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),29,"")</f>
+        <v/>
+      </c>
+      <c r="AH20" s="9">
+        <f>IF(30&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),30,"")</f>
+        <v/>
+      </c>
+      <c r="AI20" s="9">
+        <f>IF(31&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),31,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="17" customHeight="1">
+      <c r="A21" s="10">
+        <f>IF($C21="","",ROW()-20)</f>
+        <v/>
       </c>
       <c r="B21" s="11" t="n"/>
       <c r="C21" s="12" t="n"/>
@@ -2072,9 +2184,10 @@
       <c r="AH21" s="13" t="n"/>
       <c r="AI21" s="13" t="n"/>
     </row>
-    <row r="22" ht="14.5" customHeight="1">
-      <c r="A22" s="11" t="n">
-        <v>4</v>
+    <row r="22" ht="17" customHeight="1">
+      <c r="A22" s="10">
+        <f>IF($C22="","",ROW()-20)</f>
+        <v/>
       </c>
       <c r="B22" s="11" t="n"/>
       <c r="C22" s="12" t="n"/>
@@ -2111,9 +2224,10 @@
       <c r="AH22" s="13" t="n"/>
       <c r="AI22" s="13" t="n"/>
     </row>
-    <row r="23" ht="14.5" customHeight="1">
-      <c r="A23" s="11" t="n">
-        <v>5</v>
+    <row r="23" ht="17" customHeight="1">
+      <c r="A23" s="10">
+        <f>IF($C23="","",ROW()-20)</f>
+        <v/>
       </c>
       <c r="B23" s="11" t="n"/>
       <c r="C23" s="12" t="n"/>
@@ -2150,9 +2264,10 @@
       <c r="AH23" s="13" t="n"/>
       <c r="AI23" s="13" t="n"/>
     </row>
-    <row r="24" ht="14.5" customHeight="1">
-      <c r="A24" s="11" t="n">
-        <v>6</v>
+    <row r="24" ht="17" customHeight="1">
+      <c r="A24" s="10">
+        <f>IF($C24="","",ROW()-20)</f>
+        <v/>
       </c>
       <c r="B24" s="11" t="n"/>
       <c r="C24" s="12" t="n"/>
@@ -2189,9 +2304,10 @@
       <c r="AH24" s="13" t="n"/>
       <c r="AI24" s="13" t="n"/>
     </row>
-    <row r="25" ht="14.5" customHeight="1">
-      <c r="A25" s="11" t="n">
-        <v>7</v>
+    <row r="25" ht="17" customHeight="1">
+      <c r="A25" s="10">
+        <f>IF($C25="","",ROW()-20)</f>
+        <v/>
       </c>
       <c r="B25" s="11" t="n"/>
       <c r="C25" s="12" t="n"/>
@@ -2228,9 +2344,10 @@
       <c r="AH25" s="13" t="n"/>
       <c r="AI25" s="13" t="n"/>
     </row>
-    <row r="26" ht="14.5" customHeight="1">
-      <c r="A26" s="11" t="n">
-        <v>8</v>
+    <row r="26" ht="17" customHeight="1">
+      <c r="A26" s="10">
+        <f>IF($C26="","",ROW()-20)</f>
+        <v/>
       </c>
       <c r="B26" s="11" t="n"/>
       <c r="C26" s="12" t="n"/>
@@ -2267,9 +2384,10 @@
       <c r="AH26" s="13" t="n"/>
       <c r="AI26" s="13" t="n"/>
     </row>
-    <row r="27" ht="14.5" customHeight="1">
-      <c r="A27" s="11" t="n">
-        <v>9</v>
+    <row r="27" ht="17" customHeight="1">
+      <c r="A27" s="10">
+        <f>IF($C27="","",ROW()-20)</f>
+        <v/>
       </c>
       <c r="B27" s="11" t="n"/>
       <c r="C27" s="12" t="n"/>
@@ -2306,9 +2424,10 @@
       <c r="AH27" s="13" t="n"/>
       <c r="AI27" s="13" t="n"/>
     </row>
-    <row r="28" ht="14.5" customHeight="1">
-      <c r="A28" s="11" t="n">
-        <v>10</v>
+    <row r="28" ht="17" customHeight="1">
+      <c r="A28" s="10">
+        <f>IF($C28="","",ROW()-20)</f>
+        <v/>
       </c>
       <c r="B28" s="11" t="n"/>
       <c r="C28" s="12" t="n"/>
@@ -2345,9 +2464,10 @@
       <c r="AH28" s="13" t="n"/>
       <c r="AI28" s="13" t="n"/>
     </row>
-    <row r="29" ht="14.5" customHeight="1">
-      <c r="A29" s="11" t="n">
-        <v>11</v>
+    <row r="29" ht="17" customHeight="1">
+      <c r="A29" s="10">
+        <f>IF($C29="","",ROW()-20)</f>
+        <v/>
       </c>
       <c r="B29" s="11" t="n"/>
       <c r="C29" s="12" t="n"/>
@@ -2384,9 +2504,10 @@
       <c r="AH29" s="13" t="n"/>
       <c r="AI29" s="13" t="n"/>
     </row>
-    <row r="30" ht="14.5" customHeight="1">
-      <c r="A30" s="11" t="n">
-        <v>12</v>
+    <row r="30" ht="17" customHeight="1">
+      <c r="A30" s="10">
+        <f>IF($C30="","",ROW()-20)</f>
+        <v/>
       </c>
       <c r="B30" s="11" t="n"/>
       <c r="C30" s="12" t="n"/>
@@ -2423,47 +2544,50 @@
       <c r="AH30" s="13" t="n"/>
       <c r="AI30" s="13" t="n"/>
     </row>
-    <row r="31" ht="15" customHeight="1">
-      <c r="A31" s="16" t="inlineStr">
-        <is>
-          <t>CREW 3</t>
-        </is>
-      </c>
-      <c r="E31" s="17" t="n"/>
-      <c r="F31" s="17" t="n"/>
-      <c r="G31" s="17" t="n"/>
-      <c r="H31" s="17" t="n"/>
-      <c r="I31" s="17" t="n"/>
-      <c r="J31" s="17" t="n"/>
-      <c r="K31" s="17" t="n"/>
-      <c r="L31" s="17" t="n"/>
-      <c r="M31" s="17" t="n"/>
-      <c r="N31" s="17" t="n"/>
-      <c r="O31" s="17" t="n"/>
-      <c r="P31" s="17" t="n"/>
-      <c r="Q31" s="17" t="n"/>
-      <c r="R31" s="17" t="n"/>
-      <c r="S31" s="17" t="n"/>
-      <c r="T31" s="17" t="n"/>
-      <c r="U31" s="17" t="n"/>
-      <c r="V31" s="17" t="n"/>
-      <c r="W31" s="17" t="n"/>
-      <c r="X31" s="17" t="n"/>
-      <c r="Y31" s="17" t="n"/>
-      <c r="Z31" s="17" t="n"/>
-      <c r="AA31" s="17" t="n"/>
-      <c r="AB31" s="17" t="n"/>
-      <c r="AC31" s="17" t="n"/>
-      <c r="AD31" s="17" t="n"/>
-      <c r="AE31" s="17" t="n"/>
-      <c r="AF31" s="17" t="n"/>
-      <c r="AG31" s="17" t="n"/>
-      <c r="AH31" s="17" t="n"/>
-      <c r="AI31" s="17" t="n"/>
-    </row>
-    <row r="32" ht="14.5" customHeight="1">
-      <c r="A32" s="11" t="n">
-        <v>1</v>
+    <row r="31" ht="17" customHeight="1">
+      <c r="A31" s="10">
+        <f>IF($C31="","",ROW()-20)</f>
+        <v/>
+      </c>
+      <c r="B31" s="11" t="n"/>
+      <c r="C31" s="12" t="n"/>
+      <c r="D31" s="11" t="n"/>
+      <c r="E31" s="13" t="n"/>
+      <c r="F31" s="13" t="n"/>
+      <c r="G31" s="13" t="n"/>
+      <c r="H31" s="13" t="n"/>
+      <c r="I31" s="13" t="n"/>
+      <c r="J31" s="13" t="n"/>
+      <c r="K31" s="13" t="n"/>
+      <c r="L31" s="13" t="n"/>
+      <c r="M31" s="13" t="n"/>
+      <c r="N31" s="13" t="n"/>
+      <c r="O31" s="13" t="n"/>
+      <c r="P31" s="13" t="n"/>
+      <c r="Q31" s="13" t="n"/>
+      <c r="R31" s="13" t="n"/>
+      <c r="S31" s="13" t="n"/>
+      <c r="T31" s="13" t="n"/>
+      <c r="U31" s="13" t="n"/>
+      <c r="V31" s="13" t="n"/>
+      <c r="W31" s="13" t="n"/>
+      <c r="X31" s="13" t="n"/>
+      <c r="Y31" s="13" t="n"/>
+      <c r="Z31" s="13" t="n"/>
+      <c r="AA31" s="13" t="n"/>
+      <c r="AB31" s="13" t="n"/>
+      <c r="AC31" s="13" t="n"/>
+      <c r="AD31" s="13" t="n"/>
+      <c r="AE31" s="13" t="n"/>
+      <c r="AF31" s="13" t="n"/>
+      <c r="AG31" s="13" t="n"/>
+      <c r="AH31" s="13" t="n"/>
+      <c r="AI31" s="13" t="n"/>
+    </row>
+    <row r="32" ht="17" customHeight="1">
+      <c r="A32" s="10">
+        <f>IF($C32="","",ROW()-20)</f>
+        <v/>
       </c>
       <c r="B32" s="11" t="n"/>
       <c r="C32" s="12" t="n"/>
@@ -2500,126 +2624,289 @@
       <c r="AH32" s="13" t="n"/>
       <c r="AI32" s="13" t="n"/>
     </row>
-    <row r="33" ht="14.5" customHeight="1">
-      <c r="A33" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="B33" s="11" t="n"/>
-      <c r="C33" s="12" t="n"/>
-      <c r="D33" s="11" t="n"/>
-      <c r="E33" s="13" t="n"/>
-      <c r="F33" s="13" t="n"/>
-      <c r="G33" s="13" t="n"/>
-      <c r="H33" s="13" t="n"/>
-      <c r="I33" s="13" t="n"/>
-      <c r="J33" s="13" t="n"/>
-      <c r="K33" s="13" t="n"/>
-      <c r="L33" s="13" t="n"/>
-      <c r="M33" s="13" t="n"/>
-      <c r="N33" s="13" t="n"/>
-      <c r="O33" s="13" t="n"/>
-      <c r="P33" s="13" t="n"/>
-      <c r="Q33" s="13" t="n"/>
-      <c r="R33" s="13" t="n"/>
-      <c r="S33" s="13" t="n"/>
-      <c r="T33" s="13" t="n"/>
-      <c r="U33" s="13" t="n"/>
-      <c r="V33" s="13" t="n"/>
-      <c r="W33" s="13" t="n"/>
-      <c r="X33" s="13" t="n"/>
-      <c r="Y33" s="13" t="n"/>
-      <c r="Z33" s="13" t="n"/>
-      <c r="AA33" s="13" t="n"/>
-      <c r="AB33" s="13" t="n"/>
-      <c r="AC33" s="13" t="n"/>
-      <c r="AD33" s="13" t="n"/>
-      <c r="AE33" s="13" t="n"/>
-      <c r="AF33" s="13" t="n"/>
-      <c r="AG33" s="13" t="n"/>
-      <c r="AH33" s="13" t="n"/>
-      <c r="AI33" s="13" t="n"/>
-    </row>
-    <row r="34" ht="14.5" customHeight="1">
-      <c r="A34" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="B34" s="11" t="n"/>
-      <c r="C34" s="12" t="n"/>
-      <c r="D34" s="11" t="n"/>
-      <c r="E34" s="13" t="n"/>
-      <c r="F34" s="13" t="n"/>
-      <c r="G34" s="13" t="n"/>
-      <c r="H34" s="13" t="n"/>
-      <c r="I34" s="13" t="n"/>
-      <c r="J34" s="13" t="n"/>
-      <c r="K34" s="13" t="n"/>
-      <c r="L34" s="13" t="n"/>
-      <c r="M34" s="13" t="n"/>
-      <c r="N34" s="13" t="n"/>
-      <c r="O34" s="13" t="n"/>
-      <c r="P34" s="13" t="n"/>
-      <c r="Q34" s="13" t="n"/>
-      <c r="R34" s="13" t="n"/>
-      <c r="S34" s="13" t="n"/>
-      <c r="T34" s="13" t="n"/>
-      <c r="U34" s="13" t="n"/>
-      <c r="V34" s="13" t="n"/>
-      <c r="W34" s="13" t="n"/>
-      <c r="X34" s="13" t="n"/>
-      <c r="Y34" s="13" t="n"/>
-      <c r="Z34" s="13" t="n"/>
-      <c r="AA34" s="13" t="n"/>
-      <c r="AB34" s="13" t="n"/>
-      <c r="AC34" s="13" t="n"/>
-      <c r="AD34" s="13" t="n"/>
-      <c r="AE34" s="13" t="n"/>
-      <c r="AF34" s="13" t="n"/>
-      <c r="AG34" s="13" t="n"/>
-      <c r="AH34" s="13" t="n"/>
-      <c r="AI34" s="13" t="n"/>
-    </row>
-    <row r="35" ht="14.5" customHeight="1">
-      <c r="A35" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="B35" s="11" t="n"/>
-      <c r="C35" s="12" t="n"/>
-      <c r="D35" s="11" t="n"/>
-      <c r="E35" s="13" t="n"/>
-      <c r="F35" s="13" t="n"/>
-      <c r="G35" s="13" t="n"/>
-      <c r="H35" s="13" t="n"/>
-      <c r="I35" s="13" t="n"/>
-      <c r="J35" s="13" t="n"/>
-      <c r="K35" s="13" t="n"/>
-      <c r="L35" s="13" t="n"/>
-      <c r="M35" s="13" t="n"/>
-      <c r="N35" s="13" t="n"/>
-      <c r="O35" s="13" t="n"/>
-      <c r="P35" s="13" t="n"/>
-      <c r="Q35" s="13" t="n"/>
-      <c r="R35" s="13" t="n"/>
-      <c r="S35" s="13" t="n"/>
-      <c r="T35" s="13" t="n"/>
-      <c r="U35" s="13" t="n"/>
-      <c r="V35" s="13" t="n"/>
-      <c r="W35" s="13" t="n"/>
-      <c r="X35" s="13" t="n"/>
-      <c r="Y35" s="13" t="n"/>
-      <c r="Z35" s="13" t="n"/>
-      <c r="AA35" s="13" t="n"/>
-      <c r="AB35" s="13" t="n"/>
-      <c r="AC35" s="13" t="n"/>
-      <c r="AD35" s="13" t="n"/>
-      <c r="AE35" s="13" t="n"/>
-      <c r="AF35" s="13" t="n"/>
-      <c r="AG35" s="13" t="n"/>
-      <c r="AH35" s="13" t="n"/>
-      <c r="AI35" s="13" t="n"/>
-    </row>
-    <row r="36" ht="14.5" customHeight="1">
-      <c r="A36" s="11" t="n">
-        <v>5</v>
+    <row r="33" ht="17" customHeight="1">
+      <c r="A33" s="15" t="inlineStr">
+        <is>
+          <t>CREW 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="13" customHeight="1">
+      <c r="E34" s="7">
+        <f>IF(1&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,1),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="F34" s="7">
+        <f>IF(2&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,2),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="G34" s="7">
+        <f>IF(3&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,3),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="H34" s="7">
+        <f>IF(4&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,4),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="I34" s="7">
+        <f>IF(5&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,5),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="J34" s="7">
+        <f>IF(6&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,6),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="K34" s="7">
+        <f>IF(7&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,7),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="L34" s="7">
+        <f>IF(8&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,8),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="M34" s="7">
+        <f>IF(9&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,9),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="N34" s="7">
+        <f>IF(10&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,10),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="O34" s="7">
+        <f>IF(11&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,11),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="P34" s="7">
+        <f>IF(12&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,12),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="Q34" s="7">
+        <f>IF(13&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,13),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="R34" s="7">
+        <f>IF(14&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,14),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="S34" s="7">
+        <f>IF(15&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,15),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="T34" s="7">
+        <f>IF(16&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,16),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="U34" s="7">
+        <f>IF(17&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,17),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="V34" s="7">
+        <f>IF(18&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,18),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="W34" s="7">
+        <f>IF(19&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,19),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="X34" s="7">
+        <f>IF(20&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,20),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="Y34" s="7">
+        <f>IF(21&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,21),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="Z34" s="7">
+        <f>IF(22&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,22),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="AA34" s="7">
+        <f>IF(23&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,23),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="AB34" s="7">
+        <f>IF(24&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,24),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="AC34" s="7">
+        <f>IF(25&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,25),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="AD34" s="7">
+        <f>IF(26&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,26),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="AE34" s="7">
+        <f>IF(27&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,27),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="AF34" s="7">
+        <f>IF(28&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,28),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="AG34" s="7">
+        <f>IF(29&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,29),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="AH34" s="7">
+        <f>IF(30&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,30),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="AI34" s="7">
+        <f>IF(31&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,31),"ddd"),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35" ht="16" customHeight="1">
+      <c r="A35" s="8" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B35" s="8" t="inlineStr">
+        <is>
+          <t>PRN</t>
+        </is>
+      </c>
+      <c r="C35" s="8" t="inlineStr">
+        <is>
+          <t>NAME</t>
+        </is>
+      </c>
+      <c r="D35" s="8" t="inlineStr">
+        <is>
+          <t>Posn</t>
+        </is>
+      </c>
+      <c r="E35" s="9">
+        <f>IF(1&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),1,"")</f>
+        <v/>
+      </c>
+      <c r="F35" s="9">
+        <f>IF(2&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),2,"")</f>
+        <v/>
+      </c>
+      <c r="G35" s="9">
+        <f>IF(3&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),3,"")</f>
+        <v/>
+      </c>
+      <c r="H35" s="9">
+        <f>IF(4&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),4,"")</f>
+        <v/>
+      </c>
+      <c r="I35" s="9">
+        <f>IF(5&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),5,"")</f>
+        <v/>
+      </c>
+      <c r="J35" s="9">
+        <f>IF(6&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),6,"")</f>
+        <v/>
+      </c>
+      <c r="K35" s="9">
+        <f>IF(7&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),7,"")</f>
+        <v/>
+      </c>
+      <c r="L35" s="9">
+        <f>IF(8&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),8,"")</f>
+        <v/>
+      </c>
+      <c r="M35" s="9">
+        <f>IF(9&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),9,"")</f>
+        <v/>
+      </c>
+      <c r="N35" s="9">
+        <f>IF(10&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),10,"")</f>
+        <v/>
+      </c>
+      <c r="O35" s="9">
+        <f>IF(11&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),11,"")</f>
+        <v/>
+      </c>
+      <c r="P35" s="9">
+        <f>IF(12&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),12,"")</f>
+        <v/>
+      </c>
+      <c r="Q35" s="9">
+        <f>IF(13&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),13,"")</f>
+        <v/>
+      </c>
+      <c r="R35" s="9">
+        <f>IF(14&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),14,"")</f>
+        <v/>
+      </c>
+      <c r="S35" s="9">
+        <f>IF(15&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),15,"")</f>
+        <v/>
+      </c>
+      <c r="T35" s="9">
+        <f>IF(16&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),16,"")</f>
+        <v/>
+      </c>
+      <c r="U35" s="9">
+        <f>IF(17&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),17,"")</f>
+        <v/>
+      </c>
+      <c r="V35" s="9">
+        <f>IF(18&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),18,"")</f>
+        <v/>
+      </c>
+      <c r="W35" s="9">
+        <f>IF(19&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),19,"")</f>
+        <v/>
+      </c>
+      <c r="X35" s="9">
+        <f>IF(20&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),20,"")</f>
+        <v/>
+      </c>
+      <c r="Y35" s="9">
+        <f>IF(21&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),21,"")</f>
+        <v/>
+      </c>
+      <c r="Z35" s="9">
+        <f>IF(22&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),22,"")</f>
+        <v/>
+      </c>
+      <c r="AA35" s="9">
+        <f>IF(23&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),23,"")</f>
+        <v/>
+      </c>
+      <c r="AB35" s="9">
+        <f>IF(24&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),24,"")</f>
+        <v/>
+      </c>
+      <c r="AC35" s="9">
+        <f>IF(25&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),25,"")</f>
+        <v/>
+      </c>
+      <c r="AD35" s="9">
+        <f>IF(26&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),26,"")</f>
+        <v/>
+      </c>
+      <c r="AE35" s="9">
+        <f>IF(27&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),27,"")</f>
+        <v/>
+      </c>
+      <c r="AF35" s="9">
+        <f>IF(28&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),28,"")</f>
+        <v/>
+      </c>
+      <c r="AG35" s="9">
+        <f>IF(29&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),29,"")</f>
+        <v/>
+      </c>
+      <c r="AH35" s="9">
+        <f>IF(30&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),30,"")</f>
+        <v/>
+      </c>
+      <c r="AI35" s="9">
+        <f>IF(31&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),31,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36" ht="17" customHeight="1">
+      <c r="A36" s="10">
+        <f>IF($C36="","",ROW()-35)</f>
+        <v/>
       </c>
       <c r="B36" s="11" t="n"/>
       <c r="C36" s="12" t="n"/>
@@ -2656,9 +2943,10 @@
       <c r="AH36" s="13" t="n"/>
       <c r="AI36" s="13" t="n"/>
     </row>
-    <row r="37" ht="14.5" customHeight="1">
-      <c r="A37" s="11" t="n">
-        <v>6</v>
+    <row r="37" ht="17" customHeight="1">
+      <c r="A37" s="10">
+        <f>IF($C37="","",ROW()-35)</f>
+        <v/>
       </c>
       <c r="B37" s="11" t="n"/>
       <c r="C37" s="12" t="n"/>
@@ -2695,9 +2983,10 @@
       <c r="AH37" s="13" t="n"/>
       <c r="AI37" s="13" t="n"/>
     </row>
-    <row r="38" ht="14.5" customHeight="1">
-      <c r="A38" s="11" t="n">
-        <v>7</v>
+    <row r="38" ht="17" customHeight="1">
+      <c r="A38" s="10">
+        <f>IF($C38="","",ROW()-35)</f>
+        <v/>
       </c>
       <c r="B38" s="11" t="n"/>
       <c r="C38" s="12" t="n"/>
@@ -2734,9 +3023,10 @@
       <c r="AH38" s="13" t="n"/>
       <c r="AI38" s="13" t="n"/>
     </row>
-    <row r="39" ht="14.5" customHeight="1">
-      <c r="A39" s="11" t="n">
-        <v>8</v>
+    <row r="39" ht="17" customHeight="1">
+      <c r="A39" s="10">
+        <f>IF($C39="","",ROW()-35)</f>
+        <v/>
       </c>
       <c r="B39" s="11" t="n"/>
       <c r="C39" s="12" t="n"/>
@@ -2773,9 +3063,10 @@
       <c r="AH39" s="13" t="n"/>
       <c r="AI39" s="13" t="n"/>
     </row>
-    <row r="40" ht="14.5" customHeight="1">
-      <c r="A40" s="11" t="n">
-        <v>9</v>
+    <row r="40" ht="17" customHeight="1">
+      <c r="A40" s="10">
+        <f>IF($C40="","",ROW()-35)</f>
+        <v/>
       </c>
       <c r="B40" s="11" t="n"/>
       <c r="C40" s="12" t="n"/>
@@ -2812,9 +3103,10 @@
       <c r="AH40" s="13" t="n"/>
       <c r="AI40" s="13" t="n"/>
     </row>
-    <row r="41" ht="14.5" customHeight="1">
-      <c r="A41" s="11" t="n">
-        <v>10</v>
+    <row r="41" ht="17" customHeight="1">
+      <c r="A41" s="10">
+        <f>IF($C41="","",ROW()-35)</f>
+        <v/>
       </c>
       <c r="B41" s="11" t="n"/>
       <c r="C41" s="12" t="n"/>
@@ -2851,9 +3143,10 @@
       <c r="AH41" s="13" t="n"/>
       <c r="AI41" s="13" t="n"/>
     </row>
-    <row r="42" ht="14.5" customHeight="1">
-      <c r="A42" s="11" t="n">
-        <v>11</v>
+    <row r="42" ht="17" customHeight="1">
+      <c r="A42" s="10">
+        <f>IF($C42="","",ROW()-35)</f>
+        <v/>
       </c>
       <c r="B42" s="11" t="n"/>
       <c r="C42" s="12" t="n"/>
@@ -2890,9 +3183,10 @@
       <c r="AH42" s="13" t="n"/>
       <c r="AI42" s="13" t="n"/>
     </row>
-    <row r="43" ht="14.5" customHeight="1">
-      <c r="A43" s="11" t="n">
-        <v>12</v>
+    <row r="43" ht="17" customHeight="1">
+      <c r="A43" s="10">
+        <f>IF($C43="","",ROW()-35)</f>
+        <v/>
       </c>
       <c r="B43" s="11" t="n"/>
       <c r="C43" s="12" t="n"/>
@@ -2929,47 +3223,50 @@
       <c r="AH43" s="13" t="n"/>
       <c r="AI43" s="13" t="n"/>
     </row>
-    <row r="44" ht="15" customHeight="1">
-      <c r="A44" s="18" t="inlineStr">
-        <is>
-          <t>SPECIAL SHIFTING</t>
-        </is>
-      </c>
-      <c r="E44" s="19" t="n"/>
-      <c r="F44" s="19" t="n"/>
-      <c r="G44" s="19" t="n"/>
-      <c r="H44" s="19" t="n"/>
-      <c r="I44" s="19" t="n"/>
-      <c r="J44" s="19" t="n"/>
-      <c r="K44" s="19" t="n"/>
-      <c r="L44" s="19" t="n"/>
-      <c r="M44" s="19" t="n"/>
-      <c r="N44" s="19" t="n"/>
-      <c r="O44" s="19" t="n"/>
-      <c r="P44" s="19" t="n"/>
-      <c r="Q44" s="19" t="n"/>
-      <c r="R44" s="19" t="n"/>
-      <c r="S44" s="19" t="n"/>
-      <c r="T44" s="19" t="n"/>
-      <c r="U44" s="19" t="n"/>
-      <c r="V44" s="19" t="n"/>
-      <c r="W44" s="19" t="n"/>
-      <c r="X44" s="19" t="n"/>
-      <c r="Y44" s="19" t="n"/>
-      <c r="Z44" s="19" t="n"/>
-      <c r="AA44" s="19" t="n"/>
-      <c r="AB44" s="19" t="n"/>
-      <c r="AC44" s="19" t="n"/>
-      <c r="AD44" s="19" t="n"/>
-      <c r="AE44" s="19" t="n"/>
-      <c r="AF44" s="19" t="n"/>
-      <c r="AG44" s="19" t="n"/>
-      <c r="AH44" s="19" t="n"/>
-      <c r="AI44" s="19" t="n"/>
-    </row>
-    <row r="45" ht="14.5" customHeight="1">
-      <c r="A45" s="11" t="n">
-        <v>1</v>
+    <row r="44" ht="17" customHeight="1">
+      <c r="A44" s="10">
+        <f>IF($C44="","",ROW()-35)</f>
+        <v/>
+      </c>
+      <c r="B44" s="11" t="n"/>
+      <c r="C44" s="12" t="n"/>
+      <c r="D44" s="11" t="n"/>
+      <c r="E44" s="13" t="n"/>
+      <c r="F44" s="13" t="n"/>
+      <c r="G44" s="13" t="n"/>
+      <c r="H44" s="13" t="n"/>
+      <c r="I44" s="13" t="n"/>
+      <c r="J44" s="13" t="n"/>
+      <c r="K44" s="13" t="n"/>
+      <c r="L44" s="13" t="n"/>
+      <c r="M44" s="13" t="n"/>
+      <c r="N44" s="13" t="n"/>
+      <c r="O44" s="13" t="n"/>
+      <c r="P44" s="13" t="n"/>
+      <c r="Q44" s="13" t="n"/>
+      <c r="R44" s="13" t="n"/>
+      <c r="S44" s="13" t="n"/>
+      <c r="T44" s="13" t="n"/>
+      <c r="U44" s="13" t="n"/>
+      <c r="V44" s="13" t="n"/>
+      <c r="W44" s="13" t="n"/>
+      <c r="X44" s="13" t="n"/>
+      <c r="Y44" s="13" t="n"/>
+      <c r="Z44" s="13" t="n"/>
+      <c r="AA44" s="13" t="n"/>
+      <c r="AB44" s="13" t="n"/>
+      <c r="AC44" s="13" t="n"/>
+      <c r="AD44" s="13" t="n"/>
+      <c r="AE44" s="13" t="n"/>
+      <c r="AF44" s="13" t="n"/>
+      <c r="AG44" s="13" t="n"/>
+      <c r="AH44" s="13" t="n"/>
+      <c r="AI44" s="13" t="n"/>
+    </row>
+    <row r="45" ht="17" customHeight="1">
+      <c r="A45" s="10">
+        <f>IF($C45="","",ROW()-35)</f>
+        <v/>
       </c>
       <c r="B45" s="11" t="n"/>
       <c r="C45" s="12" t="n"/>
@@ -3006,9 +3303,10 @@
       <c r="AH45" s="13" t="n"/>
       <c r="AI45" s="13" t="n"/>
     </row>
-    <row r="46" ht="14.5" customHeight="1">
-      <c r="A46" s="11" t="n">
-        <v>2</v>
+    <row r="46" ht="17" customHeight="1">
+      <c r="A46" s="10">
+        <f>IF($C46="","",ROW()-35)</f>
+        <v/>
       </c>
       <c r="B46" s="11" t="n"/>
       <c r="C46" s="12" t="n"/>
@@ -3045,9 +3343,10 @@
       <c r="AH46" s="13" t="n"/>
       <c r="AI46" s="13" t="n"/>
     </row>
-    <row r="47" ht="14.5" customHeight="1">
-      <c r="A47" s="11" t="n">
-        <v>3</v>
+    <row r="47" ht="17" customHeight="1">
+      <c r="A47" s="10">
+        <f>IF($C47="","",ROW()-35)</f>
+        <v/>
       </c>
       <c r="B47" s="11" t="n"/>
       <c r="C47" s="12" t="n"/>
@@ -3084,1001 +3383,2292 @@
       <c r="AH47" s="13" t="n"/>
       <c r="AI47" s="13" t="n"/>
     </row>
-    <row r="48" ht="14.5" customHeight="1">
-      <c r="A48" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="B48" s="11" t="n"/>
-      <c r="C48" s="12" t="n"/>
-      <c r="D48" s="11" t="n"/>
-      <c r="E48" s="13" t="n"/>
-      <c r="F48" s="13" t="n"/>
-      <c r="G48" s="13" t="n"/>
-      <c r="H48" s="13" t="n"/>
-      <c r="I48" s="13" t="n"/>
-      <c r="J48" s="13" t="n"/>
-      <c r="K48" s="13" t="n"/>
-      <c r="L48" s="13" t="n"/>
-      <c r="M48" s="13" t="n"/>
-      <c r="N48" s="13" t="n"/>
-      <c r="O48" s="13" t="n"/>
-      <c r="P48" s="13" t="n"/>
-      <c r="Q48" s="13" t="n"/>
-      <c r="R48" s="13" t="n"/>
-      <c r="S48" s="13" t="n"/>
-      <c r="T48" s="13" t="n"/>
-      <c r="U48" s="13" t="n"/>
-      <c r="V48" s="13" t="n"/>
-      <c r="W48" s="13" t="n"/>
-      <c r="X48" s="13" t="n"/>
-      <c r="Y48" s="13" t="n"/>
-      <c r="Z48" s="13" t="n"/>
-      <c r="AA48" s="13" t="n"/>
-      <c r="AB48" s="13" t="n"/>
-      <c r="AC48" s="13" t="n"/>
-      <c r="AD48" s="13" t="n"/>
-      <c r="AE48" s="13" t="n"/>
-      <c r="AF48" s="13" t="n"/>
-      <c r="AG48" s="13" t="n"/>
-      <c r="AH48" s="13" t="n"/>
-      <c r="AI48" s="13" t="n"/>
-    </row>
-    <row r="49" ht="14.5" customHeight="1">
-      <c r="A49" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="B49" s="11" t="n"/>
-      <c r="C49" s="12" t="n"/>
-      <c r="D49" s="11" t="n"/>
-      <c r="E49" s="13" t="n"/>
-      <c r="F49" s="13" t="n"/>
-      <c r="G49" s="13" t="n"/>
-      <c r="H49" s="13" t="n"/>
-      <c r="I49" s="13" t="n"/>
-      <c r="J49" s="13" t="n"/>
-      <c r="K49" s="13" t="n"/>
-      <c r="L49" s="13" t="n"/>
-      <c r="M49" s="13" t="n"/>
-      <c r="N49" s="13" t="n"/>
-      <c r="O49" s="13" t="n"/>
-      <c r="P49" s="13" t="n"/>
-      <c r="Q49" s="13" t="n"/>
-      <c r="R49" s="13" t="n"/>
-      <c r="S49" s="13" t="n"/>
-      <c r="T49" s="13" t="n"/>
-      <c r="U49" s="13" t="n"/>
-      <c r="V49" s="13" t="n"/>
-      <c r="W49" s="13" t="n"/>
-      <c r="X49" s="13" t="n"/>
-      <c r="Y49" s="13" t="n"/>
-      <c r="Z49" s="13" t="n"/>
-      <c r="AA49" s="13" t="n"/>
-      <c r="AB49" s="13" t="n"/>
-      <c r="AC49" s="13" t="n"/>
-      <c r="AD49" s="13" t="n"/>
-      <c r="AE49" s="13" t="n"/>
-      <c r="AF49" s="13" t="n"/>
-      <c r="AG49" s="13" t="n"/>
-      <c r="AH49" s="13" t="n"/>
-      <c r="AI49" s="13" t="n"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="20" t="inlineStr">
+    <row r="48" ht="17" customHeight="1">
+      <c r="A48" s="16" t="inlineStr">
+        <is>
+          <t>SPECIAL SHIFTING</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="13" customHeight="1">
+      <c r="E49" s="7">
+        <f>IF(1&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,1),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="F49" s="7">
+        <f>IF(2&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,2),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="G49" s="7">
+        <f>IF(3&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,3),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="H49" s="7">
+        <f>IF(4&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,4),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="I49" s="7">
+        <f>IF(5&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,5),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="J49" s="7">
+        <f>IF(6&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,6),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="K49" s="7">
+        <f>IF(7&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,7),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="L49" s="7">
+        <f>IF(8&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,8),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="M49" s="7">
+        <f>IF(9&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,9),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="N49" s="7">
+        <f>IF(10&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,10),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="O49" s="7">
+        <f>IF(11&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,11),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="P49" s="7">
+        <f>IF(12&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,12),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="Q49" s="7">
+        <f>IF(13&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,13),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="R49" s="7">
+        <f>IF(14&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,14),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="S49" s="7">
+        <f>IF(15&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,15),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="T49" s="7">
+        <f>IF(16&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,16),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="U49" s="7">
+        <f>IF(17&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,17),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="V49" s="7">
+        <f>IF(18&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,18),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="W49" s="7">
+        <f>IF(19&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,19),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="X49" s="7">
+        <f>IF(20&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,20),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="Y49" s="7">
+        <f>IF(21&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,21),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="Z49" s="7">
+        <f>IF(22&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,22),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="AA49" s="7">
+        <f>IF(23&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,23),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="AB49" s="7">
+        <f>IF(24&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,24),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="AC49" s="7">
+        <f>IF(25&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,25),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="AD49" s="7">
+        <f>IF(26&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,26),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="AE49" s="7">
+        <f>IF(27&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,27),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="AF49" s="7">
+        <f>IF(28&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,28),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="AG49" s="7">
+        <f>IF(29&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,29),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="AH49" s="7">
+        <f>IF(30&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,30),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="AI49" s="7">
+        <f>IF(31&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,31),"ddd"),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50" ht="16" customHeight="1">
+      <c r="A50" s="8" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B50" s="8" t="inlineStr">
+        <is>
+          <t>PRN</t>
+        </is>
+      </c>
+      <c r="C50" s="8" t="inlineStr">
+        <is>
+          <t>NAME</t>
+        </is>
+      </c>
+      <c r="D50" s="8" t="inlineStr">
+        <is>
+          <t>Posn</t>
+        </is>
+      </c>
+      <c r="E50" s="9">
+        <f>IF(1&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),1,"")</f>
+        <v/>
+      </c>
+      <c r="F50" s="9">
+        <f>IF(2&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),2,"")</f>
+        <v/>
+      </c>
+      <c r="G50" s="9">
+        <f>IF(3&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),3,"")</f>
+        <v/>
+      </c>
+      <c r="H50" s="9">
+        <f>IF(4&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),4,"")</f>
+        <v/>
+      </c>
+      <c r="I50" s="9">
+        <f>IF(5&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),5,"")</f>
+        <v/>
+      </c>
+      <c r="J50" s="9">
+        <f>IF(6&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),6,"")</f>
+        <v/>
+      </c>
+      <c r="K50" s="9">
+        <f>IF(7&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),7,"")</f>
+        <v/>
+      </c>
+      <c r="L50" s="9">
+        <f>IF(8&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),8,"")</f>
+        <v/>
+      </c>
+      <c r="M50" s="9">
+        <f>IF(9&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),9,"")</f>
+        <v/>
+      </c>
+      <c r="N50" s="9">
+        <f>IF(10&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),10,"")</f>
+        <v/>
+      </c>
+      <c r="O50" s="9">
+        <f>IF(11&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),11,"")</f>
+        <v/>
+      </c>
+      <c r="P50" s="9">
+        <f>IF(12&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),12,"")</f>
+        <v/>
+      </c>
+      <c r="Q50" s="9">
+        <f>IF(13&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),13,"")</f>
+        <v/>
+      </c>
+      <c r="R50" s="9">
+        <f>IF(14&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),14,"")</f>
+        <v/>
+      </c>
+      <c r="S50" s="9">
+        <f>IF(15&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),15,"")</f>
+        <v/>
+      </c>
+      <c r="T50" s="9">
+        <f>IF(16&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),16,"")</f>
+        <v/>
+      </c>
+      <c r="U50" s="9">
+        <f>IF(17&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),17,"")</f>
+        <v/>
+      </c>
+      <c r="V50" s="9">
+        <f>IF(18&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),18,"")</f>
+        <v/>
+      </c>
+      <c r="W50" s="9">
+        <f>IF(19&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),19,"")</f>
+        <v/>
+      </c>
+      <c r="X50" s="9">
+        <f>IF(20&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),20,"")</f>
+        <v/>
+      </c>
+      <c r="Y50" s="9">
+        <f>IF(21&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),21,"")</f>
+        <v/>
+      </c>
+      <c r="Z50" s="9">
+        <f>IF(22&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),22,"")</f>
+        <v/>
+      </c>
+      <c r="AA50" s="9">
+        <f>IF(23&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),23,"")</f>
+        <v/>
+      </c>
+      <c r="AB50" s="9">
+        <f>IF(24&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),24,"")</f>
+        <v/>
+      </c>
+      <c r="AC50" s="9">
+        <f>IF(25&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),25,"")</f>
+        <v/>
+      </c>
+      <c r="AD50" s="9">
+        <f>IF(26&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),26,"")</f>
+        <v/>
+      </c>
+      <c r="AE50" s="9">
+        <f>IF(27&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),27,"")</f>
+        <v/>
+      </c>
+      <c r="AF50" s="9">
+        <f>IF(28&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),28,"")</f>
+        <v/>
+      </c>
+      <c r="AG50" s="9">
+        <f>IF(29&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),29,"")</f>
+        <v/>
+      </c>
+      <c r="AH50" s="9">
+        <f>IF(30&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),30,"")</f>
+        <v/>
+      </c>
+      <c r="AI50" s="9">
+        <f>IF(31&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),31,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51" ht="17" customHeight="1">
+      <c r="A51" s="10">
+        <f>IF($C51="","",ROW()-50)</f>
+        <v/>
+      </c>
+      <c r="B51" s="11" t="n"/>
+      <c r="C51" s="12" t="n"/>
+      <c r="D51" s="11" t="n"/>
+      <c r="E51" s="13" t="n"/>
+      <c r="F51" s="13" t="n"/>
+      <c r="G51" s="13" t="n"/>
+      <c r="H51" s="13" t="n"/>
+      <c r="I51" s="13" t="n"/>
+      <c r="J51" s="13" t="n"/>
+      <c r="K51" s="13" t="n"/>
+      <c r="L51" s="13" t="n"/>
+      <c r="M51" s="13" t="n"/>
+      <c r="N51" s="13" t="n"/>
+      <c r="O51" s="13" t="n"/>
+      <c r="P51" s="13" t="n"/>
+      <c r="Q51" s="13" t="n"/>
+      <c r="R51" s="13" t="n"/>
+      <c r="S51" s="13" t="n"/>
+      <c r="T51" s="13" t="n"/>
+      <c r="U51" s="13" t="n"/>
+      <c r="V51" s="13" t="n"/>
+      <c r="W51" s="13" t="n"/>
+      <c r="X51" s="13" t="n"/>
+      <c r="Y51" s="13" t="n"/>
+      <c r="Z51" s="13" t="n"/>
+      <c r="AA51" s="13" t="n"/>
+      <c r="AB51" s="13" t="n"/>
+      <c r="AC51" s="13" t="n"/>
+      <c r="AD51" s="13" t="n"/>
+      <c r="AE51" s="13" t="n"/>
+      <c r="AF51" s="13" t="n"/>
+      <c r="AG51" s="13" t="n"/>
+      <c r="AH51" s="13" t="n"/>
+      <c r="AI51" s="13" t="n"/>
+    </row>
+    <row r="52" ht="17" customHeight="1">
+      <c r="A52" s="10">
+        <f>IF($C52="","",ROW()-50)</f>
+        <v/>
+      </c>
+      <c r="B52" s="11" t="n"/>
+      <c r="C52" s="12" t="n"/>
+      <c r="D52" s="11" t="n"/>
+      <c r="E52" s="13" t="n"/>
+      <c r="F52" s="13" t="n"/>
+      <c r="G52" s="13" t="n"/>
+      <c r="H52" s="13" t="n"/>
+      <c r="I52" s="13" t="n"/>
+      <c r="J52" s="13" t="n"/>
+      <c r="K52" s="13" t="n"/>
+      <c r="L52" s="13" t="n"/>
+      <c r="M52" s="13" t="n"/>
+      <c r="N52" s="13" t="n"/>
+      <c r="O52" s="13" t="n"/>
+      <c r="P52" s="13" t="n"/>
+      <c r="Q52" s="13" t="n"/>
+      <c r="R52" s="13" t="n"/>
+      <c r="S52" s="13" t="n"/>
+      <c r="T52" s="13" t="n"/>
+      <c r="U52" s="13" t="n"/>
+      <c r="V52" s="13" t="n"/>
+      <c r="W52" s="13" t="n"/>
+      <c r="X52" s="13" t="n"/>
+      <c r="Y52" s="13" t="n"/>
+      <c r="Z52" s="13" t="n"/>
+      <c r="AA52" s="13" t="n"/>
+      <c r="AB52" s="13" t="n"/>
+      <c r="AC52" s="13" t="n"/>
+      <c r="AD52" s="13" t="n"/>
+      <c r="AE52" s="13" t="n"/>
+      <c r="AF52" s="13" t="n"/>
+      <c r="AG52" s="13" t="n"/>
+      <c r="AH52" s="13" t="n"/>
+      <c r="AI52" s="13" t="n"/>
+    </row>
+    <row r="53" ht="17" customHeight="1">
+      <c r="A53" s="10">
+        <f>IF($C53="","",ROW()-50)</f>
+        <v/>
+      </c>
+      <c r="B53" s="11" t="n"/>
+      <c r="C53" s="12" t="n"/>
+      <c r="D53" s="11" t="n"/>
+      <c r="E53" s="13" t="n"/>
+      <c r="F53" s="13" t="n"/>
+      <c r="G53" s="13" t="n"/>
+      <c r="H53" s="13" t="n"/>
+      <c r="I53" s="13" t="n"/>
+      <c r="J53" s="13" t="n"/>
+      <c r="K53" s="13" t="n"/>
+      <c r="L53" s="13" t="n"/>
+      <c r="M53" s="13" t="n"/>
+      <c r="N53" s="13" t="n"/>
+      <c r="O53" s="13" t="n"/>
+      <c r="P53" s="13" t="n"/>
+      <c r="Q53" s="13" t="n"/>
+      <c r="R53" s="13" t="n"/>
+      <c r="S53" s="13" t="n"/>
+      <c r="T53" s="13" t="n"/>
+      <c r="U53" s="13" t="n"/>
+      <c r="V53" s="13" t="n"/>
+      <c r="W53" s="13" t="n"/>
+      <c r="X53" s="13" t="n"/>
+      <c r="Y53" s="13" t="n"/>
+      <c r="Z53" s="13" t="n"/>
+      <c r="AA53" s="13" t="n"/>
+      <c r="AB53" s="13" t="n"/>
+      <c r="AC53" s="13" t="n"/>
+      <c r="AD53" s="13" t="n"/>
+      <c r="AE53" s="13" t="n"/>
+      <c r="AF53" s="13" t="n"/>
+      <c r="AG53" s="13" t="n"/>
+      <c r="AH53" s="13" t="n"/>
+      <c r="AI53" s="13" t="n"/>
+    </row>
+    <row r="54" ht="17" customHeight="1">
+      <c r="A54" s="10">
+        <f>IF($C54="","",ROW()-50)</f>
+        <v/>
+      </c>
+      <c r="B54" s="11" t="n"/>
+      <c r="C54" s="12" t="n"/>
+      <c r="D54" s="11" t="n"/>
+      <c r="E54" s="13" t="n"/>
+      <c r="F54" s="13" t="n"/>
+      <c r="G54" s="13" t="n"/>
+      <c r="H54" s="13" t="n"/>
+      <c r="I54" s="13" t="n"/>
+      <c r="J54" s="13" t="n"/>
+      <c r="K54" s="13" t="n"/>
+      <c r="L54" s="13" t="n"/>
+      <c r="M54" s="13" t="n"/>
+      <c r="N54" s="13" t="n"/>
+      <c r="O54" s="13" t="n"/>
+      <c r="P54" s="13" t="n"/>
+      <c r="Q54" s="13" t="n"/>
+      <c r="R54" s="13" t="n"/>
+      <c r="S54" s="13" t="n"/>
+      <c r="T54" s="13" t="n"/>
+      <c r="U54" s="13" t="n"/>
+      <c r="V54" s="13" t="n"/>
+      <c r="W54" s="13" t="n"/>
+      <c r="X54" s="13" t="n"/>
+      <c r="Y54" s="13" t="n"/>
+      <c r="Z54" s="13" t="n"/>
+      <c r="AA54" s="13" t="n"/>
+      <c r="AB54" s="13" t="n"/>
+      <c r="AC54" s="13" t="n"/>
+      <c r="AD54" s="13" t="n"/>
+      <c r="AE54" s="13" t="n"/>
+      <c r="AF54" s="13" t="n"/>
+      <c r="AG54" s="13" t="n"/>
+      <c r="AH54" s="13" t="n"/>
+      <c r="AI54" s="13" t="n"/>
+    </row>
+    <row r="55" ht="17" customHeight="1">
+      <c r="A55" s="10">
+        <f>IF($C55="","",ROW()-50)</f>
+        <v/>
+      </c>
+      <c r="B55" s="11" t="n"/>
+      <c r="C55" s="12" t="n"/>
+      <c r="D55" s="11" t="n"/>
+      <c r="E55" s="13" t="n"/>
+      <c r="F55" s="13" t="n"/>
+      <c r="G55" s="13" t="n"/>
+      <c r="H55" s="13" t="n"/>
+      <c r="I55" s="13" t="n"/>
+      <c r="J55" s="13" t="n"/>
+      <c r="K55" s="13" t="n"/>
+      <c r="L55" s="13" t="n"/>
+      <c r="M55" s="13" t="n"/>
+      <c r="N55" s="13" t="n"/>
+      <c r="O55" s="13" t="n"/>
+      <c r="P55" s="13" t="n"/>
+      <c r="Q55" s="13" t="n"/>
+      <c r="R55" s="13" t="n"/>
+      <c r="S55" s="13" t="n"/>
+      <c r="T55" s="13" t="n"/>
+      <c r="U55" s="13" t="n"/>
+      <c r="V55" s="13" t="n"/>
+      <c r="W55" s="13" t="n"/>
+      <c r="X55" s="13" t="n"/>
+      <c r="Y55" s="13" t="n"/>
+      <c r="Z55" s="13" t="n"/>
+      <c r="AA55" s="13" t="n"/>
+      <c r="AB55" s="13" t="n"/>
+      <c r="AC55" s="13" t="n"/>
+      <c r="AD55" s="13" t="n"/>
+      <c r="AE55" s="13" t="n"/>
+      <c r="AF55" s="13" t="n"/>
+      <c r="AG55" s="13" t="n"/>
+      <c r="AH55" s="13" t="n"/>
+      <c r="AI55" s="13" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="17" t="inlineStr">
         <is>
           <t>TOTAL DAILY
 CREWS MANPOWER</t>
         </is>
       </c>
-      <c r="B51" s="43" t="n"/>
-      <c r="C51" s="44" t="n"/>
-      <c r="D51" s="8" t="inlineStr">
+      <c r="B57" s="18" t="n"/>
+      <c r="C57" s="18" t="n"/>
+      <c r="D57" s="8" t="inlineStr">
         <is>
           <t>SHIFT</t>
         </is>
       </c>
-      <c r="E51" s="7">
-        <f>E3</f>
-        <v/>
-      </c>
-      <c r="F51" s="7">
-        <f>F3</f>
-        <v/>
-      </c>
-      <c r="G51" s="7">
-        <f>G3</f>
-        <v/>
-      </c>
-      <c r="H51" s="7">
-        <f>H3</f>
-        <v/>
-      </c>
-      <c r="I51" s="7">
-        <f>I3</f>
-        <v/>
-      </c>
-      <c r="J51" s="7">
-        <f>J3</f>
-        <v/>
-      </c>
-      <c r="K51" s="7">
-        <f>K3</f>
-        <v/>
-      </c>
-      <c r="L51" s="7">
-        <f>L3</f>
-        <v/>
-      </c>
-      <c r="M51" s="7">
-        <f>M3</f>
-        <v/>
-      </c>
-      <c r="N51" s="7">
-        <f>N3</f>
-        <v/>
-      </c>
-      <c r="O51" s="7">
-        <f>O3</f>
-        <v/>
-      </c>
-      <c r="P51" s="7">
-        <f>P3</f>
-        <v/>
-      </c>
-      <c r="Q51" s="7">
-        <f>Q3</f>
-        <v/>
-      </c>
-      <c r="R51" s="7">
-        <f>R3</f>
-        <v/>
-      </c>
-      <c r="S51" s="7">
-        <f>S3</f>
-        <v/>
-      </c>
-      <c r="T51" s="7">
-        <f>T3</f>
-        <v/>
-      </c>
-      <c r="U51" s="7">
-        <f>U3</f>
-        <v/>
-      </c>
-      <c r="V51" s="7">
-        <f>V3</f>
-        <v/>
-      </c>
-      <c r="W51" s="7">
-        <f>W3</f>
-        <v/>
-      </c>
-      <c r="X51" s="7">
-        <f>X3</f>
-        <v/>
-      </c>
-      <c r="Y51" s="7">
-        <f>Y3</f>
-        <v/>
-      </c>
-      <c r="Z51" s="7">
-        <f>Z3</f>
-        <v/>
-      </c>
-      <c r="AA51" s="7">
-        <f>AA3</f>
-        <v/>
-      </c>
-      <c r="AB51" s="7">
-        <f>AB3</f>
-        <v/>
-      </c>
-      <c r="AC51" s="7">
-        <f>AC3</f>
-        <v/>
-      </c>
-      <c r="AD51" s="7">
-        <f>AD3</f>
-        <v/>
-      </c>
-      <c r="AE51" s="7">
-        <f>AE3</f>
-        <v/>
-      </c>
-      <c r="AF51" s="7">
-        <f>AF3</f>
-        <v/>
-      </c>
-      <c r="AG51" s="7">
-        <f>AG3</f>
-        <v/>
-      </c>
-      <c r="AH51" s="7">
-        <f>AH3</f>
-        <v/>
-      </c>
-      <c r="AI51" s="7">
-        <f>AI3</f>
-        <v/>
-      </c>
-    </row>
-    <row r="52" ht="13.5" customHeight="1">
-      <c r="A52" s="45" t="n"/>
-      <c r="C52" s="46" t="n"/>
-      <c r="D52" s="22" t="inlineStr">
+      <c r="E57" s="7">
+        <f>E5</f>
+        <v/>
+      </c>
+      <c r="F57" s="7">
+        <f>F5</f>
+        <v/>
+      </c>
+      <c r="G57" s="7">
+        <f>G5</f>
+        <v/>
+      </c>
+      <c r="H57" s="7">
+        <f>H5</f>
+        <v/>
+      </c>
+      <c r="I57" s="7">
+        <f>I5</f>
+        <v/>
+      </c>
+      <c r="J57" s="7">
+        <f>J5</f>
+        <v/>
+      </c>
+      <c r="K57" s="7">
+        <f>K5</f>
+        <v/>
+      </c>
+      <c r="L57" s="7">
+        <f>L5</f>
+        <v/>
+      </c>
+      <c r="M57" s="7">
+        <f>M5</f>
+        <v/>
+      </c>
+      <c r="N57" s="7">
+        <f>N5</f>
+        <v/>
+      </c>
+      <c r="O57" s="7">
+        <f>O5</f>
+        <v/>
+      </c>
+      <c r="P57" s="7">
+        <f>P5</f>
+        <v/>
+      </c>
+      <c r="Q57" s="7">
+        <f>Q5</f>
+        <v/>
+      </c>
+      <c r="R57" s="7">
+        <f>R5</f>
+        <v/>
+      </c>
+      <c r="S57" s="7">
+        <f>S5</f>
+        <v/>
+      </c>
+      <c r="T57" s="7">
+        <f>T5</f>
+        <v/>
+      </c>
+      <c r="U57" s="7">
+        <f>U5</f>
+        <v/>
+      </c>
+      <c r="V57" s="7">
+        <f>V5</f>
+        <v/>
+      </c>
+      <c r="W57" s="7">
+        <f>W5</f>
+        <v/>
+      </c>
+      <c r="X57" s="7">
+        <f>X5</f>
+        <v/>
+      </c>
+      <c r="Y57" s="7">
+        <f>Y5</f>
+        <v/>
+      </c>
+      <c r="Z57" s="7">
+        <f>Z5</f>
+        <v/>
+      </c>
+      <c r="AA57" s="7">
+        <f>AA5</f>
+        <v/>
+      </c>
+      <c r="AB57" s="7">
+        <f>AB5</f>
+        <v/>
+      </c>
+      <c r="AC57" s="7">
+        <f>AC5</f>
+        <v/>
+      </c>
+      <c r="AD57" s="7">
+        <f>AD5</f>
+        <v/>
+      </c>
+      <c r="AE57" s="7">
+        <f>AE5</f>
+        <v/>
+      </c>
+      <c r="AF57" s="7">
+        <f>AF5</f>
+        <v/>
+      </c>
+      <c r="AG57" s="7">
+        <f>AG5</f>
+        <v/>
+      </c>
+      <c r="AH57" s="7">
+        <f>AH5</f>
+        <v/>
+      </c>
+      <c r="AI57" s="7">
+        <f>AI5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58" ht="15" customHeight="1">
+      <c r="A58" s="18" t="n"/>
+      <c r="B58" s="18" t="n"/>
+      <c r="C58" s="18" t="n"/>
+      <c r="D58" s="19" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="E52" s="11">
-        <f>IF(E$4="","",COUNTIF(E6:E49,"D"))</f>
-        <v/>
-      </c>
-      <c r="F52" s="11">
-        <f>IF(F$4="","",COUNTIF(F6:F49,"D"))</f>
-        <v/>
-      </c>
-      <c r="G52" s="11">
-        <f>IF(G$4="","",COUNTIF(G6:G49,"D"))</f>
-        <v/>
-      </c>
-      <c r="H52" s="11">
-        <f>IF(H$4="","",COUNTIF(H6:H49,"D"))</f>
-        <v/>
-      </c>
-      <c r="I52" s="11">
-        <f>IF(I$4="","",COUNTIF(I6:I49,"D"))</f>
-        <v/>
-      </c>
-      <c r="J52" s="11">
-        <f>IF(J$4="","",COUNTIF(J6:J49,"D"))</f>
-        <v/>
-      </c>
-      <c r="K52" s="11">
-        <f>IF(K$4="","",COUNTIF(K6:K49,"D"))</f>
-        <v/>
-      </c>
-      <c r="L52" s="11">
-        <f>IF(L$4="","",COUNTIF(L6:L49,"D"))</f>
-        <v/>
-      </c>
-      <c r="M52" s="11">
-        <f>IF(M$4="","",COUNTIF(M6:M49,"D"))</f>
-        <v/>
-      </c>
-      <c r="N52" s="11">
-        <f>IF(N$4="","",COUNTIF(N6:N49,"D"))</f>
-        <v/>
-      </c>
-      <c r="O52" s="11">
-        <f>IF(O$4="","",COUNTIF(O6:O49,"D"))</f>
-        <v/>
-      </c>
-      <c r="P52" s="11">
-        <f>IF(P$4="","",COUNTIF(P6:P49,"D"))</f>
-        <v/>
-      </c>
-      <c r="Q52" s="11">
-        <f>IF(Q$4="","",COUNTIF(Q6:Q49,"D"))</f>
-        <v/>
-      </c>
-      <c r="R52" s="11">
-        <f>IF(R$4="","",COUNTIF(R6:R49,"D"))</f>
-        <v/>
-      </c>
-      <c r="S52" s="11">
-        <f>IF(S$4="","",COUNTIF(S6:S49,"D"))</f>
-        <v/>
-      </c>
-      <c r="T52" s="11">
-        <f>IF(T$4="","",COUNTIF(T6:T49,"D"))</f>
-        <v/>
-      </c>
-      <c r="U52" s="11">
-        <f>IF(U$4="","",COUNTIF(U6:U49,"D"))</f>
-        <v/>
-      </c>
-      <c r="V52" s="11">
-        <f>IF(V$4="","",COUNTIF(V6:V49,"D"))</f>
-        <v/>
-      </c>
-      <c r="W52" s="11">
-        <f>IF(W$4="","",COUNTIF(W6:W49,"D"))</f>
-        <v/>
-      </c>
-      <c r="X52" s="11">
-        <f>IF(X$4="","",COUNTIF(X6:X49,"D"))</f>
-        <v/>
-      </c>
-      <c r="Y52" s="11">
-        <f>IF(Y$4="","",COUNTIF(Y6:Y49,"D"))</f>
-        <v/>
-      </c>
-      <c r="Z52" s="11">
-        <f>IF(Z$4="","",COUNTIF(Z6:Z49,"D"))</f>
-        <v/>
-      </c>
-      <c r="AA52" s="11">
-        <f>IF(AA$4="","",COUNTIF(AA6:AA49,"D"))</f>
-        <v/>
-      </c>
-      <c r="AB52" s="11">
-        <f>IF(AB$4="","",COUNTIF(AB6:AB49,"D"))</f>
-        <v/>
-      </c>
-      <c r="AC52" s="11">
-        <f>IF(AC$4="","",COUNTIF(AC6:AC49,"D"))</f>
-        <v/>
-      </c>
-      <c r="AD52" s="11">
-        <f>IF(AD$4="","",COUNTIF(AD6:AD49,"D"))</f>
-        <v/>
-      </c>
-      <c r="AE52" s="11">
-        <f>IF(AE$4="","",COUNTIF(AE6:AE49,"D"))</f>
-        <v/>
-      </c>
-      <c r="AF52" s="11">
-        <f>IF(AF$4="","",COUNTIF(AF6:AF49,"D"))</f>
-        <v/>
-      </c>
-      <c r="AG52" s="11">
-        <f>IF(AG$4="","",COUNTIF(AG6:AG49,"D"))</f>
-        <v/>
-      </c>
-      <c r="AH52" s="11">
-        <f>IF(AH$4="","",COUNTIF(AH6:AH49,"D"))</f>
-        <v/>
-      </c>
-      <c r="AI52" s="11">
-        <f>IF(AI$4="","",COUNTIF(AI6:AI49,"D"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="53" ht="13.5" customHeight="1">
-      <c r="A53" s="45" t="n"/>
-      <c r="C53" s="46" t="n"/>
-      <c r="D53" s="23" t="inlineStr">
+      <c r="E58" s="11">
+        <f>IF(E$5="","",COUNTIF(E6:E55,"D"))</f>
+        <v/>
+      </c>
+      <c r="F58" s="11">
+        <f>IF(F$5="","",COUNTIF(F6:F55,"D"))</f>
+        <v/>
+      </c>
+      <c r="G58" s="11">
+        <f>IF(G$5="","",COUNTIF(G6:G55,"D"))</f>
+        <v/>
+      </c>
+      <c r="H58" s="11">
+        <f>IF(H$5="","",COUNTIF(H6:H55,"D"))</f>
+        <v/>
+      </c>
+      <c r="I58" s="11">
+        <f>IF(I$5="","",COUNTIF(I6:I55,"D"))</f>
+        <v/>
+      </c>
+      <c r="J58" s="11">
+        <f>IF(J$5="","",COUNTIF(J6:J55,"D"))</f>
+        <v/>
+      </c>
+      <c r="K58" s="11">
+        <f>IF(K$5="","",COUNTIF(K6:K55,"D"))</f>
+        <v/>
+      </c>
+      <c r="L58" s="11">
+        <f>IF(L$5="","",COUNTIF(L6:L55,"D"))</f>
+        <v/>
+      </c>
+      <c r="M58" s="11">
+        <f>IF(M$5="","",COUNTIF(M6:M55,"D"))</f>
+        <v/>
+      </c>
+      <c r="N58" s="11">
+        <f>IF(N$5="","",COUNTIF(N6:N55,"D"))</f>
+        <v/>
+      </c>
+      <c r="O58" s="11">
+        <f>IF(O$5="","",COUNTIF(O6:O55,"D"))</f>
+        <v/>
+      </c>
+      <c r="P58" s="11">
+        <f>IF(P$5="","",COUNTIF(P6:P55,"D"))</f>
+        <v/>
+      </c>
+      <c r="Q58" s="11">
+        <f>IF(Q$5="","",COUNTIF(Q6:Q55,"D"))</f>
+        <v/>
+      </c>
+      <c r="R58" s="11">
+        <f>IF(R$5="","",COUNTIF(R6:R55,"D"))</f>
+        <v/>
+      </c>
+      <c r="S58" s="11">
+        <f>IF(S$5="","",COUNTIF(S6:S55,"D"))</f>
+        <v/>
+      </c>
+      <c r="T58" s="11">
+        <f>IF(T$5="","",COUNTIF(T6:T55,"D"))</f>
+        <v/>
+      </c>
+      <c r="U58" s="11">
+        <f>IF(U$5="","",COUNTIF(U6:U55,"D"))</f>
+        <v/>
+      </c>
+      <c r="V58" s="11">
+        <f>IF(V$5="","",COUNTIF(V6:V55,"D"))</f>
+        <v/>
+      </c>
+      <c r="W58" s="11">
+        <f>IF(W$5="","",COUNTIF(W6:W55,"D"))</f>
+        <v/>
+      </c>
+      <c r="X58" s="11">
+        <f>IF(X$5="","",COUNTIF(X6:X55,"D"))</f>
+        <v/>
+      </c>
+      <c r="Y58" s="11">
+        <f>IF(Y$5="","",COUNTIF(Y6:Y55,"D"))</f>
+        <v/>
+      </c>
+      <c r="Z58" s="11">
+        <f>IF(Z$5="","",COUNTIF(Z6:Z55,"D"))</f>
+        <v/>
+      </c>
+      <c r="AA58" s="11">
+        <f>IF(AA$5="","",COUNTIF(AA6:AA55,"D"))</f>
+        <v/>
+      </c>
+      <c r="AB58" s="11">
+        <f>IF(AB$5="","",COUNTIF(AB6:AB55,"D"))</f>
+        <v/>
+      </c>
+      <c r="AC58" s="11">
+        <f>IF(AC$5="","",COUNTIF(AC6:AC55,"D"))</f>
+        <v/>
+      </c>
+      <c r="AD58" s="11">
+        <f>IF(AD$5="","",COUNTIF(AD6:AD55,"D"))</f>
+        <v/>
+      </c>
+      <c r="AE58" s="11">
+        <f>IF(AE$5="","",COUNTIF(AE6:AE55,"D"))</f>
+        <v/>
+      </c>
+      <c r="AF58" s="11">
+        <f>IF(AF$5="","",COUNTIF(AF6:AF55,"D"))</f>
+        <v/>
+      </c>
+      <c r="AG58" s="11">
+        <f>IF(AG$5="","",COUNTIF(AG6:AG55,"D"))</f>
+        <v/>
+      </c>
+      <c r="AH58" s="11">
+        <f>IF(AH$5="","",COUNTIF(AH6:AH55,"D"))</f>
+        <v/>
+      </c>
+      <c r="AI58" s="11">
+        <f>IF(AI$5="","",COUNTIF(AI6:AI55,"D"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59" ht="15" customHeight="1">
+      <c r="A59" s="18" t="n"/>
+      <c r="B59" s="18" t="n"/>
+      <c r="C59" s="18" t="n"/>
+      <c r="D59" s="20" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="E53" s="11">
-        <f>IF(E$4="","",COUNTIF(E6:E49,"T"))</f>
-        <v/>
-      </c>
-      <c r="F53" s="11">
-        <f>IF(F$4="","",COUNTIF(F6:F49,"T"))</f>
-        <v/>
-      </c>
-      <c r="G53" s="11">
-        <f>IF(G$4="","",COUNTIF(G6:G49,"T"))</f>
-        <v/>
-      </c>
-      <c r="H53" s="11">
-        <f>IF(H$4="","",COUNTIF(H6:H49,"T"))</f>
-        <v/>
-      </c>
-      <c r="I53" s="11">
-        <f>IF(I$4="","",COUNTIF(I6:I49,"T"))</f>
-        <v/>
-      </c>
-      <c r="J53" s="11">
-        <f>IF(J$4="","",COUNTIF(J6:J49,"T"))</f>
-        <v/>
-      </c>
-      <c r="K53" s="11">
-        <f>IF(K$4="","",COUNTIF(K6:K49,"T"))</f>
-        <v/>
-      </c>
-      <c r="L53" s="11">
-        <f>IF(L$4="","",COUNTIF(L6:L49,"T"))</f>
-        <v/>
-      </c>
-      <c r="M53" s="11">
-        <f>IF(M$4="","",COUNTIF(M6:M49,"T"))</f>
-        <v/>
-      </c>
-      <c r="N53" s="11">
-        <f>IF(N$4="","",COUNTIF(N6:N49,"T"))</f>
-        <v/>
-      </c>
-      <c r="O53" s="11">
-        <f>IF(O$4="","",COUNTIF(O6:O49,"T"))</f>
-        <v/>
-      </c>
-      <c r="P53" s="11">
-        <f>IF(P$4="","",COUNTIF(P6:P49,"T"))</f>
-        <v/>
-      </c>
-      <c r="Q53" s="11">
-        <f>IF(Q$4="","",COUNTIF(Q6:Q49,"T"))</f>
-        <v/>
-      </c>
-      <c r="R53" s="11">
-        <f>IF(R$4="","",COUNTIF(R6:R49,"T"))</f>
-        <v/>
-      </c>
-      <c r="S53" s="11">
-        <f>IF(S$4="","",COUNTIF(S6:S49,"T"))</f>
-        <v/>
-      </c>
-      <c r="T53" s="11">
-        <f>IF(T$4="","",COUNTIF(T6:T49,"T"))</f>
-        <v/>
-      </c>
-      <c r="U53" s="11">
-        <f>IF(U$4="","",COUNTIF(U6:U49,"T"))</f>
-        <v/>
-      </c>
-      <c r="V53" s="11">
-        <f>IF(V$4="","",COUNTIF(V6:V49,"T"))</f>
-        <v/>
-      </c>
-      <c r="W53" s="11">
-        <f>IF(W$4="","",COUNTIF(W6:W49,"T"))</f>
-        <v/>
-      </c>
-      <c r="X53" s="11">
-        <f>IF(X$4="","",COUNTIF(X6:X49,"T"))</f>
-        <v/>
-      </c>
-      <c r="Y53" s="11">
-        <f>IF(Y$4="","",COUNTIF(Y6:Y49,"T"))</f>
-        <v/>
-      </c>
-      <c r="Z53" s="11">
-        <f>IF(Z$4="","",COUNTIF(Z6:Z49,"T"))</f>
-        <v/>
-      </c>
-      <c r="AA53" s="11">
-        <f>IF(AA$4="","",COUNTIF(AA6:AA49,"T"))</f>
-        <v/>
-      </c>
-      <c r="AB53" s="11">
-        <f>IF(AB$4="","",COUNTIF(AB6:AB49,"T"))</f>
-        <v/>
-      </c>
-      <c r="AC53" s="11">
-        <f>IF(AC$4="","",COUNTIF(AC6:AC49,"T"))</f>
-        <v/>
-      </c>
-      <c r="AD53" s="11">
-        <f>IF(AD$4="","",COUNTIF(AD6:AD49,"T"))</f>
-        <v/>
-      </c>
-      <c r="AE53" s="11">
-        <f>IF(AE$4="","",COUNTIF(AE6:AE49,"T"))</f>
-        <v/>
-      </c>
-      <c r="AF53" s="11">
-        <f>IF(AF$4="","",COUNTIF(AF6:AF49,"T"))</f>
-        <v/>
-      </c>
-      <c r="AG53" s="11">
-        <f>IF(AG$4="","",COUNTIF(AG6:AG49,"T"))</f>
-        <v/>
-      </c>
-      <c r="AH53" s="11">
-        <f>IF(AH$4="","",COUNTIF(AH6:AH49,"T"))</f>
-        <v/>
-      </c>
-      <c r="AI53" s="11">
-        <f>IF(AI$4="","",COUNTIF(AI6:AI49,"T"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="54" ht="13.5" customHeight="1">
-      <c r="A54" s="47" t="n"/>
-      <c r="B54" s="48" t="n"/>
-      <c r="C54" s="49" t="n"/>
-      <c r="D54" s="24" t="inlineStr">
+      <c r="E59" s="11">
+        <f>IF(E$5="","",COUNTIF(E6:E55,"T"))</f>
+        <v/>
+      </c>
+      <c r="F59" s="11">
+        <f>IF(F$5="","",COUNTIF(F6:F55,"T"))</f>
+        <v/>
+      </c>
+      <c r="G59" s="11">
+        <f>IF(G$5="","",COUNTIF(G6:G55,"T"))</f>
+        <v/>
+      </c>
+      <c r="H59" s="11">
+        <f>IF(H$5="","",COUNTIF(H6:H55,"T"))</f>
+        <v/>
+      </c>
+      <c r="I59" s="11">
+        <f>IF(I$5="","",COUNTIF(I6:I55,"T"))</f>
+        <v/>
+      </c>
+      <c r="J59" s="11">
+        <f>IF(J$5="","",COUNTIF(J6:J55,"T"))</f>
+        <v/>
+      </c>
+      <c r="K59" s="11">
+        <f>IF(K$5="","",COUNTIF(K6:K55,"T"))</f>
+        <v/>
+      </c>
+      <c r="L59" s="11">
+        <f>IF(L$5="","",COUNTIF(L6:L55,"T"))</f>
+        <v/>
+      </c>
+      <c r="M59" s="11">
+        <f>IF(M$5="","",COUNTIF(M6:M55,"T"))</f>
+        <v/>
+      </c>
+      <c r="N59" s="11">
+        <f>IF(N$5="","",COUNTIF(N6:N55,"T"))</f>
+        <v/>
+      </c>
+      <c r="O59" s="11">
+        <f>IF(O$5="","",COUNTIF(O6:O55,"T"))</f>
+        <v/>
+      </c>
+      <c r="P59" s="11">
+        <f>IF(P$5="","",COUNTIF(P6:P55,"T"))</f>
+        <v/>
+      </c>
+      <c r="Q59" s="11">
+        <f>IF(Q$5="","",COUNTIF(Q6:Q55,"T"))</f>
+        <v/>
+      </c>
+      <c r="R59" s="11">
+        <f>IF(R$5="","",COUNTIF(R6:R55,"T"))</f>
+        <v/>
+      </c>
+      <c r="S59" s="11">
+        <f>IF(S$5="","",COUNTIF(S6:S55,"T"))</f>
+        <v/>
+      </c>
+      <c r="T59" s="11">
+        <f>IF(T$5="","",COUNTIF(T6:T55,"T"))</f>
+        <v/>
+      </c>
+      <c r="U59" s="11">
+        <f>IF(U$5="","",COUNTIF(U6:U55,"T"))</f>
+        <v/>
+      </c>
+      <c r="V59" s="11">
+        <f>IF(V$5="","",COUNTIF(V6:V55,"T"))</f>
+        <v/>
+      </c>
+      <c r="W59" s="11">
+        <f>IF(W$5="","",COUNTIF(W6:W55,"T"))</f>
+        <v/>
+      </c>
+      <c r="X59" s="11">
+        <f>IF(X$5="","",COUNTIF(X6:X55,"T"))</f>
+        <v/>
+      </c>
+      <c r="Y59" s="11">
+        <f>IF(Y$5="","",COUNTIF(Y6:Y55,"T"))</f>
+        <v/>
+      </c>
+      <c r="Z59" s="11">
+        <f>IF(Z$5="","",COUNTIF(Z6:Z55,"T"))</f>
+        <v/>
+      </c>
+      <c r="AA59" s="11">
+        <f>IF(AA$5="","",COUNTIF(AA6:AA55,"T"))</f>
+        <v/>
+      </c>
+      <c r="AB59" s="11">
+        <f>IF(AB$5="","",COUNTIF(AB6:AB55,"T"))</f>
+        <v/>
+      </c>
+      <c r="AC59" s="11">
+        <f>IF(AC$5="","",COUNTIF(AC6:AC55,"T"))</f>
+        <v/>
+      </c>
+      <c r="AD59" s="11">
+        <f>IF(AD$5="","",COUNTIF(AD6:AD55,"T"))</f>
+        <v/>
+      </c>
+      <c r="AE59" s="11">
+        <f>IF(AE$5="","",COUNTIF(AE6:AE55,"T"))</f>
+        <v/>
+      </c>
+      <c r="AF59" s="11">
+        <f>IF(AF$5="","",COUNTIF(AF6:AF55,"T"))</f>
+        <v/>
+      </c>
+      <c r="AG59" s="11">
+        <f>IF(AG$5="","",COUNTIF(AG6:AG55,"T"))</f>
+        <v/>
+      </c>
+      <c r="AH59" s="11">
+        <f>IF(AH$5="","",COUNTIF(AH6:AH55,"T"))</f>
+        <v/>
+      </c>
+      <c r="AI59" s="11">
+        <f>IF(AI$5="","",COUNTIF(AI6:AI55,"T"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60" ht="15" customHeight="1">
+      <c r="A60" s="18" t="n"/>
+      <c r="B60" s="18" t="n"/>
+      <c r="C60" s="18" t="n"/>
+      <c r="D60" s="21" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
-      <c r="E54" s="11">
-        <f>IF(E$4="","",COUNTIF(E6:E49,"G"))</f>
-        <v/>
-      </c>
-      <c r="F54" s="11">
-        <f>IF(F$4="","",COUNTIF(F6:F49,"G"))</f>
-        <v/>
-      </c>
-      <c r="G54" s="11">
-        <f>IF(G$4="","",COUNTIF(G6:G49,"G"))</f>
-        <v/>
-      </c>
-      <c r="H54" s="11">
-        <f>IF(H$4="","",COUNTIF(H6:H49,"G"))</f>
-        <v/>
-      </c>
-      <c r="I54" s="11">
-        <f>IF(I$4="","",COUNTIF(I6:I49,"G"))</f>
-        <v/>
-      </c>
-      <c r="J54" s="11">
-        <f>IF(J$4="","",COUNTIF(J6:J49,"G"))</f>
-        <v/>
-      </c>
-      <c r="K54" s="11">
-        <f>IF(K$4="","",COUNTIF(K6:K49,"G"))</f>
-        <v/>
-      </c>
-      <c r="L54" s="11">
-        <f>IF(L$4="","",COUNTIF(L6:L49,"G"))</f>
-        <v/>
-      </c>
-      <c r="M54" s="11">
-        <f>IF(M$4="","",COUNTIF(M6:M49,"G"))</f>
-        <v/>
-      </c>
-      <c r="N54" s="11">
-        <f>IF(N$4="","",COUNTIF(N6:N49,"G"))</f>
-        <v/>
-      </c>
-      <c r="O54" s="11">
-        <f>IF(O$4="","",COUNTIF(O6:O49,"G"))</f>
-        <v/>
-      </c>
-      <c r="P54" s="11">
-        <f>IF(P$4="","",COUNTIF(P6:P49,"G"))</f>
-        <v/>
-      </c>
-      <c r="Q54" s="11">
-        <f>IF(Q$4="","",COUNTIF(Q6:Q49,"G"))</f>
-        <v/>
-      </c>
-      <c r="R54" s="11">
-        <f>IF(R$4="","",COUNTIF(R6:R49,"G"))</f>
-        <v/>
-      </c>
-      <c r="S54" s="11">
-        <f>IF(S$4="","",COUNTIF(S6:S49,"G"))</f>
-        <v/>
-      </c>
-      <c r="T54" s="11">
-        <f>IF(T$4="","",COUNTIF(T6:T49,"G"))</f>
-        <v/>
-      </c>
-      <c r="U54" s="11">
-        <f>IF(U$4="","",COUNTIF(U6:U49,"G"))</f>
-        <v/>
-      </c>
-      <c r="V54" s="11">
-        <f>IF(V$4="","",COUNTIF(V6:V49,"G"))</f>
-        <v/>
-      </c>
-      <c r="W54" s="11">
-        <f>IF(W$4="","",COUNTIF(W6:W49,"G"))</f>
-        <v/>
-      </c>
-      <c r="X54" s="11">
-        <f>IF(X$4="","",COUNTIF(X6:X49,"G"))</f>
-        <v/>
-      </c>
-      <c r="Y54" s="11">
-        <f>IF(Y$4="","",COUNTIF(Y6:Y49,"G"))</f>
-        <v/>
-      </c>
-      <c r="Z54" s="11">
-        <f>IF(Z$4="","",COUNTIF(Z6:Z49,"G"))</f>
-        <v/>
-      </c>
-      <c r="AA54" s="11">
-        <f>IF(AA$4="","",COUNTIF(AA6:AA49,"G"))</f>
-        <v/>
-      </c>
-      <c r="AB54" s="11">
-        <f>IF(AB$4="","",COUNTIF(AB6:AB49,"G"))</f>
-        <v/>
-      </c>
-      <c r="AC54" s="11">
-        <f>IF(AC$4="","",COUNTIF(AC6:AC49,"G"))</f>
-        <v/>
-      </c>
-      <c r="AD54" s="11">
-        <f>IF(AD$4="","",COUNTIF(AD6:AD49,"G"))</f>
-        <v/>
-      </c>
-      <c r="AE54" s="11">
-        <f>IF(AE$4="","",COUNTIF(AE6:AE49,"G"))</f>
-        <v/>
-      </c>
-      <c r="AF54" s="11">
-        <f>IF(AF$4="","",COUNTIF(AF6:AF49,"G"))</f>
-        <v/>
-      </c>
-      <c r="AG54" s="11">
-        <f>IF(AG$4="","",COUNTIF(AG6:AG49,"G"))</f>
-        <v/>
-      </c>
-      <c r="AH54" s="11">
-        <f>IF(AH$4="","",COUNTIF(AH6:AH49,"G"))</f>
-        <v/>
-      </c>
-      <c r="AI54" s="11">
-        <f>IF(AI$4="","",COUNTIF(AI6:AI49,"G"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="55" ht="13.5" customHeight="1">
-      <c r="A55" s="21" t="n"/>
-      <c r="B55" s="21" t="n"/>
-      <c r="C55" s="21" t="n"/>
-      <c r="D55" s="13" t="inlineStr">
+      <c r="E60" s="11">
+        <f>IF(E$5="","",COUNTIF(E6:E55,"G"))</f>
+        <v/>
+      </c>
+      <c r="F60" s="11">
+        <f>IF(F$5="","",COUNTIF(F6:F55,"G"))</f>
+        <v/>
+      </c>
+      <c r="G60" s="11">
+        <f>IF(G$5="","",COUNTIF(G6:G55,"G"))</f>
+        <v/>
+      </c>
+      <c r="H60" s="11">
+        <f>IF(H$5="","",COUNTIF(H6:H55,"G"))</f>
+        <v/>
+      </c>
+      <c r="I60" s="11">
+        <f>IF(I$5="","",COUNTIF(I6:I55,"G"))</f>
+        <v/>
+      </c>
+      <c r="J60" s="11">
+        <f>IF(J$5="","",COUNTIF(J6:J55,"G"))</f>
+        <v/>
+      </c>
+      <c r="K60" s="11">
+        <f>IF(K$5="","",COUNTIF(K6:K55,"G"))</f>
+        <v/>
+      </c>
+      <c r="L60" s="11">
+        <f>IF(L$5="","",COUNTIF(L6:L55,"G"))</f>
+        <v/>
+      </c>
+      <c r="M60" s="11">
+        <f>IF(M$5="","",COUNTIF(M6:M55,"G"))</f>
+        <v/>
+      </c>
+      <c r="N60" s="11">
+        <f>IF(N$5="","",COUNTIF(N6:N55,"G"))</f>
+        <v/>
+      </c>
+      <c r="O60" s="11">
+        <f>IF(O$5="","",COUNTIF(O6:O55,"G"))</f>
+        <v/>
+      </c>
+      <c r="P60" s="11">
+        <f>IF(P$5="","",COUNTIF(P6:P55,"G"))</f>
+        <v/>
+      </c>
+      <c r="Q60" s="11">
+        <f>IF(Q$5="","",COUNTIF(Q6:Q55,"G"))</f>
+        <v/>
+      </c>
+      <c r="R60" s="11">
+        <f>IF(R$5="","",COUNTIF(R6:R55,"G"))</f>
+        <v/>
+      </c>
+      <c r="S60" s="11">
+        <f>IF(S$5="","",COUNTIF(S6:S55,"G"))</f>
+        <v/>
+      </c>
+      <c r="T60" s="11">
+        <f>IF(T$5="","",COUNTIF(T6:T55,"G"))</f>
+        <v/>
+      </c>
+      <c r="U60" s="11">
+        <f>IF(U$5="","",COUNTIF(U6:U55,"G"))</f>
+        <v/>
+      </c>
+      <c r="V60" s="11">
+        <f>IF(V$5="","",COUNTIF(V6:V55,"G"))</f>
+        <v/>
+      </c>
+      <c r="W60" s="11">
+        <f>IF(W$5="","",COUNTIF(W6:W55,"G"))</f>
+        <v/>
+      </c>
+      <c r="X60" s="11">
+        <f>IF(X$5="","",COUNTIF(X6:X55,"G"))</f>
+        <v/>
+      </c>
+      <c r="Y60" s="11">
+        <f>IF(Y$5="","",COUNTIF(Y6:Y55,"G"))</f>
+        <v/>
+      </c>
+      <c r="Z60" s="11">
+        <f>IF(Z$5="","",COUNTIF(Z6:Z55,"G"))</f>
+        <v/>
+      </c>
+      <c r="AA60" s="11">
+        <f>IF(AA$5="","",COUNTIF(AA6:AA55,"G"))</f>
+        <v/>
+      </c>
+      <c r="AB60" s="11">
+        <f>IF(AB$5="","",COUNTIF(AB6:AB55,"G"))</f>
+        <v/>
+      </c>
+      <c r="AC60" s="11">
+        <f>IF(AC$5="","",COUNTIF(AC6:AC55,"G"))</f>
+        <v/>
+      </c>
+      <c r="AD60" s="11">
+        <f>IF(AD$5="","",COUNTIF(AD6:AD55,"G"))</f>
+        <v/>
+      </c>
+      <c r="AE60" s="11">
+        <f>IF(AE$5="","",COUNTIF(AE6:AE55,"G"))</f>
+        <v/>
+      </c>
+      <c r="AF60" s="11">
+        <f>IF(AF$5="","",COUNTIF(AF6:AF55,"G"))</f>
+        <v/>
+      </c>
+      <c r="AG60" s="11">
+        <f>IF(AG$5="","",COUNTIF(AG6:AG55,"G"))</f>
+        <v/>
+      </c>
+      <c r="AH60" s="11">
+        <f>IF(AH$5="","",COUNTIF(AH6:AH55,"G"))</f>
+        <v/>
+      </c>
+      <c r="AI60" s="11">
+        <f>IF(AI$5="","",COUNTIF(AI6:AI55,"G"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61" ht="15" customHeight="1">
+      <c r="A61" s="18" t="n"/>
+      <c r="B61" s="18" t="n"/>
+      <c r="C61" s="18" t="n"/>
+      <c r="D61" s="22" t="inlineStr">
         <is>
           <t>TOT</t>
         </is>
       </c>
-      <c r="E55" s="13">
-        <f>IF(E$4="","",SUM(E52:E54))</f>
-        <v/>
-      </c>
-      <c r="F55" s="13">
-        <f>IF(F$4="","",SUM(F52:F54))</f>
-        <v/>
-      </c>
-      <c r="G55" s="13">
-        <f>IF(G$4="","",SUM(G52:G54))</f>
-        <v/>
-      </c>
-      <c r="H55" s="13">
-        <f>IF(H$4="","",SUM(H52:H54))</f>
-        <v/>
-      </c>
-      <c r="I55" s="13">
-        <f>IF(I$4="","",SUM(I52:I54))</f>
-        <v/>
-      </c>
-      <c r="J55" s="13">
-        <f>IF(J$4="","",SUM(J52:J54))</f>
-        <v/>
-      </c>
-      <c r="K55" s="13">
-        <f>IF(K$4="","",SUM(K52:K54))</f>
-        <v/>
-      </c>
-      <c r="L55" s="13">
-        <f>IF(L$4="","",SUM(L52:L54))</f>
-        <v/>
-      </c>
-      <c r="M55" s="13">
-        <f>IF(M$4="","",SUM(M52:M54))</f>
-        <v/>
-      </c>
-      <c r="N55" s="13">
-        <f>IF(N$4="","",SUM(N52:N54))</f>
-        <v/>
-      </c>
-      <c r="O55" s="13">
-        <f>IF(O$4="","",SUM(O52:O54))</f>
-        <v/>
-      </c>
-      <c r="P55" s="13">
-        <f>IF(P$4="","",SUM(P52:P54))</f>
-        <v/>
-      </c>
-      <c r="Q55" s="13">
-        <f>IF(Q$4="","",SUM(Q52:Q54))</f>
-        <v/>
-      </c>
-      <c r="R55" s="13">
-        <f>IF(R$4="","",SUM(R52:R54))</f>
-        <v/>
-      </c>
-      <c r="S55" s="13">
-        <f>IF(S$4="","",SUM(S52:S54))</f>
-        <v/>
-      </c>
-      <c r="T55" s="13">
-        <f>IF(T$4="","",SUM(T52:T54))</f>
-        <v/>
-      </c>
-      <c r="U55" s="13">
-        <f>IF(U$4="","",SUM(U52:U54))</f>
-        <v/>
-      </c>
-      <c r="V55" s="13">
-        <f>IF(V$4="","",SUM(V52:V54))</f>
-        <v/>
-      </c>
-      <c r="W55" s="13">
-        <f>IF(W$4="","",SUM(W52:W54))</f>
-        <v/>
-      </c>
-      <c r="X55" s="13">
-        <f>IF(X$4="","",SUM(X52:X54))</f>
-        <v/>
-      </c>
-      <c r="Y55" s="13">
-        <f>IF(Y$4="","",SUM(Y52:Y54))</f>
-        <v/>
-      </c>
-      <c r="Z55" s="13">
-        <f>IF(Z$4="","",SUM(Z52:Z54))</f>
-        <v/>
-      </c>
-      <c r="AA55" s="13">
-        <f>IF(AA$4="","",SUM(AA52:AA54))</f>
-        <v/>
-      </c>
-      <c r="AB55" s="13">
-        <f>IF(AB$4="","",SUM(AB52:AB54))</f>
-        <v/>
-      </c>
-      <c r="AC55" s="13">
-        <f>IF(AC$4="","",SUM(AC52:AC54))</f>
-        <v/>
-      </c>
-      <c r="AD55" s="13">
-        <f>IF(AD$4="","",SUM(AD52:AD54))</f>
-        <v/>
-      </c>
-      <c r="AE55" s="13">
-        <f>IF(AE$4="","",SUM(AE52:AE54))</f>
-        <v/>
-      </c>
-      <c r="AF55" s="13">
-        <f>IF(AF$4="","",SUM(AF52:AF54))</f>
-        <v/>
-      </c>
-      <c r="AG55" s="13">
-        <f>IF(AG$4="","",SUM(AG52:AG54))</f>
-        <v/>
-      </c>
-      <c r="AH55" s="13">
-        <f>IF(AH$4="","",SUM(AH52:AH54))</f>
-        <v/>
-      </c>
-      <c r="AI55" s="13">
-        <f>IF(AI$4="","",SUM(AI52:AI54))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="25" t="inlineStr">
+      <c r="E61" s="23">
+        <f>IF(E$5="","",SUM(E58:E60))</f>
+        <v/>
+      </c>
+      <c r="F61" s="23">
+        <f>IF(F$5="","",SUM(F58:F60))</f>
+        <v/>
+      </c>
+      <c r="G61" s="23">
+        <f>IF(G$5="","",SUM(G58:G60))</f>
+        <v/>
+      </c>
+      <c r="H61" s="23">
+        <f>IF(H$5="","",SUM(H58:H60))</f>
+        <v/>
+      </c>
+      <c r="I61" s="23">
+        <f>IF(I$5="","",SUM(I58:I60))</f>
+        <v/>
+      </c>
+      <c r="J61" s="23">
+        <f>IF(J$5="","",SUM(J58:J60))</f>
+        <v/>
+      </c>
+      <c r="K61" s="23">
+        <f>IF(K$5="","",SUM(K58:K60))</f>
+        <v/>
+      </c>
+      <c r="L61" s="23">
+        <f>IF(L$5="","",SUM(L58:L60))</f>
+        <v/>
+      </c>
+      <c r="M61" s="23">
+        <f>IF(M$5="","",SUM(M58:M60))</f>
+        <v/>
+      </c>
+      <c r="N61" s="23">
+        <f>IF(N$5="","",SUM(N58:N60))</f>
+        <v/>
+      </c>
+      <c r="O61" s="23">
+        <f>IF(O$5="","",SUM(O58:O60))</f>
+        <v/>
+      </c>
+      <c r="P61" s="23">
+        <f>IF(P$5="","",SUM(P58:P60))</f>
+        <v/>
+      </c>
+      <c r="Q61" s="23">
+        <f>IF(Q$5="","",SUM(Q58:Q60))</f>
+        <v/>
+      </c>
+      <c r="R61" s="23">
+        <f>IF(R$5="","",SUM(R58:R60))</f>
+        <v/>
+      </c>
+      <c r="S61" s="23">
+        <f>IF(S$5="","",SUM(S58:S60))</f>
+        <v/>
+      </c>
+      <c r="T61" s="23">
+        <f>IF(T$5="","",SUM(T58:T60))</f>
+        <v/>
+      </c>
+      <c r="U61" s="23">
+        <f>IF(U$5="","",SUM(U58:U60))</f>
+        <v/>
+      </c>
+      <c r="V61" s="23">
+        <f>IF(V$5="","",SUM(V58:V60))</f>
+        <v/>
+      </c>
+      <c r="W61" s="23">
+        <f>IF(W$5="","",SUM(W58:W60))</f>
+        <v/>
+      </c>
+      <c r="X61" s="23">
+        <f>IF(X$5="","",SUM(X58:X60))</f>
+        <v/>
+      </c>
+      <c r="Y61" s="23">
+        <f>IF(Y$5="","",SUM(Y58:Y60))</f>
+        <v/>
+      </c>
+      <c r="Z61" s="23">
+        <f>IF(Z$5="","",SUM(Z58:Z60))</f>
+        <v/>
+      </c>
+      <c r="AA61" s="23">
+        <f>IF(AA$5="","",SUM(AA58:AA60))</f>
+        <v/>
+      </c>
+      <c r="AB61" s="23">
+        <f>IF(AB$5="","",SUM(AB58:AB60))</f>
+        <v/>
+      </c>
+      <c r="AC61" s="23">
+        <f>IF(AC$5="","",SUM(AC58:AC60))</f>
+        <v/>
+      </c>
+      <c r="AD61" s="23">
+        <f>IF(AD$5="","",SUM(AD58:AD60))</f>
+        <v/>
+      </c>
+      <c r="AE61" s="23">
+        <f>IF(AE$5="","",SUM(AE58:AE60))</f>
+        <v/>
+      </c>
+      <c r="AF61" s="23">
+        <f>IF(AF$5="","",SUM(AF58:AF60))</f>
+        <v/>
+      </c>
+      <c r="AG61" s="23">
+        <f>IF(AG$5="","",SUM(AG58:AG60))</f>
+        <v/>
+      </c>
+      <c r="AH61" s="23">
+        <f>IF(AH$5="","",SUM(AH58:AH60))</f>
+        <v/>
+      </c>
+      <c r="AI61" s="23">
+        <f>IF(AI$5="","",SUM(AI58:AI60))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="24" t="inlineStr">
         <is>
           <t>SHIFT TIMES</t>
         </is>
       </c>
-      <c r="F57" s="25" t="inlineStr">
+      <c r="F63" s="24" t="inlineStr">
         <is>
           <t>CODE LEGEND</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="14" customHeight="1">
-      <c r="B58" s="26" t="inlineStr">
+    <row r="64" ht="16" customHeight="1">
+      <c r="B64" s="19" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="C58" s="27" t="inlineStr">
+      <c r="C64" s="25" t="inlineStr">
         <is>
           <t>DAY (07:00 - 15:00)</t>
         </is>
       </c>
-      <c r="F58" s="22" t="inlineStr">
+      <c r="F64" s="26" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="G58" s="50" t="n"/>
-      <c r="H58" s="28" t="inlineStr">
+      <c r="G64" s="18" t="n"/>
+      <c r="H64" s="27" t="inlineStr">
         <is>
           <t>DAY</t>
         </is>
       </c>
-      <c r="J58" s="23" t="inlineStr">
+      <c r="L64" s="28" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="K58" s="50" t="n"/>
-      <c r="L58" s="28" t="inlineStr">
+      <c r="M64" s="18" t="n"/>
+      <c r="N64" s="27" t="inlineStr">
         <is>
           <t>TWILIGHT</t>
         </is>
       </c>
-      <c r="N58" s="24" t="inlineStr">
+      <c r="R64" s="29" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
-      <c r="O58" s="50" t="n"/>
-      <c r="P58" s="28" t="inlineStr">
+      <c r="S64" s="18" t="n"/>
+      <c r="T64" s="27" t="inlineStr">
         <is>
           <t>GRAVEYARD</t>
         </is>
       </c>
-      <c r="R58" s="29" t="inlineStr">
+      <c r="X64" s="30" t="inlineStr">
         <is>
           <t>TR</t>
         </is>
       </c>
-      <c r="S58" s="50" t="n"/>
-      <c r="T58" s="28" t="inlineStr">
+      <c r="Y64" s="18" t="n"/>
+      <c r="Z64" s="27" t="inlineStr">
         <is>
           <t>TRAINING</t>
         </is>
       </c>
-      <c r="V58" s="30" t="inlineStr">
+      <c r="AD64" s="31" t="inlineStr">
         <is>
           <t>V</t>
         </is>
       </c>
-      <c r="W58" s="50" t="n"/>
-      <c r="X58" s="28" t="inlineStr">
+      <c r="AE64" s="18" t="n"/>
+      <c r="AF64" s="27" t="inlineStr">
         <is>
           <t>VACATION</t>
         </is>
       </c>
-      <c r="Z58" s="31" t="inlineStr">
+    </row>
+    <row r="65" ht="16" customHeight="1">
+      <c r="B65" s="20" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C65" s="25" t="inlineStr">
+        <is>
+          <t>TWI (15:00 - 23:00)</t>
+        </is>
+      </c>
+      <c r="F65" s="32" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="AA58" s="50" t="n"/>
-      <c r="AB58" s="28" t="inlineStr">
+      <c r="G65" s="18" t="n"/>
+      <c r="H65" s="27" t="inlineStr">
         <is>
           <t>REST/RDO</t>
         </is>
       </c>
-      <c r="AD58" s="32" t="inlineStr">
+      <c r="L65" s="33" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="AE58" s="50" t="n"/>
-      <c r="AF58" s="28" t="inlineStr">
+      <c r="M65" s="18" t="n"/>
+      <c r="N65" s="27" t="inlineStr">
         <is>
           <t>ABSENT</t>
         </is>
       </c>
-    </row>
-    <row r="59" ht="14" customHeight="1">
-      <c r="B59" s="33" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="C59" s="27" t="inlineStr">
-        <is>
-          <t>TWI (15:00 - 23:00)</t>
-        </is>
-      </c>
-      <c r="F59" s="34" t="inlineStr">
+      <c r="R65" s="34" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="G59" s="50" t="n"/>
-      <c r="H59" s="28" t="inlineStr">
+      <c r="S65" s="18" t="n"/>
+      <c r="T65" s="27" t="inlineStr">
         <is>
           <t>HOLIDAY</t>
         </is>
       </c>
-      <c r="J59" s="35" t="inlineStr">
+      <c r="X65" s="35" t="inlineStr">
         <is>
           <t>OT</t>
         </is>
       </c>
-      <c r="K59" s="50" t="n"/>
-      <c r="L59" s="28" t="inlineStr">
+      <c r="Y65" s="18" t="n"/>
+      <c r="Z65" s="27" t="inlineStr">
         <is>
           <t>OVERTIME</t>
         </is>
       </c>
-      <c r="N59" s="36" t="inlineStr">
+      <c r="AD65" s="36" t="inlineStr">
         <is>
           <t>OS</t>
         </is>
       </c>
-      <c r="O59" s="50" t="n"/>
-      <c r="P59" s="28" t="inlineStr">
+      <c r="AE65" s="18" t="n"/>
+      <c r="AF65" s="27" t="inlineStr">
         <is>
           <t>OUTSTATION</t>
         </is>
       </c>
-      <c r="R59" s="37" t="inlineStr">
+    </row>
+    <row r="66" ht="16" customHeight="1">
+      <c r="B66" s="21" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="C66" s="25" t="inlineStr">
+        <is>
+          <t>GRV (23:00 - 07:00)</t>
+        </is>
+      </c>
+      <c r="F66" s="37" t="inlineStr">
         <is>
           <t>S/L</t>
         </is>
       </c>
-      <c r="S59" s="50" t="n"/>
-      <c r="T59" s="28" t="inlineStr">
+      <c r="G66" s="18" t="n"/>
+      <c r="H66" s="27" t="inlineStr">
         <is>
           <t>SICK LEAVE</t>
         </is>
       </c>
-      <c r="V59" s="38" t="inlineStr">
+      <c r="L66" s="38" t="inlineStr">
         <is>
           <t>C/T</t>
         </is>
       </c>
-      <c r="W59" s="50" t="n"/>
-      <c r="X59" s="28" t="inlineStr">
+      <c r="M66" s="18" t="n"/>
+      <c r="N66" s="27" t="inlineStr">
         <is>
           <t>COMP TIME</t>
         </is>
       </c>
-      <c r="Z59" s="39" t="inlineStr">
+      <c r="R66" s="39" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="AA59" s="50" t="n"/>
-      <c r="AB59" s="28" t="inlineStr">
+      <c r="S66" s="18" t="n"/>
+      <c r="T66" s="27" t="inlineStr">
         <is>
           <t>LATE/LEAVE</t>
         </is>
       </c>
-      <c r="AD59" s="40" t="inlineStr">
+      <c r="X66" s="40" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="AE59" s="50" t="n"/>
-      <c r="AF59" s="28" t="inlineStr">
+      <c r="Y66" s="18" t="n"/>
+      <c r="Z66" s="27" t="inlineStr">
         <is>
           <t>NOTE</t>
         </is>
       </c>
     </row>
-    <row r="60" ht="14" customHeight="1">
-      <c r="B60" s="41" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="C60" s="27" t="inlineStr">
-        <is>
-          <t>GRV (23:00 - 07:00)</t>
+    <row r="68">
+      <c r="A68" s="41" t="inlineStr">
+        <is>
+          <t>STAFF LIST — copy names into the crews above (excluded from print)</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="8" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B69" s="8" t="inlineStr">
+        <is>
+          <t>PRN</t>
+        </is>
+      </c>
+      <c r="C69" s="8" t="inlineStr">
+        <is>
+          <t>NAME</t>
+        </is>
+      </c>
+      <c r="D69" s="8" t="inlineStr">
+        <is>
+          <t>Posn</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="15" customHeight="1">
+      <c r="A70" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="B70" s="11" t="inlineStr">
+        <is>
+          <t>13006435</t>
+        </is>
+      </c>
+      <c r="C70" s="42" t="inlineStr">
+        <is>
+          <t>HOMAID ALJAHDALI</t>
+        </is>
+      </c>
+      <c r="D70" s="43" t="inlineStr">
+        <is>
+          <t>ACT/SUPV</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="15" customHeight="1">
+      <c r="A71" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="B71" s="11" t="inlineStr">
+        <is>
+          <t>13008931</t>
+        </is>
+      </c>
+      <c r="C71" s="42" t="inlineStr">
+        <is>
+          <t>RONILO NOGADAS AMEN</t>
+        </is>
+      </c>
+      <c r="D71" s="43" t="inlineStr">
+        <is>
+          <t>ACT/SUPV</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="15" customHeight="1">
+      <c r="A72" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="B72" s="11" t="inlineStr">
+        <is>
+          <t>13010279</t>
+        </is>
+      </c>
+      <c r="C72" s="42" t="inlineStr">
+        <is>
+          <t>AHMED M. ALWAHBI</t>
+        </is>
+      </c>
+      <c r="D72" s="43" t="inlineStr">
+        <is>
+          <t>ACT/SUPV</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="15" customHeight="1">
+      <c r="A73" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="B73" s="11" t="inlineStr">
+        <is>
+          <t>13007568</t>
+        </is>
+      </c>
+      <c r="C73" s="42" t="inlineStr">
+        <is>
+          <t>NAIF ALANEZI</t>
+        </is>
+      </c>
+      <c r="D73" s="43" t="inlineStr">
+        <is>
+          <t>ACT/SUPV</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="15" customHeight="1">
+      <c r="A74" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="B74" s="11" t="inlineStr">
+        <is>
+          <t>30005295</t>
+        </is>
+      </c>
+      <c r="C74" s="42" t="inlineStr">
+        <is>
+          <t>RODEL CLEMENTE</t>
+        </is>
+      </c>
+      <c r="D74" s="43" t="inlineStr">
+        <is>
+          <t>TECH</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="15" customHeight="1">
+      <c r="A75" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="B75" s="11" t="inlineStr">
+        <is>
+          <t>30001593</t>
+        </is>
+      </c>
+      <c r="C75" s="42" t="inlineStr">
+        <is>
+          <t>FYSAL M. ALEDAINI</t>
+        </is>
+      </c>
+      <c r="D75" s="43" t="inlineStr">
+        <is>
+          <t>OJT</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="15" customHeight="1">
+      <c r="A76" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="B76" s="11" t="inlineStr">
+        <is>
+          <t>30001338</t>
+        </is>
+      </c>
+      <c r="C76" s="42" t="inlineStr">
+        <is>
+          <t>MASHHOUR ALSULAIMANI</t>
+        </is>
+      </c>
+      <c r="D76" s="43" t="inlineStr">
+        <is>
+          <t>OJT</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="15" customHeight="1">
+      <c r="A77" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="B77" s="11" t="inlineStr">
+        <is>
+          <t>30001573</t>
+        </is>
+      </c>
+      <c r="C77" s="42" t="inlineStr">
+        <is>
+          <t>JEHAD M. HAKAMI</t>
+        </is>
+      </c>
+      <c r="D77" s="43" t="inlineStr">
+        <is>
+          <t>OJT</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="15" customHeight="1">
+      <c r="A78" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B78" s="11" t="inlineStr">
+        <is>
+          <t>30001366</t>
+        </is>
+      </c>
+      <c r="C78" s="42" t="inlineStr">
+        <is>
+          <t>ABDULAZIZ ZAKOUR</t>
+        </is>
+      </c>
+      <c r="D78" s="43" t="inlineStr">
+        <is>
+          <t>OJT</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="15" customHeight="1">
+      <c r="A79" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="B79" s="11" t="inlineStr">
+        <is>
+          <t>30001450</t>
+        </is>
+      </c>
+      <c r="C79" s="42" t="inlineStr">
+        <is>
+          <t>MUHAMMED ALSHAIKH</t>
+        </is>
+      </c>
+      <c r="D79" s="43" t="inlineStr">
+        <is>
+          <t>OJT</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="15" customHeight="1">
+      <c r="A80" s="10" t="n">
+        <v>11</v>
+      </c>
+      <c r="B80" s="11" t="inlineStr">
+        <is>
+          <t>30001602</t>
+        </is>
+      </c>
+      <c r="C80" s="42" t="inlineStr">
+        <is>
+          <t>AHMED M. ALYAMANI</t>
+        </is>
+      </c>
+      <c r="D80" s="43" t="inlineStr">
+        <is>
+          <t>OJT</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="15" customHeight="1">
+      <c r="A81" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="B81" s="11" t="inlineStr">
+        <is>
+          <t>40001135</t>
+        </is>
+      </c>
+      <c r="C81" s="42" t="inlineStr">
+        <is>
+          <t>SYAHLENDRA SYAMSOE</t>
+        </is>
+      </c>
+      <c r="D81" s="43" t="inlineStr">
+        <is>
+          <t>FITTER</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="15" customHeight="1">
+      <c r="A82" s="10" t="n">
+        <v>13</v>
+      </c>
+      <c r="B82" s="11" t="inlineStr">
+        <is>
+          <t>70010082</t>
+        </is>
+      </c>
+      <c r="C82" s="42" t="inlineStr">
+        <is>
+          <t>MOHAMMAD KAIFI</t>
+        </is>
+      </c>
+      <c r="D82" s="43" t="inlineStr">
+        <is>
+          <t>FITTER</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="15" customHeight="1">
+      <c r="A83" s="10" t="n">
+        <v>14</v>
+      </c>
+      <c r="B83" s="11" t="inlineStr">
+        <is>
+          <t>13009258</t>
+        </is>
+      </c>
+      <c r="C83" s="42" t="inlineStr">
+        <is>
+          <t>ALI ALAHMADI</t>
+        </is>
+      </c>
+      <c r="D83" s="43" t="inlineStr">
+        <is>
+          <t>FITTER</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="15" customHeight="1">
+      <c r="A84" s="10" t="n">
+        <v>15</v>
+      </c>
+      <c r="B84" s="11" t="inlineStr">
+        <is>
+          <t>13009255</t>
+        </is>
+      </c>
+      <c r="C84" s="42" t="inlineStr">
+        <is>
+          <t>HOSSAM ALGHAMDI</t>
+        </is>
+      </c>
+      <c r="D84" s="43" t="inlineStr">
+        <is>
+          <t>FITTER</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="15" customHeight="1">
+      <c r="A85" s="10" t="n">
+        <v>16</v>
+      </c>
+      <c r="B85" s="11" t="inlineStr">
+        <is>
+          <t>13009047</t>
+        </is>
+      </c>
+      <c r="C85" s="42" t="inlineStr">
+        <is>
+          <t>JIMRICKS AQINO</t>
+        </is>
+      </c>
+      <c r="D85" s="43" t="inlineStr">
+        <is>
+          <t>FITTER</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="15" customHeight="1">
+      <c r="A86" s="10" t="n">
+        <v>17</v>
+      </c>
+      <c r="B86" s="11" t="inlineStr">
+        <is>
+          <t>13006567</t>
+        </is>
+      </c>
+      <c r="C86" s="42" t="inlineStr">
+        <is>
+          <t>AHMED AL-GHAMDI</t>
+        </is>
+      </c>
+      <c r="D86" s="43" t="inlineStr">
+        <is>
+          <t>ACT/SUPV</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="15" customHeight="1">
+      <c r="A87" s="10" t="n">
+        <v>18</v>
+      </c>
+      <c r="B87" s="11" t="inlineStr">
+        <is>
+          <t>13010253</t>
+        </is>
+      </c>
+      <c r="C87" s="42" t="inlineStr">
+        <is>
+          <t>AHMED S. ALGHAMDI</t>
+        </is>
+      </c>
+      <c r="D87" s="43" t="inlineStr">
+        <is>
+          <t>ACT/SUPV</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="15" customHeight="1">
+      <c r="A88" s="10" t="n">
+        <v>19</v>
+      </c>
+      <c r="B88" s="11" t="inlineStr">
+        <is>
+          <t>13007276</t>
+        </is>
+      </c>
+      <c r="C88" s="42" t="inlineStr">
+        <is>
+          <t>MOHAMMED BAROOM</t>
+        </is>
+      </c>
+      <c r="D88" s="43" t="inlineStr">
+        <is>
+          <t>TECH</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="15" customHeight="1">
+      <c r="A89" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="B89" s="11" t="inlineStr">
+        <is>
+          <t>13010286</t>
+        </is>
+      </c>
+      <c r="C89" s="42" t="inlineStr">
+        <is>
+          <t>ABDULAZIZ F. ALBOUQ</t>
+        </is>
+      </c>
+      <c r="D89" s="43" t="inlineStr">
+        <is>
+          <t>TECH</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="15" customHeight="1">
+      <c r="A90" s="10" t="n">
+        <v>21</v>
+      </c>
+      <c r="B90" s="11" t="inlineStr">
+        <is>
+          <t>30004221</t>
+        </is>
+      </c>
+      <c r="C90" s="42" t="inlineStr">
+        <is>
+          <t>YOUSEF BARIFAH</t>
+        </is>
+      </c>
+      <c r="D90" s="43" t="inlineStr">
+        <is>
+          <t>TECH</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="15" customHeight="1">
+      <c r="A91" s="10" t="n">
+        <v>22</v>
+      </c>
+      <c r="B91" s="11" t="inlineStr">
+        <is>
+          <t>30001345</t>
+        </is>
+      </c>
+      <c r="C91" s="42" t="inlineStr">
+        <is>
+          <t>AHMED ALSHARIF</t>
+        </is>
+      </c>
+      <c r="D91" s="43" t="inlineStr">
+        <is>
+          <t>OJT</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="15" customHeight="1">
+      <c r="A92" s="10" t="n">
+        <v>23</v>
+      </c>
+      <c r="B92" s="11" t="inlineStr">
+        <is>
+          <t>30001351</t>
+        </is>
+      </c>
+      <c r="C92" s="42" t="inlineStr">
+        <is>
+          <t>KHALID ALSHUBRAMI</t>
+        </is>
+      </c>
+      <c r="D92" s="43" t="inlineStr">
+        <is>
+          <t>OJT</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="15" customHeight="1">
+      <c r="A93" s="10" t="n">
+        <v>24</v>
+      </c>
+      <c r="B93" s="11" t="inlineStr">
+        <is>
+          <t>30001451</t>
+        </is>
+      </c>
+      <c r="C93" s="42" t="inlineStr">
+        <is>
+          <t>MUHAMMED ALHARBI</t>
+        </is>
+      </c>
+      <c r="D93" s="43" t="inlineStr">
+        <is>
+          <t>OJT</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="15" customHeight="1">
+      <c r="A94" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="B94" s="11" t="inlineStr">
+        <is>
+          <t>30001452</t>
+        </is>
+      </c>
+      <c r="C94" s="42" t="inlineStr">
+        <is>
+          <t>SAAD ALDOSARI</t>
+        </is>
+      </c>
+      <c r="D94" s="43" t="inlineStr">
+        <is>
+          <t>OJT</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="15" customHeight="1">
+      <c r="A95" s="10" t="n">
+        <v>26</v>
+      </c>
+      <c r="B95" s="11" t="inlineStr">
+        <is>
+          <t>30001461</t>
+        </is>
+      </c>
+      <c r="C95" s="42" t="inlineStr">
+        <is>
+          <t>HUSSAM ALTHUBAITI</t>
+        </is>
+      </c>
+      <c r="D95" s="43" t="inlineStr">
+        <is>
+          <t>OJT</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="15" customHeight="1">
+      <c r="A96" s="10" t="n">
+        <v>27</v>
+      </c>
+      <c r="B96" s="11" t="inlineStr">
+        <is>
+          <t>30001575</t>
+        </is>
+      </c>
+      <c r="C96" s="42" t="inlineStr">
+        <is>
+          <t>FADUL A. FADUL</t>
+        </is>
+      </c>
+      <c r="D96" s="43" t="inlineStr">
+        <is>
+          <t>OJT</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="15" customHeight="1">
+      <c r="A97" s="10" t="n">
+        <v>28</v>
+      </c>
+      <c r="B97" s="11" t="inlineStr">
+        <is>
+          <t>30001577</t>
+        </is>
+      </c>
+      <c r="C97" s="42" t="inlineStr">
+        <is>
+          <t>FOUAD A. MOJALLY</t>
+        </is>
+      </c>
+      <c r="D97" s="43" t="inlineStr">
+        <is>
+          <t>OJT</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="15" customHeight="1">
+      <c r="A98" s="10" t="n">
+        <v>29</v>
+      </c>
+      <c r="B98" s="11" t="inlineStr">
+        <is>
+          <t>30001774</t>
+        </is>
+      </c>
+      <c r="C98" s="42" t="inlineStr">
+        <is>
+          <t>SAAD A. ALQAHTANI</t>
+        </is>
+      </c>
+      <c r="D98" s="43" t="inlineStr">
+        <is>
+          <t>OJT</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="15" customHeight="1">
+      <c r="A99" s="10" t="n">
+        <v>30</v>
+      </c>
+      <c r="B99" s="11" t="inlineStr">
+        <is>
+          <t>40000188</t>
+        </is>
+      </c>
+      <c r="C99" s="42" t="inlineStr">
+        <is>
+          <t>RAKAN AGILY</t>
+        </is>
+      </c>
+      <c r="D99" s="43" t="inlineStr">
+        <is>
+          <t>FITTER</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="15" customHeight="1">
+      <c r="A100" s="10" t="n">
+        <v>31</v>
+      </c>
+      <c r="B100" s="11" t="inlineStr">
+        <is>
+          <t>13009042</t>
+        </is>
+      </c>
+      <c r="C100" s="42" t="inlineStr">
+        <is>
+          <t>OLANDRES JR BEINVENIDO</t>
+        </is>
+      </c>
+      <c r="D100" s="43" t="inlineStr">
+        <is>
+          <t>FITTER</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="15" customHeight="1">
+      <c r="A101" s="10" t="n">
+        <v>32</v>
+      </c>
+      <c r="B101" s="11" t="inlineStr">
+        <is>
+          <t>40000706</t>
+        </is>
+      </c>
+      <c r="C101" s="42" t="inlineStr">
+        <is>
+          <t>JASON C. GUEVARRA</t>
+        </is>
+      </c>
+      <c r="D101" s="43" t="inlineStr">
+        <is>
+          <t>FITTER</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="15" customHeight="1">
+      <c r="A102" s="10" t="n">
+        <v>33</v>
+      </c>
+      <c r="B102" s="11" t="inlineStr">
+        <is>
+          <t>13009023</t>
+        </is>
+      </c>
+      <c r="C102" s="42" t="inlineStr">
+        <is>
+          <t>SAMEER ALDUSUQI</t>
+        </is>
+      </c>
+      <c r="D102" s="43" t="inlineStr">
+        <is>
+          <t>FITTER</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="15" customHeight="1">
+      <c r="A103" s="10" t="n">
+        <v>34</v>
+      </c>
+      <c r="B103" s="11" t="inlineStr">
+        <is>
+          <t>13004037</t>
+        </is>
+      </c>
+      <c r="C103" s="42" t="inlineStr">
+        <is>
+          <t>KHALID FAISAL AL-ALAWI</t>
+        </is>
+      </c>
+      <c r="D103" s="43" t="inlineStr">
+        <is>
+          <t>SUPV</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="15" customHeight="1">
+      <c r="A104" s="10" t="n">
+        <v>35</v>
+      </c>
+      <c r="B104" s="11" t="inlineStr">
+        <is>
+          <t>13010931</t>
+        </is>
+      </c>
+      <c r="C104" s="42" t="inlineStr">
+        <is>
+          <t>SULTAN ALMASRI</t>
+        </is>
+      </c>
+      <c r="D104" s="43" t="inlineStr">
+        <is>
+          <t>TECH</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="15" customHeight="1">
+      <c r="A105" s="10" t="n">
+        <v>36</v>
+      </c>
+      <c r="B105" s="11" t="inlineStr">
+        <is>
+          <t>30003319</t>
+        </is>
+      </c>
+      <c r="C105" s="42" t="inlineStr">
+        <is>
+          <t>MANSOUR ALHARBI</t>
+        </is>
+      </c>
+      <c r="D105" s="43" t="inlineStr">
+        <is>
+          <t>TECH</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="15" customHeight="1">
+      <c r="A106" s="10" t="n">
+        <v>37</v>
+      </c>
+      <c r="B106" s="11" t="inlineStr">
+        <is>
+          <t>30003362</t>
+        </is>
+      </c>
+      <c r="C106" s="42" t="inlineStr">
+        <is>
+          <t>AYMAN HAMED</t>
+        </is>
+      </c>
+      <c r="D106" s="43" t="inlineStr">
+        <is>
+          <t>TECH</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="15" customHeight="1">
+      <c r="A107" s="10" t="n">
+        <v>38</v>
+      </c>
+      <c r="B107" s="11" t="inlineStr">
+        <is>
+          <t>30003449</t>
+        </is>
+      </c>
+      <c r="C107" s="42" t="inlineStr">
+        <is>
+          <t>HAZEM ALSUBHI</t>
+        </is>
+      </c>
+      <c r="D107" s="43" t="inlineStr">
+        <is>
+          <t>TECH</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="15" customHeight="1">
+      <c r="A108" s="10" t="n">
+        <v>39</v>
+      </c>
+      <c r="B108" s="11" t="inlineStr">
+        <is>
+          <t>30003471</t>
+        </is>
+      </c>
+      <c r="C108" s="42" t="inlineStr">
+        <is>
+          <t>MOHAMMED ALOQBA</t>
+        </is>
+      </c>
+      <c r="D108" s="43" t="inlineStr">
+        <is>
+          <t>TECH</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="15" customHeight="1">
+      <c r="A109" s="10" t="n">
+        <v>40</v>
+      </c>
+      <c r="B109" s="11" t="inlineStr">
+        <is>
+          <t>30003607</t>
+        </is>
+      </c>
+      <c r="C109" s="42" t="inlineStr">
+        <is>
+          <t>SIRAJ KHAYAT</t>
+        </is>
+      </c>
+      <c r="D109" s="43" t="inlineStr">
+        <is>
+          <t>TECH</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="15" customHeight="1">
+      <c r="A110" s="10" t="n">
+        <v>41</v>
+      </c>
+      <c r="B110" s="11" t="inlineStr">
+        <is>
+          <t>30004358</t>
+        </is>
+      </c>
+      <c r="C110" s="42" t="inlineStr">
+        <is>
+          <t>SALMAN ALJAADANI</t>
+        </is>
+      </c>
+      <c r="D110" s="43" t="inlineStr">
+        <is>
+          <t>TECH</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="15" customHeight="1">
+      <c r="A111" s="10" t="n">
+        <v>42</v>
+      </c>
+      <c r="B111" s="11" t="inlineStr">
+        <is>
+          <t>30004434</t>
+        </is>
+      </c>
+      <c r="C111" s="42" t="inlineStr">
+        <is>
+          <t>EID ALRIFAI</t>
+        </is>
+      </c>
+      <c r="D111" s="43" t="inlineStr">
+        <is>
+          <t>TECH</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="15" customHeight="1">
+      <c r="A112" s="10" t="n">
+        <v>43</v>
+      </c>
+      <c r="B112" s="11" t="inlineStr">
+        <is>
+          <t>30004838</t>
+        </is>
+      </c>
+      <c r="C112" s="42" t="inlineStr">
+        <is>
+          <t>MUAED MEERA</t>
+        </is>
+      </c>
+      <c r="D112" s="43" t="inlineStr">
+        <is>
+          <t>TECH</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="40">
-    <mergeCell ref="A5:D5"/>
+  <mergeCells count="39">
+    <mergeCell ref="H66:K66"/>
+    <mergeCell ref="T66:W66"/>
+    <mergeCell ref="R64:S64"/>
+    <mergeCell ref="H65:K65"/>
     <mergeCell ref="E2:AI2"/>
-    <mergeCell ref="AB58:AC58"/>
-    <mergeCell ref="C58:D58"/>
-    <mergeCell ref="E1:AE1"/>
-    <mergeCell ref="V58:W58"/>
-    <mergeCell ref="J59:K59"/>
-    <mergeCell ref="H58:I58"/>
-    <mergeCell ref="R59:S59"/>
-    <mergeCell ref="AF1:AI1"/>
-    <mergeCell ref="A44:D44"/>
-    <mergeCell ref="F59:G59"/>
-    <mergeCell ref="T58:U58"/>
-    <mergeCell ref="AD59:AE59"/>
-    <mergeCell ref="H59:I59"/>
-    <mergeCell ref="A31:D31"/>
-    <mergeCell ref="A51:C54"/>
-    <mergeCell ref="P59:Q59"/>
-    <mergeCell ref="T59:U59"/>
-    <mergeCell ref="V59:W59"/>
-    <mergeCell ref="AB59:AC59"/>
-    <mergeCell ref="N58:O58"/>
-    <mergeCell ref="Z58:AA58"/>
-    <mergeCell ref="C59:D59"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="C60:D60"/>
-    <mergeCell ref="L58:M58"/>
-    <mergeCell ref="X58:Y58"/>
-    <mergeCell ref="AF59:AG59"/>
-    <mergeCell ref="AF58:AG58"/>
-    <mergeCell ref="N59:O59"/>
-    <mergeCell ref="F58:G58"/>
-    <mergeCell ref="A18:D18"/>
-    <mergeCell ref="L59:M59"/>
-    <mergeCell ref="X59:Y59"/>
-    <mergeCell ref="P58:Q58"/>
-    <mergeCell ref="Z59:AA59"/>
-    <mergeCell ref="R58:S58"/>
-    <mergeCell ref="J58:K58"/>
-    <mergeCell ref="AD58:AE58"/>
+    <mergeCell ref="F65:G65"/>
+    <mergeCell ref="AD64:AE64"/>
+    <mergeCell ref="L66:M66"/>
+    <mergeCell ref="A48:AI48"/>
+    <mergeCell ref="C64:D64"/>
+    <mergeCell ref="X66:Y66"/>
+    <mergeCell ref="A68:J68"/>
+    <mergeCell ref="N65:Q65"/>
+    <mergeCell ref="C65:D65"/>
+    <mergeCell ref="Z65:AC65"/>
+    <mergeCell ref="A1:AI1"/>
+    <mergeCell ref="A57:C61"/>
+    <mergeCell ref="R65:S65"/>
+    <mergeCell ref="AD65:AE65"/>
+    <mergeCell ref="F66:G66"/>
+    <mergeCell ref="L64:M64"/>
+    <mergeCell ref="X65:Y65"/>
+    <mergeCell ref="N66:Q66"/>
+    <mergeCell ref="Z66:AC66"/>
+    <mergeCell ref="X64:Y64"/>
+    <mergeCell ref="A18:AI18"/>
+    <mergeCell ref="A3:AI3"/>
+    <mergeCell ref="H64:K64"/>
+    <mergeCell ref="T65:W65"/>
+    <mergeCell ref="R66:S66"/>
+    <mergeCell ref="AF65:AI65"/>
+    <mergeCell ref="A33:AI33"/>
+    <mergeCell ref="N64:Q64"/>
+    <mergeCell ref="T64:W64"/>
+    <mergeCell ref="C66:D66"/>
+    <mergeCell ref="L65:M65"/>
+    <mergeCell ref="Z64:AC64"/>
+    <mergeCell ref="AF64:AI64"/>
+    <mergeCell ref="F64:G64"/>
   </mergeCells>
   <conditionalFormatting sqref="E6:AI17">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
@@ -4124,10 +5714,10 @@
       <formula>"N"</formula>
     </cfRule>
     <cfRule type="expression" priority="15" dxfId="14">
-      <formula>AND(E$4&lt;&gt;"",OR(E$3="Fri",E$3="Sat"))</formula>
+      <formula>AND(E$5&lt;&gt;"",OR(E$4="Fri",E$4="Sat"))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E19:AI30">
+  <conditionalFormatting sqref="E21:AI32">
     <cfRule type="cellIs" priority="16" operator="equal" dxfId="0">
       <formula>"D"</formula>
     </cfRule>
@@ -4171,10 +5761,10 @@
       <formula>"N"</formula>
     </cfRule>
     <cfRule type="expression" priority="30" dxfId="14">
-      <formula>AND(E$4&lt;&gt;"",OR(E$3="Fri",E$3="Sat"))</formula>
+      <formula>AND(E$5&lt;&gt;"",OR(E$4="Fri",E$4="Sat"))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E32:AI43">
+  <conditionalFormatting sqref="E36:AI47">
     <cfRule type="cellIs" priority="31" operator="equal" dxfId="0">
       <formula>"D"</formula>
     </cfRule>
@@ -4218,10 +5808,10 @@
       <formula>"N"</formula>
     </cfRule>
     <cfRule type="expression" priority="45" dxfId="14">
-      <formula>AND(E$4&lt;&gt;"",OR(E$3="Fri",E$3="Sat"))</formula>
+      <formula>AND(E$5&lt;&gt;"",OR(E$4="Fri",E$4="Sat"))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E45:AI49">
+  <conditionalFormatting sqref="E51:AI55">
     <cfRule type="cellIs" priority="46" operator="equal" dxfId="0">
       <formula>"D"</formula>
     </cfRule>
@@ -4265,9 +5855,54 @@
       <formula>"N"</formula>
     </cfRule>
     <cfRule type="expression" priority="60" dxfId="14">
-      <formula>AND(E$4&lt;&gt;"",OR(E$3="Fri",E$3="Sat"))</formula>
+      <formula>AND(E$5&lt;&gt;"",OR(E$4="Fri",E$4="Sat"))</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="A6:D17">
+    <cfRule type="expression" priority="61" dxfId="15">
+      <formula>$D6="OJT"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="62" dxfId="16">
+      <formula>$D6="ACT/SUPV"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A21:D32">
+    <cfRule type="expression" priority="63" dxfId="15">
+      <formula>$D21="OJT"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="64" dxfId="16">
+      <formula>$D21="ACT/SUPV"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A36:D47">
+    <cfRule type="expression" priority="65" dxfId="15">
+      <formula>$D36="OJT"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="66" dxfId="16">
+      <formula>$D36="ACT/SUPV"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A51:D55">
+    <cfRule type="expression" priority="67" dxfId="15">
+      <formula>$D51="OJT"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="68" dxfId="16">
+      <formula>$D51="ACT/SUPV"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A70:D112">
+    <cfRule type="expression" priority="69" dxfId="15">
+      <formula>$D70="OJT"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="70" dxfId="16">
+      <formula>$D70="ACT/SUPV"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="E6:AI17 E21:AI32 E36:AI47 E51:AI55" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"D,T,G,TR,V,R,A,H,OT,OS,S/L,C/T,L,N"</formula1>
+    </dataValidation>
+  </dataValidations>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.3" bottom="0.3" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
